--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G14">

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4">

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G4">

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q31">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-26 19:30:00</t>
+          <t>2026-10-26 19:05:00</t>
         </is>
       </c>
     </row>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC42">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q34">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC33">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="O15">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="P15">
-        <v>1.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>7.17</v>
+        <v>11</v>
       </c>
       <c r="O16">
-        <v>4.45</v>
+        <v>6.3</v>
       </c>
       <c r="P16">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.71</v>
+        <v>7.17</v>
       </c>
       <c r="O17">
-        <v>3.15</v>
+        <v>4.45</v>
       </c>
       <c r="P17">
-        <v>2.78</v>
+        <v>1.4</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-26 13:30:00</t>
+          <t>2026-10-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.9</v>
+        <v>2.71</v>
       </c>
       <c r="O18">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="P18">
-        <v>3.44</v>
+        <v>2.78</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-26 13:45:00</t>
+          <t>2026-10-26 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.66</v>
+        <v>1.9</v>
       </c>
       <c r="O19">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="P19">
-        <v>2.29</v>
+        <v>3.44</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-26 14:00:00</t>
+          <t>2026-10-26 13:45:00</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="O23">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.56</v>
+        <v>3.12</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
       <c r="O24">
         <v>3.28</v>
       </c>
       <c r="P24">
-        <v>3.07</v>
+        <v>2.56</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-10-26 14:30:00</t>
+          <t>2026-10-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.56</v>
+        <v>2.23</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P25">
-        <v>1.67</v>
+        <v>3.07</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-26 15:00:00</t>
+          <t>2026-10-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.31</v>
+        <v>4.56</v>
       </c>
       <c r="O26">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>7.55</v>
+        <v>1.67</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4663,27 +4663,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.55</v>
+        <v>1.31</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="P27">
-        <v>2.45</v>
+        <v>7.55</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-10-26 15:05:00</t>
+          <t>2026-10-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-10-26 15:30:00</t>
+          <t>2026-10-26 15:05:00</t>
         </is>
       </c>
     </row>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G29">
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-10-26 15:45:00</t>
+          <t>2026-10-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.01</v>
+        <v>8.1</v>
       </c>
       <c r="O31">
-        <v>3.29</v>
+        <v>4.79</v>
       </c>
       <c r="P31">
-        <v>3.82</v>
+        <v>1.43</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-10-26 16:30:00</t>
+          <t>2026-10-26 15:45:00</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.64</v>
+        <v>2.01</v>
       </c>
       <c r="O32">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="P32">
-        <v>2.3</v>
+        <v>3.82</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.03</v>
+        <v>2.64</v>
       </c>
       <c r="O33">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="P33">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
+        <v>2</v>
+      </c>
+      <c r="AB33">
         <v>1.8</v>
-      </c>
-      <c r="AB33">
-        <v>2</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.89</v>
+        <v>2.03</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P34">
-        <v>2.43</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-26 16:45:00</t>
+          <t>2026-10-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.32</v>
+        <v>2.89</v>
       </c>
       <c r="O35">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-26 17:00:00</t>
+          <t>2026-10-26 16:45:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-26 17:30:00</t>
+          <t>2026-10-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-26 17:45:00</t>
+          <t>2026-10-26 17:30:00</t>
         </is>
       </c>
     </row>
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-26 19:00:00</t>
+          <t>2026-10-26 17:45:00</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G40">

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>3.41</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU48"/>
+  <dimension ref="A1:AU49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="O35">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.32</v>
+        <v>2.89</v>
       </c>
       <c r="O36">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-26 17:00:00</t>
+          <t>2026-10-26 16:45:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-26 17:30:00</t>
+          <t>2026-10-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.76</v>
+        <v>2.73</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="P39">
-        <v>4.61</v>
+        <v>2.59</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-26 17:45:00</t>
+          <t>2026-10-26 17:30:00</t>
         </is>
       </c>
     </row>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-26 19:00:00</t>
+          <t>2026-10-26 17:45:00</t>
         </is>
       </c>
     </row>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-26 19:05:00</t>
+          <t>2026-10-26 19:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-26 19:30:00</t>
+          <t>2026-10-26 19:05:00</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-26 20:00:00</t>
+          <t>2026-10-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-10-26 20:30:00</t>
+          <t>2026-10-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-10-26 21:00:00</t>
+          <t>2026-10-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,156 +8086,319 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Montego Bay United</t>
         </is>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>0</v>
-      </c>
-      <c r="AB48">
-        <v>0</v>
-      </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
-        <v>0</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>0</v>
-      </c>
-      <c r="AG48">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>0</v>
-      </c>
-      <c r="AK48">
-        <v>0</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>-1</v>
-      </c>
-      <c r="AN48">
-        <v>-1</v>
-      </c>
-      <c r="AO48">
-        <v>-1</v>
-      </c>
-      <c r="AP48">
-        <v>-1</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
-        <v>0</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
         <is>
           <t>2026-10-26 22:00:00</t>
         </is>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1785,55 +1785,55 @@
         <v>10.6</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>1.4</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>2.78</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.29</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>3.12</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>2.56</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,34 +4393,34 @@
         <v>3.07</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA25">
         <v>1.85</v>
@@ -4429,19 +4429,19 @@
         <v>1.91</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>1.67</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>7.55</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5371,34 +5371,34 @@
         <v>1.43</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA31">
         <v>1.77</v>
@@ -5407,19 +5407,19 @@
         <v>1.88</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5697,34 +5697,34 @@
         <v>2.3</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA33">
         <v>2</v>
@@ -5733,19 +5733,19 @@
         <v>1.8</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,34 +5860,34 @@
         <v>3.16</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
         <v>1.8</v>
@@ -5896,19 +5896,19 @@
         <v>2</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>2.04</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>4.61</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7979,34 +7979,34 @@
         <v>5.12</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA47">
         <v>1.93</v>
@@ -8015,19 +8015,19 @@
         <v>1.77</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2926,55 +2926,55 @@
         <v>1.15</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>3.44</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>2.45</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>2.43</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>2.59</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7327,34 +7327,34 @@
         <v>3.43</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA43">
         <v>2.03</v>
@@ -7363,19 +7363,19 @@
         <v>1.83</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>7.9</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL46">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P13">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>3.9</v>
+        <v>1.77</v>
       </c>
       <c r="R13">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z13">
-        <v>4.65</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB13">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE13">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG13">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>1.28</v>
+        <v>3.05</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="O14">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P14">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="Q14">
-        <v>1.77</v>
+        <v>3.9</v>
       </c>
       <c r="R14">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
+        <v>1.25</v>
+      </c>
+      <c r="T14">
+        <v>3.6</v>
+      </c>
+      <c r="U14">
+        <v>2.32</v>
+      </c>
+      <c r="V14">
+        <v>1.6</v>
+      </c>
+      <c r="W14">
+        <v>1.11</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
+        <v>1.12</v>
+      </c>
+      <c r="Z14">
+        <v>4.65</v>
+      </c>
+      <c r="AA14">
+        <v>1.57</v>
+      </c>
+      <c r="AB14">
+        <v>2.43</v>
+      </c>
+      <c r="AC14">
+        <v>2.28</v>
+      </c>
+      <c r="AD14">
+        <v>1.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.18</v>
+      </c>
+      <c r="AF14">
+        <v>1.5</v>
+      </c>
+      <c r="AG14">
+        <v>2.45</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.2</v>
       </c>
-      <c r="T14">
-        <v>4</v>
-      </c>
-      <c r="U14">
-        <v>2</v>
-      </c>
-      <c r="V14">
-        <v>1.75</v>
-      </c>
-      <c r="W14">
-        <v>1.2</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.07</v>
-      </c>
-      <c r="Z14">
-        <v>7</v>
-      </c>
-      <c r="AA14">
-        <v>1.36</v>
-      </c>
-      <c r="AB14">
-        <v>2.7</v>
-      </c>
-      <c r="AC14">
-        <v>2.1</v>
-      </c>
-      <c r="AD14">
-        <v>1.8</v>
-      </c>
-      <c r="AE14">
-        <v>1.27</v>
-      </c>
-      <c r="AF14">
-        <v>1.61</v>
-      </c>
-      <c r="AG14">
-        <v>2.3</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.14</v>
-      </c>
       <c r="AK14">
-        <v>3.05</v>
+        <v>1.28</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7">

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU49"/>
+  <dimension ref="A1:AU50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G6">
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="S6">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
+        <v>1.53</v>
+      </c>
+      <c r="W6">
+        <v>1.12</v>
+      </c>
+      <c r="X6">
+        <v>1.02</v>
+      </c>
+      <c r="Y6">
+        <v>1.16</v>
+      </c>
+      <c r="Z6">
+        <v>4.15</v>
+      </c>
+      <c r="AA6">
+        <v>1.61</v>
+      </c>
+      <c r="AB6">
+        <v>2.13</v>
+      </c>
+      <c r="AC6">
+        <v>2.49</v>
+      </c>
+      <c r="AD6">
+        <v>1.42</v>
+      </c>
+      <c r="AE6">
+        <v>1.13</v>
+      </c>
+      <c r="AF6">
         <v>1.75</v>
       </c>
-      <c r="W6">
-        <v>1.2</v>
-      </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>1.11</v>
-      </c>
-      <c r="Z6">
-        <v>6.09</v>
-      </c>
-      <c r="AA6">
-        <v>1.38</v>
-      </c>
-      <c r="AB6">
-        <v>2.89</v>
-      </c>
-      <c r="AC6">
-        <v>2.01</v>
-      </c>
-      <c r="AD6">
-        <v>1.78</v>
-      </c>
-      <c r="AE6">
-        <v>1.3</v>
-      </c>
-      <c r="AF6">
-        <v>1.65</v>
-      </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G7">
@@ -1459,55 +1459,55 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="R7">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z7">
-        <v>4.15</v>
+        <v>6.09</v>
       </c>
       <c r="AA7">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AB7">
-        <v>2.13</v>
+        <v>2.89</v>
       </c>
       <c r="AC7">
-        <v>2.49</v>
+        <v>2.01</v>
       </c>
       <c r="AD7">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK7">
-        <v>2.43</v>
+        <v>3.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:30:00</t>
+          <t>2026-10-26 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-26 11:00:00</t>
+          <t>2026-10-26 10:30:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.94</v>
+        <v>1.23</v>
       </c>
       <c r="O10">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>3.56</v>
+        <v>10.6</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-26 12:00:00</t>
+          <t>2026-10-26 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Halaba Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Halaba Ketema</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
+        <v>2.1</v>
+      </c>
+      <c r="O13">
+        <v>3.1</v>
+      </c>
+      <c r="P13">
+        <v>3.3</v>
+      </c>
+      <c r="Q13">
+        <v>2.8</v>
+      </c>
+      <c r="R13">
+        <v>1.95</v>
+      </c>
+      <c r="S13">
+        <v>1.44</v>
+      </c>
+      <c r="T13">
+        <v>2.45</v>
+      </c>
+      <c r="U13">
+        <v>3.3</v>
+      </c>
+      <c r="V13">
+        <v>1.29</v>
+      </c>
+      <c r="W13">
+        <v>1.03</v>
+      </c>
+      <c r="X13">
+        <v>1.04</v>
+      </c>
+      <c r="Y13">
         <v>1.4</v>
       </c>
-      <c r="O13">
-        <v>5.25</v>
-      </c>
-      <c r="P13">
-        <v>7</v>
-      </c>
-      <c r="Q13">
-        <v>1.77</v>
-      </c>
-      <c r="R13">
-        <v>2.6</v>
-      </c>
-      <c r="S13">
-        <v>1.2</v>
-      </c>
-      <c r="T13">
-        <v>4</v>
-      </c>
-      <c r="U13">
-        <v>2</v>
-      </c>
-      <c r="V13">
-        <v>1.75</v>
-      </c>
-      <c r="W13">
-        <v>1.2</v>
-      </c>
-      <c r="X13">
+      <c r="Z13">
+        <v>2.56</v>
+      </c>
+      <c r="AA13">
+        <v>2.5</v>
+      </c>
+      <c r="AB13">
+        <v>1.5</v>
+      </c>
+      <c r="AC13">
+        <v>4.35</v>
+      </c>
+      <c r="AD13">
+        <v>1.17</v>
+      </c>
+      <c r="AE13">
         <v>1.01</v>
       </c>
-      <c r="Y13">
-        <v>1.07</v>
-      </c>
-      <c r="Z13">
-        <v>7</v>
-      </c>
-      <c r="AA13">
-        <v>1.36</v>
-      </c>
-      <c r="AB13">
-        <v>2.7</v>
-      </c>
-      <c r="AC13">
-        <v>2.1</v>
-      </c>
-      <c r="AD13">
-        <v>1.8</v>
-      </c>
-      <c r="AE13">
-        <v>1.27</v>
-      </c>
       <c r="AF13">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AK13">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-26 13:00:00</t>
+          <t>2026-10-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="O14">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P14">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>3.9</v>
+        <v>1.77</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>4.65</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AC14">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AD14">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE14">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AF14">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG14">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>1.28</v>
+        <v>3.05</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA15">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>1.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="O16">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="P16">
-        <v>1.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="AB16">
-        <v>2.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC16">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>7.17</v>
+        <v>11</v>
       </c>
       <c r="O17">
-        <v>4.45</v>
+        <v>6.3</v>
       </c>
       <c r="P17">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="Q17">
-        <v>6.54</v>
+        <v>8.75</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="T17">
-        <v>3.22</v>
+        <v>4.5</v>
       </c>
       <c r="U17">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z17">
-        <v>3.88</v>
+        <v>5.45</v>
       </c>
       <c r="AA17">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AB17">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="AC17">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="AD17">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG17">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AK17">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.71</v>
+        <v>7.17</v>
       </c>
       <c r="O18">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q18">
-        <v>3.48</v>
+        <v>5.54</v>
       </c>
       <c r="R18">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="S18">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="U18">
-        <v>3.48</v>
+        <v>2.54</v>
       </c>
       <c r="V18">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="W18">
+        <v>1.12</v>
+      </c>
+      <c r="X18">
         <v>1.03</v>
       </c>
-      <c r="X18">
-        <v>1.05</v>
-      </c>
       <c r="Y18">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>2.49</v>
+        <v>3.84</v>
       </c>
       <c r="AA18">
-        <v>2.49</v>
+        <v>1.71</v>
       </c>
       <c r="AB18">
-        <v>1.55</v>
+        <v>2.08</v>
       </c>
       <c r="AC18">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD18">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="AG18">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-26 13:30:00</t>
+          <t>2026-10-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.9</v>
+        <v>2.71</v>
       </c>
       <c r="O19">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>3.44</v>
+        <v>2.78</v>
       </c>
       <c r="Q19">
-        <v>2.48</v>
+        <v>3.48</v>
       </c>
       <c r="R19">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="T19">
-        <v>3.08</v>
+        <v>2.31</v>
       </c>
       <c r="U19">
-        <v>2.44</v>
+        <v>3.48</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="Z19">
-        <v>3.58</v>
+        <v>2.49</v>
       </c>
       <c r="AA19">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="AB19">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AC19">
-        <v>2.83</v>
+        <v>4.6</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>1.63</v>
+        <v>1.99</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-26 13:45:00</t>
+          <t>2026-10-26 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.66</v>
+        <v>1.9</v>
       </c>
       <c r="O20">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="P20">
-        <v>2.29</v>
+        <v>3.44</v>
       </c>
       <c r="Q20">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S20">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U20">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z20">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AA20">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AC20">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD20">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG20">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-10-26 14:00:00</t>
+          <t>2026-10-26 13:45:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="O21">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="P21">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="Q21">
-        <v>4.32</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T21">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U21">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V21">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>4.17</v>
+        <v>3.72</v>
       </c>
       <c r="AA21">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AB21">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AC21">
-        <v>2.42</v>
+        <v>2.78</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE21">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
         <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AK21">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q22">
-        <v>2.3</v>
+        <v>4.32</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S22">
         <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>3.58</v>
+        <v>4.17</v>
       </c>
       <c r="AA22">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB22">
-        <v>1.92</v>
+        <v>2.21</v>
       </c>
       <c r="AC22">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="AD22">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF22">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.91</v>
+        <v>1.19</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q23">
+        <v>2.3</v>
+      </c>
+      <c r="R23">
+        <v>2.25</v>
+      </c>
+      <c r="S23">
+        <v>1.3</v>
+      </c>
+      <c r="T23">
+        <v>3.2</v>
+      </c>
+      <c r="U23">
+        <v>2.63</v>
+      </c>
+      <c r="V23">
+        <v>1.44</v>
+      </c>
+      <c r="W23">
+        <v>1.1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1.21</v>
+      </c>
+      <c r="Z23">
+        <v>3.58</v>
+      </c>
+      <c r="AA23">
+        <v>1.76</v>
+      </c>
+      <c r="AB23">
+        <v>1.92</v>
+      </c>
+      <c r="AC23">
         <v>2.88</v>
       </c>
-      <c r="R23">
-        <v>2.38</v>
-      </c>
-      <c r="S23">
+      <c r="AD23">
+        <v>1.32</v>
+      </c>
+      <c r="AE23">
+        <v>1.09</v>
+      </c>
+      <c r="AF23">
+        <v>1.71</v>
+      </c>
+      <c r="AG23">
+        <v>2</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.22</v>
       </c>
-      <c r="T23">
-        <v>3.56</v>
-      </c>
-      <c r="U23">
-        <v>2.14</v>
-      </c>
-      <c r="V23">
-        <v>1.64</v>
-      </c>
-      <c r="W23">
-        <v>1.15</v>
-      </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.12</v>
-      </c>
-      <c r="Z23">
-        <v>4.75</v>
-      </c>
-      <c r="AA23">
-        <v>1.47</v>
-      </c>
-      <c r="AB23">
-        <v>2.35</v>
-      </c>
-      <c r="AC23">
-        <v>2.25</v>
-      </c>
-      <c r="AD23">
-        <v>1.59</v>
-      </c>
-      <c r="AE23">
-        <v>1.21</v>
-      </c>
-      <c r="AF23">
-        <v>1.44</v>
-      </c>
-      <c r="AG23">
-        <v>2.62</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.25</v>
-      </c>
       <c r="AK23">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="O24">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.56</v>
+        <v>3.12</v>
       </c>
       <c r="Q24">
-        <v>3.63</v>
+        <v>2.88</v>
       </c>
       <c r="R24">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>2.82</v>
+        <v>3.56</v>
       </c>
       <c r="U24">
-        <v>2.74</v>
+        <v>2.14</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
+        <v>1.12</v>
+      </c>
+      <c r="Z24">
+        <v>4.75</v>
+      </c>
+      <c r="AA24">
+        <v>1.47</v>
+      </c>
+      <c r="AB24">
+        <v>2.35</v>
+      </c>
+      <c r="AC24">
+        <v>2.25</v>
+      </c>
+      <c r="AD24">
+        <v>1.59</v>
+      </c>
+      <c r="AE24">
+        <v>1.21</v>
+      </c>
+      <c r="AF24">
+        <v>1.44</v>
+      </c>
+      <c r="AG24">
+        <v>2.62</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.25</v>
       </c>
-      <c r="Z24">
-        <v>3.28</v>
-      </c>
-      <c r="AA24">
-        <v>1.95</v>
-      </c>
-      <c r="AB24">
-        <v>1.82</v>
-      </c>
-      <c r="AC24">
-        <v>3.2</v>
-      </c>
-      <c r="AD24">
-        <v>1.26</v>
-      </c>
-      <c r="AE24">
-        <v>1.05</v>
-      </c>
-      <c r="AF24">
-        <v>1.7</v>
-      </c>
-      <c r="AG24">
-        <v>2.04</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.28</v>
-      </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,28 +4384,28 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
       <c r="O25">
         <v>3.28</v>
       </c>
       <c r="P25">
-        <v>3.07</v>
+        <v>2.56</v>
       </c>
       <c r="Q25">
-        <v>3.18</v>
+        <v>3.63</v>
       </c>
       <c r="R25">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="S25">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="U25">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="V25">
         <v>1.38</v>
@@ -4417,22 +4417,22 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
+        <v>1.25</v>
+      </c>
+      <c r="Z25">
+        <v>3.28</v>
+      </c>
+      <c r="AA25">
+        <v>1.95</v>
+      </c>
+      <c r="AB25">
+        <v>1.82</v>
+      </c>
+      <c r="AC25">
+        <v>3.2</v>
+      </c>
+      <c r="AD25">
         <v>1.26</v>
-      </c>
-      <c r="Z25">
-        <v>3.2</v>
-      </c>
-      <c r="AA25">
-        <v>1.85</v>
-      </c>
-      <c r="AB25">
-        <v>1.91</v>
-      </c>
-      <c r="AC25">
-        <v>3.32</v>
-      </c>
-      <c r="AD25">
-        <v>1.3</v>
       </c>
       <c r="AE25">
         <v>1.05</v>
@@ -4441,7 +4441,7 @@
         <v>1.7</v>
       </c>
       <c r="AG25">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-26 14:30:00</t>
+          <t>2026-10-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.56</v>
+        <v>2.23</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P26">
-        <v>1.67</v>
+        <v>3.07</v>
       </c>
       <c r="Q26">
-        <v>6.5</v>
+        <v>3.18</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U26">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z26">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA26">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC26">
-        <v>2.92</v>
+        <v>3.32</v>
       </c>
       <c r="AD26">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AG26">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AK26">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-26 15:00:00</t>
+          <t>2026-10-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
+        <v>4.56</v>
+      </c>
+      <c r="O27">
+        <v>3.6</v>
+      </c>
+      <c r="P27">
+        <v>1.67</v>
+      </c>
+      <c r="Q27">
+        <v>6.5</v>
+      </c>
+      <c r="R27">
+        <v>2.25</v>
+      </c>
+      <c r="S27">
+        <v>1.33</v>
+      </c>
+      <c r="T27">
+        <v>3</v>
+      </c>
+      <c r="U27">
+        <v>2.67</v>
+      </c>
+      <c r="V27">
+        <v>1.4</v>
+      </c>
+      <c r="W27">
+        <v>1.06</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>1.24</v>
+      </c>
+      <c r="Z27">
+        <v>3.34</v>
+      </c>
+      <c r="AA27">
+        <v>1.84</v>
+      </c>
+      <c r="AB27">
+        <v>1.95</v>
+      </c>
+      <c r="AC27">
+        <v>2.92</v>
+      </c>
+      <c r="AD27">
         <v>1.31</v>
       </c>
-      <c r="O27">
-        <v>5.6</v>
-      </c>
-      <c r="P27">
-        <v>7.55</v>
-      </c>
-      <c r="Q27">
-        <v>1.82</v>
-      </c>
-      <c r="R27">
-        <v>2.44</v>
-      </c>
-      <c r="S27">
-        <v>1.2</v>
-      </c>
-      <c r="T27">
-        <v>3.8</v>
-      </c>
-      <c r="U27">
-        <v>2.23</v>
-      </c>
-      <c r="V27">
-        <v>1.65</v>
-      </c>
-      <c r="W27">
-        <v>1.11</v>
-      </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
-        <v>1.1</v>
-      </c>
-      <c r="Z27">
-        <v>5.05</v>
-      </c>
-      <c r="AA27">
-        <v>1.53</v>
-      </c>
-      <c r="AB27">
-        <v>2.38</v>
-      </c>
-      <c r="AC27">
-        <v>2.26</v>
-      </c>
-      <c r="AD27">
-        <v>1.65</v>
-      </c>
       <c r="AE27">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AG27">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>2.95</v>
+        <v>1.07</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.55</v>
+        <v>1.31</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="P28">
-        <v>2.45</v>
+        <v>7.55</v>
       </c>
       <c r="Q28">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="U28">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W28">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
+        <v>1.1</v>
+      </c>
+      <c r="Z28">
+        <v>5.05</v>
+      </c>
+      <c r="AA28">
+        <v>1.53</v>
+      </c>
+      <c r="AB28">
+        <v>2.38</v>
+      </c>
+      <c r="AC28">
+        <v>2.26</v>
+      </c>
+      <c r="AD28">
+        <v>1.65</v>
+      </c>
+      <c r="AE28">
         <v>1.19</v>
       </c>
-      <c r="Z28">
-        <v>4.01</v>
-      </c>
-      <c r="AA28">
-        <v>1.73</v>
-      </c>
-      <c r="AB28">
-        <v>2.02</v>
-      </c>
-      <c r="AC28">
-        <v>2.74</v>
-      </c>
-      <c r="AD28">
-        <v>1.35</v>
-      </c>
-      <c r="AE28">
-        <v>1.1</v>
-      </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK28">
-        <v>1.65</v>
+        <v>2.95</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-10-26 15:05:00</t>
+          <t>2026-10-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="Q29">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R29">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="U29">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="V29">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z29">
-        <v>5.51</v>
+        <v>4.01</v>
       </c>
       <c r="AA29">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AB29">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="AC29">
+        <v>2.74</v>
+      </c>
+      <c r="AD29">
+        <v>1.35</v>
+      </c>
+      <c r="AE29">
+        <v>1.1</v>
+      </c>
+      <c r="AF29">
+        <v>1.6</v>
+      </c>
+      <c r="AG29">
         <v>2.19</v>
       </c>
-      <c r="AD29">
-        <v>1.62</v>
-      </c>
-      <c r="AE29">
-        <v>1.22</v>
-      </c>
-      <c r="AF29">
-        <v>1.41</v>
-      </c>
-      <c r="AG29">
-        <v>2.69</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
         <v>1.65</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-10-26 15:30:00</t>
+          <t>2026-10-26 15:05:00</t>
         </is>
       </c>
     </row>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>7.42</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-10-26 15:45:00</t>
+          <t>2026-10-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.01</v>
+        <v>8.1</v>
       </c>
       <c r="O32">
-        <v>3.29</v>
+        <v>4.79</v>
       </c>
       <c r="P32">
-        <v>3.82</v>
+        <v>1.43</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA32">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AB32">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-10-26 16:30:00</t>
+          <t>2026-10-26 15:45:00</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.64</v>
+        <v>2.01</v>
       </c>
       <c r="O33">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="P33">
-        <v>2.3</v>
+        <v>3.82</v>
       </c>
       <c r="Q33">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC33">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.03</v>
+        <v>2.64</v>
       </c>
       <c r="O34">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>2.59</v>
+        <v>3.6</v>
       </c>
       <c r="R34">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AA34">
+        <v>2</v>
+      </c>
+      <c r="AB34">
         <v>1.8</v>
       </c>
-      <c r="AB34">
-        <v>2</v>
-      </c>
       <c r="AC34">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD34">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AG34">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="AK34">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
+        <v>2.03</v>
+      </c>
+      <c r="O35">
+        <v>3.34</v>
+      </c>
+      <c r="P35">
+        <v>3.16</v>
+      </c>
+      <c r="Q35">
+        <v>2.59</v>
+      </c>
+      <c r="R35">
+        <v>2.14</v>
+      </c>
+      <c r="S35">
+        <v>1.28</v>
+      </c>
+      <c r="T35">
+        <v>3.08</v>
+      </c>
+      <c r="U35">
         <v>2.45</v>
-      </c>
-      <c r="O35">
-        <v>3.3</v>
-      </c>
-      <c r="P35">
-        <v>2.5</v>
-      </c>
-      <c r="Q35">
-        <v>3.09</v>
-      </c>
-      <c r="R35">
-        <v>2.1</v>
-      </c>
-      <c r="S35">
-        <v>1.33</v>
-      </c>
-      <c r="T35">
-        <v>3.17</v>
-      </c>
-      <c r="U35">
-        <v>2.5</v>
       </c>
       <c r="V35">
         <v>1.44</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z35">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB35">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD35">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-26 16:45:00</t>
+          <t>2026-10-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="O36">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q36">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="R36">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="U36">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="V36">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="AA36">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB36">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD36">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AE36">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AG36">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.32</v>
+        <v>2.89</v>
       </c>
       <c r="O37">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="Q37">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R37">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="S37">
+        <v>1.45</v>
+      </c>
+      <c r="T37">
+        <v>2.7</v>
+      </c>
+      <c r="U37">
+        <v>3.2</v>
+      </c>
+      <c r="V37">
+        <v>1.35</v>
+      </c>
+      <c r="W37">
+        <v>1.03</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.3</v>
+      </c>
+      <c r="Z37">
+        <v>2.97</v>
+      </c>
+      <c r="AA37">
+        <v>2.05</v>
+      </c>
+      <c r="AB37">
+        <v>1.72</v>
+      </c>
+      <c r="AC37">
+        <v>3.5</v>
+      </c>
+      <c r="AD37">
+        <v>1.22</v>
+      </c>
+      <c r="AE37">
+        <v>1.04</v>
+      </c>
+      <c r="AF37">
+        <v>1.79</v>
+      </c>
+      <c r="AG37">
+        <v>1.92</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.29</v>
       </c>
-      <c r="T37">
-        <v>2.91</v>
-      </c>
-      <c r="U37">
-        <v>2.47</v>
-      </c>
-      <c r="V37">
-        <v>1.46</v>
-      </c>
-      <c r="W37">
-        <v>1.08</v>
-      </c>
-      <c r="X37">
-        <v>1.03</v>
-      </c>
-      <c r="Y37">
-        <v>1.18</v>
-      </c>
-      <c r="Z37">
-        <v>3.92</v>
-      </c>
-      <c r="AA37">
-        <v>1.73</v>
-      </c>
-      <c r="AB37">
-        <v>2.07</v>
-      </c>
-      <c r="AC37">
-        <v>2.9</v>
-      </c>
-      <c r="AD37">
-        <v>1.39</v>
-      </c>
-      <c r="AE37">
-        <v>1.14</v>
-      </c>
-      <c r="AF37">
-        <v>1.59</v>
-      </c>
-      <c r="AG37">
-        <v>2.18</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.25</v>
-      </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-26 17:00:00</t>
+          <t>2026-10-26 16:45:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,65 +6503,65 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.95</v>
+        <v>3.32</v>
       </c>
       <c r="O38">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="P38">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="Q38">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="R38">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
+        <v>1.29</v>
+      </c>
+      <c r="T38">
+        <v>2.91</v>
+      </c>
+      <c r="U38">
+        <v>2.47</v>
+      </c>
+      <c r="V38">
         <v>1.46</v>
       </c>
-      <c r="T38">
-        <v>2.5</v>
-      </c>
-      <c r="U38">
-        <v>3.29</v>
-      </c>
-      <c r="V38">
-        <v>1.34</v>
-      </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>3.09</v>
+        <v>3.92</v>
       </c>
       <c r="AA38">
+        <v>1.73</v>
+      </c>
+      <c r="AB38">
+        <v>2.07</v>
+      </c>
+      <c r="AC38">
+        <v>2.9</v>
+      </c>
+      <c r="AD38">
+        <v>1.39</v>
+      </c>
+      <c r="AE38">
+        <v>1.14</v>
+      </c>
+      <c r="AF38">
+        <v>1.59</v>
+      </c>
+      <c r="AG38">
         <v>2.18</v>
       </c>
-      <c r="AB38">
-        <v>1.79</v>
-      </c>
-      <c r="AC38">
-        <v>3.72</v>
-      </c>
-      <c r="AD38">
-        <v>1.22</v>
-      </c>
-      <c r="AE38">
-        <v>1.03</v>
-      </c>
-      <c r="AF38">
-        <v>1.87</v>
-      </c>
-      <c r="AG38">
-        <v>1.8</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.73</v>
+        <v>1.95</v>
       </c>
       <c r="O39">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="P39">
+        <v>4</v>
+      </c>
+      <c r="Q39">
         <v>2.59</v>
       </c>
-      <c r="Q39">
-        <v>3.2</v>
-      </c>
       <c r="R39">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T39">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U39">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="V39">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z39">
-        <v>2.92</v>
+        <v>3.09</v>
       </c>
       <c r="AA39">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AB39">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AC39">
-        <v>3.89</v>
+        <v>3.72</v>
       </c>
       <c r="AD39">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE39">
         <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-26 17:30:00</t>
+          <t>2026-10-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.76</v>
+        <v>2.73</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="P40">
-        <v>4.61</v>
+        <v>2.59</v>
       </c>
       <c r="Q40">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="U40">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z40">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA40">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AB40">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AC40">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="AD40">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE40">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG40">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK40">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-26 17:45:00</t>
+          <t>2026-10-26 17:30:00</t>
         </is>
       </c>
     </row>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-26 19:00:00</t>
+          <t>2026-10-26 17:45:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-26 19:05:00</t>
+          <t>2026-10-26 19:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-26 19:30:00</t>
+          <t>2026-10-26 19:05:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.6</v>
+        <v>2.18</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P44">
-        <v>1.98</v>
+        <v>3.43</v>
       </c>
       <c r="Q44">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S44">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T44">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="U44">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W44">
+        <v>1.06</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1.25</v>
+      </c>
+      <c r="Z44">
+        <v>3.28</v>
+      </c>
+      <c r="AA44">
+        <v>2.03</v>
+      </c>
+      <c r="AB44">
+        <v>1.83</v>
+      </c>
+      <c r="AC44">
+        <v>3.14</v>
+      </c>
+      <c r="AD44">
+        <v>1.27</v>
+      </c>
+      <c r="AE44">
         <v>1.07</v>
       </c>
-      <c r="X44">
-        <v>1.02</v>
-      </c>
-      <c r="Y44">
-        <v>1.37</v>
-      </c>
-      <c r="Z44">
-        <v>2.83</v>
-      </c>
-      <c r="AA44">
-        <v>2.1</v>
-      </c>
-      <c r="AB44">
-        <v>1.65</v>
-      </c>
-      <c r="AC44">
-        <v>3.7</v>
-      </c>
-      <c r="AD44">
-        <v>1.2</v>
-      </c>
-      <c r="AE44">
-        <v>1.04</v>
-      </c>
       <c r="AF44">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AG44">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK44">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,81 +7644,81 @@
         </is>
       </c>
       <c r="N45">
+        <v>3.6</v>
+      </c>
+      <c r="O45">
+        <v>3.2</v>
+      </c>
+      <c r="P45">
+        <v>1.98</v>
+      </c>
+      <c r="Q45">
+        <v>4</v>
+      </c>
+      <c r="R45">
+        <v>2.1</v>
+      </c>
+      <c r="S45">
         <v>1.4</v>
       </c>
-      <c r="O45">
-        <v>5.01</v>
-      </c>
-      <c r="P45">
-        <v>7.9</v>
-      </c>
-      <c r="Q45">
-        <v>1.75</v>
-      </c>
-      <c r="R45">
-        <v>2.5</v>
-      </c>
-      <c r="S45">
+      <c r="T45">
+        <v>2.75</v>
+      </c>
+      <c r="U45">
+        <v>2.83</v>
+      </c>
+      <c r="V45">
+        <v>1.36</v>
+      </c>
+      <c r="W45">
+        <v>1.07</v>
+      </c>
+      <c r="X45">
+        <v>1.02</v>
+      </c>
+      <c r="Y45">
+        <v>1.37</v>
+      </c>
+      <c r="Z45">
+        <v>2.83</v>
+      </c>
+      <c r="AA45">
+        <v>2.1</v>
+      </c>
+      <c r="AB45">
+        <v>1.65</v>
+      </c>
+      <c r="AC45">
+        <v>3.7</v>
+      </c>
+      <c r="AD45">
+        <v>1.2</v>
+      </c>
+      <c r="AE45">
+        <v>1.04</v>
+      </c>
+      <c r="AF45">
+        <v>1.89</v>
+      </c>
+      <c r="AG45">
+        <v>1.8</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>1.3</v>
+      </c>
+      <c r="AK45">
         <v>1.25</v>
       </c>
-      <c r="T45">
-        <v>3.55</v>
-      </c>
-      <c r="U45">
-        <v>2.25</v>
-      </c>
-      <c r="V45">
-        <v>1.56</v>
-      </c>
-      <c r="W45">
-        <v>1.12</v>
-      </c>
-      <c r="X45">
-        <v>1.01</v>
-      </c>
-      <c r="Y45">
-        <v>1.19</v>
-      </c>
-      <c r="Z45">
-        <v>4.7</v>
-      </c>
-      <c r="AA45">
-        <v>1.63</v>
-      </c>
-      <c r="AB45">
-        <v>2.33</v>
-      </c>
-      <c r="AC45">
-        <v>2.41</v>
-      </c>
-      <c r="AD45">
-        <v>1.45</v>
-      </c>
-      <c r="AE45">
-        <v>1.15</v>
-      </c>
-      <c r="AF45">
-        <v>1.84</v>
-      </c>
-      <c r="AG45">
-        <v>1.86</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.12</v>
-      </c>
-      <c r="AK45">
-        <v>3.19</v>
-      </c>
       <c r="AL45">
         <v>0</v>
       </c>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-10-26 20:00:00</t>
+          <t>2026-10-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>5.01</v>
       </c>
       <c r="P46">
-        <v>4</v>
+        <v>7.9</v>
       </c>
       <c r="Q46">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="R46">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AA46">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB46">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="AC46">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AD46">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE46">
         <v>1.15</v>
       </c>
       <c r="AF46">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AG46">
-        <v>2.13</v>
+        <v>1.86</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK46">
-        <v>2.1</v>
+        <v>3.19</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O47">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>5.12</v>
+        <v>4</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
+        <v>2.5</v>
+      </c>
+      <c r="V47">
+        <v>1.5</v>
+      </c>
+      <c r="W47">
+        <v>1.11</v>
+      </c>
+      <c r="X47">
+        <v>1.02</v>
+      </c>
+      <c r="Y47">
+        <v>1.17</v>
+      </c>
+      <c r="Z47">
+        <v>4.2</v>
+      </c>
+      <c r="AA47">
+        <v>1.67</v>
+      </c>
+      <c r="AB47">
+        <v>2.16</v>
+      </c>
+      <c r="AC47">
         <v>2.63</v>
       </c>
-      <c r="V47">
-        <v>1.38</v>
-      </c>
-      <c r="W47">
-        <v>1.05</v>
-      </c>
-      <c r="X47">
-        <v>1.01</v>
-      </c>
-      <c r="Y47">
-        <v>1.25</v>
-      </c>
-      <c r="Z47">
-        <v>3.28</v>
-      </c>
-      <c r="AA47">
-        <v>1.93</v>
-      </c>
-      <c r="AB47">
-        <v>1.77</v>
-      </c>
-      <c r="AC47">
-        <v>3.3</v>
-      </c>
       <c r="AD47">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF47">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>1.72</v>
+        <v>2.13</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK47">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-10-26 20:30:00</t>
+          <t>2026-10-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-10-26 21:00:00</t>
+          <t>2026-10-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,156 +8249,319 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Montego Bay United</t>
         </is>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
-      <c r="AG49">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>0</v>
-      </c>
-      <c r="AK49">
-        <v>0</v>
-      </c>
-      <c r="AL49">
-        <v>0</v>
-      </c>
-      <c r="AM49">
-        <v>-1</v>
-      </c>
-      <c r="AN49">
-        <v>-1</v>
-      </c>
-      <c r="AO49">
-        <v>-1</v>
-      </c>
-      <c r="AP49">
-        <v>-1</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-10-26 22:00:00</t>
         </is>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P10">
-        <v>10.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -1954,7 +1954,7 @@
         <v>2.5</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T10">
         <v>3.2</v>
@@ -2621,7 +2621,7 @@
         <v>1.2</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14">
         <v>1.07</v>
@@ -2630,19 +2630,19 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB14">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AC14">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AD14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE14">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF14">
         <v>1.61</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2760,13 +2760,13 @@
         <v>3.9</v>
       </c>
       <c r="P15">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.25</v>
@@ -2775,28 +2775,28 @@
         <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="V15">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA15">
         <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AC15">
         <v>2.28</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
         <v>1.28</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
         <v>2.7</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-26 19:00:00</t>
+          <t>2026-10-26 18:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-26 19:05:00</t>
+          <t>2026-10-26 19:00:00</t>
         </is>
       </c>
     </row>
@@ -7434,27 +7434,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-26 19:30:00</t>
+          <t>2026-10-26 19:05:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.6</v>
+        <v>2.18</v>
       </c>
       <c r="O45">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P45">
-        <v>1.98</v>
+        <v>3.43</v>
       </c>
       <c r="Q45">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="R45">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T45">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="U45">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W45">
+        <v>1.06</v>
+      </c>
+      <c r="X45">
+        <v>1</v>
+      </c>
+      <c r="Y45">
+        <v>1.25</v>
+      </c>
+      <c r="Z45">
+        <v>3.28</v>
+      </c>
+      <c r="AA45">
+        <v>2.03</v>
+      </c>
+      <c r="AB45">
+        <v>1.83</v>
+      </c>
+      <c r="AC45">
+        <v>3.14</v>
+      </c>
+      <c r="AD45">
+        <v>1.27</v>
+      </c>
+      <c r="AE45">
         <v>1.07</v>
       </c>
-      <c r="X45">
-        <v>1.02</v>
-      </c>
-      <c r="Y45">
-        <v>1.37</v>
-      </c>
-      <c r="Z45">
-        <v>2.83</v>
-      </c>
-      <c r="AA45">
-        <v>2.1</v>
-      </c>
-      <c r="AB45">
-        <v>1.65</v>
-      </c>
-      <c r="AC45">
-        <v>3.7</v>
-      </c>
-      <c r="AD45">
-        <v>1.2</v>
-      </c>
-      <c r="AE45">
-        <v>1.04</v>
-      </c>
       <c r="AF45">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AG45">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK45">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,81 +7807,81 @@
         </is>
       </c>
       <c r="N46">
+        <v>3.6</v>
+      </c>
+      <c r="O46">
+        <v>3.2</v>
+      </c>
+      <c r="P46">
+        <v>1.98</v>
+      </c>
+      <c r="Q46">
+        <v>4</v>
+      </c>
+      <c r="R46">
+        <v>2.1</v>
+      </c>
+      <c r="S46">
         <v>1.4</v>
       </c>
-      <c r="O46">
-        <v>5.01</v>
-      </c>
-      <c r="P46">
-        <v>7.9</v>
-      </c>
-      <c r="Q46">
-        <v>1.75</v>
-      </c>
-      <c r="R46">
-        <v>2.5</v>
-      </c>
-      <c r="S46">
+      <c r="T46">
+        <v>2.75</v>
+      </c>
+      <c r="U46">
+        <v>2.83</v>
+      </c>
+      <c r="V46">
+        <v>1.36</v>
+      </c>
+      <c r="W46">
+        <v>1.07</v>
+      </c>
+      <c r="X46">
+        <v>1.02</v>
+      </c>
+      <c r="Y46">
+        <v>1.37</v>
+      </c>
+      <c r="Z46">
+        <v>2.83</v>
+      </c>
+      <c r="AA46">
+        <v>2.1</v>
+      </c>
+      <c r="AB46">
+        <v>1.65</v>
+      </c>
+      <c r="AC46">
+        <v>3.7</v>
+      </c>
+      <c r="AD46">
+        <v>1.2</v>
+      </c>
+      <c r="AE46">
+        <v>1.04</v>
+      </c>
+      <c r="AF46">
+        <v>1.89</v>
+      </c>
+      <c r="AG46">
+        <v>1.8</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>1.3</v>
+      </c>
+      <c r="AK46">
         <v>1.25</v>
       </c>
-      <c r="T46">
-        <v>3.55</v>
-      </c>
-      <c r="U46">
-        <v>2.25</v>
-      </c>
-      <c r="V46">
-        <v>1.56</v>
-      </c>
-      <c r="W46">
-        <v>1.12</v>
-      </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
-      <c r="Y46">
-        <v>1.19</v>
-      </c>
-      <c r="Z46">
-        <v>4.7</v>
-      </c>
-      <c r="AA46">
-        <v>1.63</v>
-      </c>
-      <c r="AB46">
-        <v>2.33</v>
-      </c>
-      <c r="AC46">
-        <v>2.41</v>
-      </c>
-      <c r="AD46">
-        <v>1.45</v>
-      </c>
-      <c r="AE46">
-        <v>1.15</v>
-      </c>
-      <c r="AF46">
-        <v>1.84</v>
-      </c>
-      <c r="AG46">
-        <v>1.86</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.12</v>
-      </c>
-      <c r="AK46">
-        <v>3.19</v>
-      </c>
       <c r="AL46">
         <v>0</v>
       </c>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-10-26 20:00:00</t>
+          <t>2026-10-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>5.01</v>
       </c>
       <c r="P47">
-        <v>4</v>
+        <v>7.9</v>
       </c>
       <c r="Q47">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="R47">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AA47">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB47">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="AC47">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AD47">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE47">
         <v>1.15</v>
       </c>
       <c r="AF47">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AG47">
-        <v>2.13</v>
+        <v>1.86</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK47">
-        <v>2.1</v>
+        <v>3.19</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2612,7 +2612,7 @@
         <v>4</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V14">
         <v>1.75</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
         <v>3</v>
@@ -2763,7 +2763,7 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>3.84</v>
+        <v>3.28</v>
       </c>
       <c r="R15">
         <v>2.3</v>
@@ -2796,7 +2796,7 @@
         <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AC15">
         <v>2.28</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="O19">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="P19">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q19">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="R19">
         <v>1.83</v>
@@ -3433,16 +3433,16 @@
         <v>1.23</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z19">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AA19">
         <v>2.49</v>
@@ -3451,13 +3451,13 @@
         <v>1.55</v>
       </c>
       <c r="AC19">
-        <v>4.6</v>
+        <v>4.74</v>
       </c>
       <c r="AD19">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE19">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF19">
         <v>1.99</v>
@@ -3479,7 +3479,7 @@
         <v>1.39</v>
       </c>
       <c r="AK19">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O21">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="P21">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="Q21">
         <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S21">
         <v>1.32</v>
@@ -3759,7 +3759,7 @@
         <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3898,10 +3898,10 @@
         <v>3.75</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q22">
         <v>4.32</v>
@@ -3910,10 +3910,10 @@
         <v>2.33</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="U22">
         <v>2.38</v>
@@ -3934,7 +3934,7 @@
         <v>4.17</v>
       </c>
       <c r="AA22">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB22">
         <v>2.21</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.86</v>
       </c>
       <c r="AK22">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK23">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="Q24">
         <v>2.88</v>
@@ -4236,10 +4236,10 @@
         <v>2.38</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T24">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
         <v>2.14</v>
@@ -4257,7 +4257,7 @@
         <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AA24">
         <v>1.47</v>
@@ -4393,10 +4393,10 @@
         <v>2.56</v>
       </c>
       <c r="Q25">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="R25">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
         <v>1.33</v>
@@ -4405,43 +4405,43 @@
         <v>2.82</v>
       </c>
       <c r="U25">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC25">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF25">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,55 +4547,55 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="O26">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="P26">
+        <v>2.7</v>
+      </c>
+      <c r="Q26">
         <v>3.07</v>
       </c>
-      <c r="Q26">
-        <v>3.18</v>
-      </c>
       <c r="R26">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S26">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U26">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
         <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA26">
+        <v>1.93</v>
+      </c>
+      <c r="AB26">
         <v>1.85</v>
       </c>
-      <c r="AB26">
-        <v>1.91</v>
-      </c>
       <c r="AC26">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE26">
         <v>1.05</v>
@@ -4620,7 +4620,7 @@
         <v>1.35</v>
       </c>
       <c r="AK26">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.56</v>
+        <v>5.59</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="P27">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Q27">
         <v>6.5</v>
@@ -4725,7 +4725,7 @@
         <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
         <v>3</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>2.23</v>
       </c>
       <c r="AK27">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,31 +5036,31 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="O29">
         <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q29">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T29">
         <v>3.22</v>
       </c>
       <c r="U29">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W29">
         <v>1.09</v>
@@ -5072,13 +5072,13 @@
         <v>1.19</v>
       </c>
       <c r="Z29">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="AA29">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB29">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AC29">
         <v>2.74</v>
@@ -5090,10 +5090,10 @@
         <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG29">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5205,19 +5205,19 @@
         <v>3.8</v>
       </c>
       <c r="P30">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
       </c>
       <c r="R30">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S30">
         <v>1.22</v>
       </c>
       <c r="T30">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U30">
         <v>2.1</v>
@@ -5226,19 +5226,19 @@
         <v>1.64</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y30">
         <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="AA30">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB30">
         <v>2.6</v>
@@ -5253,10 +5253,10 @@
         <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG30">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="O32">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="P32">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Q32">
-        <v>7.42</v>
+        <v>7.02</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="S32">
         <v>1.35</v>
@@ -5546,37 +5546,37 @@
         <v>3</v>
       </c>
       <c r="U32">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V32">
         <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="AA32">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AB32">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AC32">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
         <v>2.1</v>
@@ -5598,7 +5598,7 @@
         <v>2.9</v>
       </c>
       <c r="AK32">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="P33">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB33">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
         <v>2.5</v>
       </c>
       <c r="Q36">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S36">
         <v>1.33</v>
       </c>
       <c r="T36">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="U36">
         <v>2.5</v>
@@ -6204,16 +6204,16 @@
         <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA36">
         <v>1.82</v>
@@ -6222,19 +6222,19 @@
         <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD36">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,52 +6340,52 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P37">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
       </c>
       <c r="R37">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S37">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
         <v>2.7</v>
       </c>
       <c r="U37">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="V37">
         <v>1.35</v>
       </c>
       <c r="W37">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z37">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA37">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB37">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC37">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD37">
         <v>1.22</v>
@@ -6394,10 +6394,10 @@
         <v>1.04</v>
       </c>
       <c r="AF37">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK37">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="O38">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="P38">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q38">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R38">
         <v>2.22</v>
@@ -6521,7 +6521,7 @@
         <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
         <v>2.47</v>
@@ -6530,7 +6530,7 @@
         <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.03</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O39">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
         <v>4</v>
@@ -6678,31 +6678,31 @@
         <v>2.59</v>
       </c>
       <c r="R39">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S39">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T39">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U39">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="V39">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y39">
         <v>1.37</v>
       </c>
       <c r="Z39">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AA39">
         <v>2.18</v>
@@ -6711,16 +6711,16 @@
         <v>1.79</v>
       </c>
       <c r="AC39">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="AD39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG39">
         <v>1.8</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
         <v>1.8</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1133,55 +1133,55 @@
         <v>6.35</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
         <v>1.29</v>
@@ -1450,61 +1450,61 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q7">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="R7">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T7">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V7">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W7">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z7">
-        <v>6.09</v>
+        <v>6.55</v>
       </c>
       <c r="AA7">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AB7">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="AC7">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AD7">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AE7">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF7">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
         <v>2.15</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK7">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1655,7 +1655,7 @@
         <v>1.93</v>
       </c>
       <c r="AB8">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
         <v>3.34</v>
@@ -2455,7 +2455,7 @@
         <v>1.29</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
         <v>1.04</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
         <v>3</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AB16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>3.13</v>
       </c>
       <c r="P19">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4079,7 +4079,7 @@
         <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
         <v>1.44</v>
@@ -4260,7 +4260,7 @@
         <v>4.7</v>
       </c>
       <c r="AA24">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB24">
         <v>2.35</v>
@@ -4393,49 +4393,49 @@
         <v>2.56</v>
       </c>
       <c r="Q25">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U25">
         <v>2.62</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA25">
         <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC25">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE25">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF25">
         <v>1.67</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         <v>3.92</v>
       </c>
       <c r="P27">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Q27">
         <v>6.5</v>
@@ -4876,16 +4876,16 @@
         <v>1.31</v>
       </c>
       <c r="O28">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="P28">
-        <v>7.55</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>1.82</v>
       </c>
       <c r="R28">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="S28">
         <v>1.2</v>
@@ -4894,10 +4894,10 @@
         <v>3.8</v>
       </c>
       <c r="U28">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="V28">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W28">
         <v>1.11</v>
@@ -4912,7 +4912,7 @@
         <v>5.05</v>
       </c>
       <c r="AA28">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AB28">
         <v>2.38</v>
@@ -5039,13 +5039,13 @@
         <v>2.13</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="P29">
         <v>2.4</v>
       </c>
       <c r="Q29">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="R29">
         <v>2.2</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O30">
         <v>3.8</v>
@@ -5208,10 +5208,10 @@
         <v>2.58</v>
       </c>
       <c r="Q30">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S30">
         <v>1.22</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>1.9</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P31">
         <v>4.2</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB31">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>7.7</v>
       </c>
       <c r="O32">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="P32">
         <v>1.4</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
         <v>3.42</v>
@@ -5860,7 +5860,7 @@
         <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="R34">
         <v>2.08</v>
@@ -5872,7 +5872,7 @@
         <v>2.72</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
         <v>1.36</v>
@@ -5884,16 +5884,16 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA34">
         <v>2</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC34">
         <v>3.14</v>
@@ -5905,10 +5905,10 @@
         <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG34">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AK34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6189,13 +6189,13 @@
         <v>3.11</v>
       </c>
       <c r="R36">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="S36">
         <v>1.33</v>
       </c>
       <c r="T36">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="U36">
         <v>2.5</v>
@@ -6250,7 +6250,7 @@
         <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6355,7 +6355,7 @@
         <v>2</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T37">
         <v>2.7</v>
@@ -6530,7 +6530,7 @@
         <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
         <v>1.03</v>
@@ -6675,7 +6675,7 @@
         <v>4</v>
       </c>
       <c r="Q39">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="R39">
         <v>2.21</v>
@@ -6684,16 +6684,16 @@
         <v>1.44</v>
       </c>
       <c r="T39">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U39">
         <v>3.2</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="P40">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S40">
         <v>1.4</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P41">
-        <v>4.61</v>
+        <v>3.65</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -7046,7 +7046,7 @@
         <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG41">
         <v>1.75</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q42">
         <v>2.05</v>
@@ -7182,37 +7182,37 @@
         <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="AA42">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB42">
         <v>2.16</v>
       </c>
       <c r="AC42">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AD42">
         <v>1.47</v>
       </c>
       <c r="AE42">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF42">
         <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK42">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="O45">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P45">
-        <v>3.43</v>
+        <v>3.1</v>
       </c>
       <c r="Q45">
         <v>2.7</v>
@@ -7659,16 +7659,16 @@
         <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="U45">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V45">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W45">
         <v>1.06</v>
@@ -7677,22 +7677,22 @@
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z45">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="AA45">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB45">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AC45">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="AD45">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE45">
         <v>1.07</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK45">
         <v>1.69</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O46">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P46">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q46">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="R46">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S46">
         <v>1.4</v>
@@ -7828,7 +7828,7 @@
         <v>2.75</v>
       </c>
       <c r="U46">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="V46">
         <v>1.36</v>
@@ -7846,7 +7846,7 @@
         <v>2.83</v>
       </c>
       <c r="AA46">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB46">
         <v>1.65</v>
@@ -7861,10 +7861,10 @@
         <v>1.04</v>
       </c>
       <c r="AF46">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG46">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK46">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O47">
-        <v>5.01</v>
+        <v>5.25</v>
       </c>
       <c r="P47">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="Q47">
         <v>1.75</v>
@@ -7994,19 +7994,19 @@
         <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W47">
         <v>1.12</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA47">
         <v>1.63</v>
@@ -8015,13 +8015,13 @@
         <v>2.33</v>
       </c>
       <c r="AC47">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AD47">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AE47">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF47">
         <v>1.84</v>
@@ -8043,7 +8043,7 @@
         <v>1.12</v>
       </c>
       <c r="AK47">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>5.12</v>
+        <v>5.75</v>
       </c>
       <c r="Q48">
         <v>2.05</v>
@@ -8163,7 +8163,7 @@
         <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
         <v>1.25</v>
@@ -8172,10 +8172,10 @@
         <v>3.28</v>
       </c>
       <c r="AA48">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB48">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC48">
         <v>3.3</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
         <v>2.38</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z5">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC5">
         <v>2.49</v>
       </c>
       <c r="AD5">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE5">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK5">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q6">
+        <v>1.59</v>
+      </c>
+      <c r="R6">
+        <v>2.75</v>
+      </c>
+      <c r="S6">
+        <v>1.16</v>
+      </c>
+      <c r="T6">
+        <v>4.05</v>
+      </c>
+      <c r="U6">
         <v>1.91</v>
       </c>
-      <c r="R6">
-        <v>2.4</v>
-      </c>
-      <c r="S6">
-        <v>1.29</v>
-      </c>
-      <c r="T6">
-        <v>3.3</v>
-      </c>
-      <c r="U6">
-        <v>2.38</v>
-      </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z6">
-        <v>4.15</v>
+        <v>6.55</v>
       </c>
       <c r="AA6">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AB6">
-        <v>2.13</v>
+        <v>2.92</v>
       </c>
       <c r="AC6">
-        <v>2.49</v>
+        <v>1.84</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK6">
-        <v>2.43</v>
+        <v>3.6</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="O7">
-        <v>5.6</v>
+        <v>4.45</v>
       </c>
       <c r="P7">
-        <v>7.4</v>
+        <v>6.35</v>
       </c>
       <c r="Q7">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="R7">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="S7">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="T7">
-        <v>4.05</v>
+        <v>3.18</v>
       </c>
       <c r="U7">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>6.55</v>
+        <v>4.25</v>
       </c>
       <c r="AA7">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>2.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>1.84</v>
+        <v>2.49</v>
       </c>
       <c r="AD7">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AE7">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AF7">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>1.15</v>
       </c>
       <c r="Q17">
-        <v>8.75</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R17">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="S17">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T17">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U17">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V17">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z17">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="AA17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AB17">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC17">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AD17">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE17">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF17">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG17">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3569,61 +3569,61 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="O20">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="Q20">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="R20">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V20">
         <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="AA20">
         <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
         <v>2.1</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,16 +3741,16 @@
         <v>2.21</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="R21">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
         <v>1.32</v>
       </c>
       <c r="T21">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
         <v>2.55</v>
@@ -3759,10 +3759,10 @@
         <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
         <v>1.2</v>
@@ -3786,10 +3786,10 @@
         <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>2.7</v>
       </c>
       <c r="Q26">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="R26">
         <v>2</v>
@@ -4620,7 +4620,7 @@
         <v>1.35</v>
       </c>
       <c r="AK26">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>5.59</v>
+        <v>5.25</v>
       </c>
       <c r="O27">
         <v>3.92</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2630,7 +2630,7 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
         <v>2.81</v>
@@ -2766,7 +2766,7 @@
         <v>3.28</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
         <v>1.25</v>
@@ -3415,7 +3415,7 @@
         <v>2.55</v>
       </c>
       <c r="Q19">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="R19">
         <v>1.83</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
         <v>1.73</v>
@@ -4079,7 +4079,7 @@
         <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V23">
         <v>1.44</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O29">
         <v>3.41</v>
       </c>
       <c r="P29">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q29">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
         <v>1.31</v>
@@ -5208,10 +5208,10 @@
         <v>2.58</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="R30">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S30">
         <v>1.22</v>
@@ -5241,7 +5241,7 @@
         <v>1.49</v>
       </c>
       <c r="AB30">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AC30">
         <v>2.19</v>
@@ -5528,7 +5528,7 @@
         <v>7.7</v>
       </c>
       <c r="O32">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="P32">
         <v>1.4</v>
@@ -5598,7 +5598,7 @@
         <v>2.9</v>
       </c>
       <c r="AK32">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
         <v>3.35</v>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="R36">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="U36">
         <v>2.5</v>
@@ -6204,10 +6204,10 @@
         <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
         <v>1.22</v>
@@ -6219,22 +6219,22 @@
         <v>1.82</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC36">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD36">
         <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6352,7 +6352,7 @@
         <v>3.4</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S37">
         <v>1.45</v>
@@ -6361,7 +6361,7 @@
         <v>2.7</v>
       </c>
       <c r="U37">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="V37">
         <v>1.35</v>
@@ -6382,7 +6382,7 @@
         <v>2.06</v>
       </c>
       <c r="AB37">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC37">
         <v>4</v>
@@ -6506,7 +6506,7 @@
         <v>3.3</v>
       </c>
       <c r="O38">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="P38">
         <v>2.05</v>
@@ -6515,7 +6515,7 @@
         <v>3.75</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S38">
         <v>1.29</v>
@@ -6536,10 +6536,10 @@
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>3.92</v>
+        <v>4.07</v>
       </c>
       <c r="AA38">
         <v>1.73</v>
@@ -6557,10 +6557,10 @@
         <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="O40">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P40">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -6868,10 +6868,10 @@
         <v>2.92</v>
       </c>
       <c r="AA40">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AB40">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC40">
         <v>3.89</v>
@@ -7197,7 +7197,7 @@
         <v>1.68</v>
       </c>
       <c r="AB42">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
         <v>2.64</v>
@@ -7647,7 +7647,7 @@
         <v>2.17</v>
       </c>
       <c r="O45">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P45">
         <v>3.1</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="O47">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="P47">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q47">
         <v>1.75</v>
@@ -7988,7 +7988,7 @@
         <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="U47">
         <v>2.25</v>
@@ -8006,28 +8006,28 @@
         <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA47">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB47">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AC47">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD47">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE47">
         <v>1.22</v>
       </c>
       <c r="AF47">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AG47">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK47">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1133,10 +1133,10 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="R5">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S5">
         <v>1.29</v>
@@ -1151,7 +1151,7 @@
         <v>1.53</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.02</v>
@@ -1160,19 +1160,19 @@
         <v>1.16</v>
       </c>
       <c r="Z5">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA5">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB5">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC5">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE5">
         <v>1.13</v>
@@ -1181,7 +1181,7 @@
         <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O6">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="P6">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="Q6">
         <v>1.59</v>
       </c>
       <c r="R6">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="S6">
         <v>1.16</v>
@@ -1314,7 +1314,7 @@
         <v>1.8</v>
       </c>
       <c r="W6">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1326,10 +1326,10 @@
         <v>6.55</v>
       </c>
       <c r="AA6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB6">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AC6">
         <v>1.84</v>
@@ -1341,7 +1341,7 @@
         <v>1.32</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
         <v>2.15</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="O7">
-        <v>4.45</v>
+        <v>4.02</v>
       </c>
       <c r="P7">
-        <v>6.35</v>
+        <v>5.4</v>
       </c>
       <c r="Q7">
         <v>1.95</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>2.5</v>
       </c>
       <c r="S10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
         <v>3.2</v>
@@ -1975,7 +1975,7 @@
         <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="AA10">
         <v>1.71</v>
@@ -1993,7 +1993,7 @@
         <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
         <v>1.61</v>
@@ -2434,7 +2434,7 @@
         <v>3.1</v>
       </c>
       <c r="P13">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -2446,7 +2446,7 @@
         <v>1.44</v>
       </c>
       <c r="T13">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="U13">
         <v>3.3</v>
@@ -2476,7 +2476,7 @@
         <v>4.35</v>
       </c>
       <c r="AD13">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="O14">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P14">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="Q14">
-        <v>1.77</v>
+        <v>3.28</v>
       </c>
       <c r="R14">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="V14">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AA14">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>2.81</v>
+        <v>2.35</v>
       </c>
       <c r="AC14">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AD14">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="O15">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P15">
-        <v>1.98</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>3.28</v>
+        <v>1.77</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="U15">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="V15">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z15">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="AC15">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AD15">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE15">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AF15">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,37 +2923,37 @@
         <v>2.7</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA16">
         <v>3.1</v>
@@ -2962,19 +2962,19 @@
         <v>1.36</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3264,10 +3264,10 @@
         <v>3.14</v>
       </c>
       <c r="U18">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="V18">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
         <v>1.12</v>
@@ -3288,19 +3288,19 @@
         <v>2.08</v>
       </c>
       <c r="AC18">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AD18">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE18">
         <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>1.23</v>
       </c>
       <c r="W19">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X19">
         <v>1.06</v>
@@ -3445,10 +3445,10 @@
         <v>2.65</v>
       </c>
       <c r="AA19">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AB19">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AC19">
         <v>4.74</v>
@@ -3771,10 +3771,10 @@
         <v>3.72</v>
       </c>
       <c r="AA21">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AC21">
         <v>2.78</v>
@@ -3783,7 +3783,7 @@
         <v>1.41</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
         <v>1.62</v>
@@ -3910,10 +3910,10 @@
         <v>2.33</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
         <v>2.38</v>
@@ -3940,7 +3940,7 @@
         <v>2.21</v>
       </c>
       <c r="AC22">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="AD22">
         <v>1.44</v>
@@ -3952,7 +3952,7 @@
         <v>1.57</v>
       </c>
       <c r="AG22">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
         <v>1.44</v>
@@ -4088,28 +4088,28 @@
         <v>1.1</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
         <v>1.21</v>
       </c>
       <c r="Z23">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="AA23">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AC23">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AD23">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
         <v>1.71</v>
@@ -4230,25 +4230,25 @@
         <v>2.55</v>
       </c>
       <c r="Q24">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R24">
         <v>2.38</v>
       </c>
       <c r="S24">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
         <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="V24">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
         <v>1.02</v>
@@ -4257,22 +4257,22 @@
         <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>4.7</v>
+        <v>5.28</v>
       </c>
       <c r="AA24">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB24">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AC24">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AD24">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AE24">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF24">
         <v>1.44</v>
@@ -4396,7 +4396,7 @@
         <v>4</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
         <v>1.3</v>
@@ -4405,7 +4405,7 @@
         <v>2.88</v>
       </c>
       <c r="U25">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V25">
         <v>1.42</v>
@@ -4426,7 +4426,7 @@
         <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AC25">
         <v>2.92</v>
@@ -4457,7 +4457,7 @@
         <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="O26">
         <v>3.23</v>
@@ -4719,7 +4719,7 @@
         <v>1.5</v>
       </c>
       <c r="Q27">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="R27">
         <v>2.25</v>
@@ -4731,10 +4731,10 @@
         <v>3</v>
       </c>
       <c r="U27">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
         <v>1.06</v>
@@ -4743,13 +4743,13 @@
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA27">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB27">
         <v>1.95</v>
@@ -4761,13 +4761,13 @@
         <v>1.31</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>2.23</v>
       </c>
       <c r="AK27">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         <v>2.15</v>
       </c>
       <c r="O29">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
         <v>2.38</v>
       </c>
       <c r="Q29">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S29">
         <v>1.31</v>
@@ -5057,7 +5057,7 @@
         <v>3.22</v>
       </c>
       <c r="U29">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
         <v>1.49</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>3.8</v>
       </c>
       <c r="P30">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="Q30">
         <v>2.71</v>
@@ -5241,16 +5241,16 @@
         <v>1.49</v>
       </c>
       <c r="AB30">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AC30">
         <v>2.19</v>
       </c>
       <c r="AD30">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF30">
         <v>1.4</v>
@@ -5528,13 +5528,13 @@
         <v>7.7</v>
       </c>
       <c r="O32">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="P32">
         <v>1.4</v>
       </c>
       <c r="Q32">
-        <v>7.02</v>
+        <v>5.8</v>
       </c>
       <c r="R32">
         <v>2.27</v>
@@ -5570,7 +5570,7 @@
         <v>2.01</v>
       </c>
       <c r="AC32">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD32">
         <v>1.37</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.13</v>
       </c>
       <c r="P33">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q36">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="R36">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="S36">
         <v>1.36</v>
@@ -6219,7 +6219,7 @@
         <v>1.82</v>
       </c>
       <c r="AB36">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC36">
         <v>3.2</v>
@@ -6228,13 +6228,13 @@
         <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
         <v>1.55</v>
@@ -6358,7 +6358,7 @@
         <v>1.45</v>
       </c>
       <c r="T37">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U37">
         <v>3.2</v>
@@ -6367,7 +6367,7 @@
         <v>1.35</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6385,7 +6385,7 @@
         <v>1.68</v>
       </c>
       <c r="AC37">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD37">
         <v>1.22</v>
@@ -6515,7 +6515,7 @@
         <v>3.75</v>
       </c>
       <c r="R38">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
         <v>1.29</v>
@@ -6536,10 +6536,10 @@
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.07</v>
+        <v>3.92</v>
       </c>
       <c r="AA38">
         <v>1.73</v>
@@ -6557,7 +6557,7 @@
         <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
         <v>2.2</v>
@@ -6669,13 +6669,13 @@
         <v>1.92</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P39">
         <v>4</v>
       </c>
       <c r="Q39">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R39">
         <v>2.21</v>
@@ -6696,7 +6696,7 @@
         <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
         <v>1.37</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P40">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -6850,7 +6850,7 @@
         <v>2.45</v>
       </c>
       <c r="U40">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="V40">
         <v>1.33</v>
@@ -6871,22 +6871,22 @@
         <v>2.3</v>
       </c>
       <c r="AB40">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC40">
         <v>3.89</v>
       </c>
       <c r="AD40">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE40">
         <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>1.43</v>
       </c>
       <c r="T41">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U41">
         <v>2.8</v>
@@ -7028,10 +7028,10 @@
         <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA41">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB41">
         <v>1.71</v>
@@ -7040,7 +7040,7 @@
         <v>3.5</v>
       </c>
       <c r="AD41">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE41">
         <v>1.04</v>
@@ -7158,7 +7158,7 @@
         <v>1.61</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
         <v>4.33</v>
@@ -7182,7 +7182,7 @@
         <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
         <v>1.02</v>
@@ -7194,7 +7194,7 @@
         <v>4.35</v>
       </c>
       <c r="AA42">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
         <v>2.15</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="O45">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="P45">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q45">
         <v>2.7</v>
@@ -7659,10 +7659,10 @@
         <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T45">
-        <v>3.07</v>
+        <v>2.72</v>
       </c>
       <c r="U45">
         <v>2.82</v>
@@ -7671,7 +7671,7 @@
         <v>1.42</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
         <v>1</v>
@@ -7680,7 +7680,7 @@
         <v>1.29</v>
       </c>
       <c r="Z45">
-        <v>3.38</v>
+        <v>3.66</v>
       </c>
       <c r="AA45">
         <v>1.95</v>
@@ -7695,7 +7695,7 @@
         <v>1.32</v>
       </c>
       <c r="AE45">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
         <v>1.71</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1197,7 +1197,7 @@
         <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="O7">
-        <v>4.02</v>
+        <v>3.89</v>
       </c>
       <c r="P7">
-        <v>5.4</v>
+        <v>5.22</v>
       </c>
       <c r="Q7">
         <v>1.95</v>
@@ -1945,7 +1945,7 @@
         <v>5.1</v>
       </c>
       <c r="P10">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -2434,7 +2434,7 @@
         <v>3.1</v>
       </c>
       <c r="P13">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -2446,7 +2446,7 @@
         <v>1.44</v>
       </c>
       <c r="T13">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="U13">
         <v>3.3</v>
@@ -2476,7 +2476,7 @@
         <v>4.35</v>
       </c>
       <c r="AD13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
@@ -2612,10 +2612,10 @@
         <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W14">
         <v>1.11</v>
@@ -2763,7 +2763,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R15">
         <v>2.92</v>
@@ -2772,7 +2772,7 @@
         <v>1.2</v>
       </c>
       <c r="T15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U15">
         <v>2.04</v>
@@ -2796,7 +2796,7 @@
         <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AC15">
         <v>1.92</v>
@@ -2926,16 +2926,16 @@
         <v>2.87</v>
       </c>
       <c r="Q16">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="R16">
         <v>1.85</v>
       </c>
       <c r="S16">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="T16">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U16">
         <v>3.8</v>
@@ -2947,25 +2947,25 @@
         <v>1.04</v>
       </c>
       <c r="X16">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y16">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Z16">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AA16">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="AB16">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC16">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE16">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="O17">
-        <v>6.3</v>
+        <v>5.75</v>
       </c>
       <c r="P17">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Q17">
-        <v>8.949999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="R17">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="S17">
         <v>1.16</v>
@@ -3116,7 +3116,7 @@
         <v>1.09</v>
       </c>
       <c r="Z17">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="AA17">
         <v>1.38</v>
@@ -3131,13 +3131,13 @@
         <v>1.69</v>
       </c>
       <c r="AE17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF17">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG17">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
         <v>1.11</v>
@@ -3412,7 +3412,7 @@
         <v>3.13</v>
       </c>
       <c r="P19">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="Q19">
         <v>3.37</v>
@@ -3578,7 +3578,7 @@
         <v>3.95</v>
       </c>
       <c r="Q20">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R20">
         <v>2.3</v>
@@ -3593,7 +3593,7 @@
         <v>2.45</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
         <v>1.11</v>
@@ -3614,7 +3614,7 @@
         <v>2</v>
       </c>
       <c r="AC20">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD20">
         <v>1.42</v>
@@ -3642,7 +3642,7 @@
         <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>3.72</v>
       </c>
       <c r="AA21">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB21">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AC21">
         <v>2.78</v>
@@ -3904,10 +3904,10 @@
         <v>1.73</v>
       </c>
       <c r="Q22">
-        <v>4.32</v>
+        <v>4.48</v>
       </c>
       <c r="R22">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
         <v>1.3</v>
@@ -4079,7 +4079,7 @@
         <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V23">
         <v>1.44</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="O26">
         <v>3.23</v>
@@ -4580,10 +4580,10 @@
         <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
         <v>1.93</v>
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="O28">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="P28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="R28">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="S28">
         <v>1.2</v>
       </c>
       <c r="T28">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U28">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V28">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
         <v>1.02</v>
@@ -4909,13 +4909,13 @@
         <v>1.1</v>
       </c>
       <c r="Z28">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA28">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB28">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AC28">
         <v>2.26</v>
@@ -4946,7 +4946,7 @@
         <v>1.12</v>
       </c>
       <c r="AK28">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5057,7 +5057,7 @@
         <v>3.22</v>
       </c>
       <c r="U29">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="V29">
         <v>1.49</v>
@@ -5109,7 +5109,7 @@
         <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>1.88</v>
       </c>
       <c r="O33">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5860,10 +5860,10 @@
         <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="R34">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
         <v>1.36</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC35">
         <v>2.88</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P36">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="Q36">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="R36">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S36">
+        <v>1.45</v>
+      </c>
+      <c r="T36">
+        <v>2.71</v>
+      </c>
+      <c r="U36">
+        <v>3.2</v>
+      </c>
+      <c r="V36">
+        <v>1.35</v>
+      </c>
+      <c r="W36">
+        <v>1.06</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.33</v>
+      </c>
+      <c r="Z36">
+        <v>3</v>
+      </c>
+      <c r="AA36">
+        <v>2.06</v>
+      </c>
+      <c r="AB36">
+        <v>1.68</v>
+      </c>
+      <c r="AC36">
+        <v>3.9</v>
+      </c>
+      <c r="AD36">
+        <v>1.22</v>
+      </c>
+      <c r="AE36">
+        <v>1.04</v>
+      </c>
+      <c r="AF36">
+        <v>1.83</v>
+      </c>
+      <c r="AG36">
+        <v>1.85</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.36</v>
       </c>
-      <c r="T36">
-        <v>3</v>
-      </c>
-      <c r="U36">
-        <v>2.5</v>
-      </c>
-      <c r="V36">
-        <v>1.44</v>
-      </c>
-      <c r="W36">
-        <v>1.05</v>
-      </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>1.22</v>
-      </c>
-      <c r="Z36">
-        <v>3.8</v>
-      </c>
-      <c r="AA36">
-        <v>1.82</v>
-      </c>
-      <c r="AB36">
-        <v>1.9</v>
-      </c>
-      <c r="AC36">
-        <v>3.2</v>
-      </c>
-      <c r="AD36">
-        <v>1.33</v>
-      </c>
-      <c r="AE36">
-        <v>1.08</v>
-      </c>
-      <c r="AF36">
-        <v>1.73</v>
-      </c>
-      <c r="AG36">
-        <v>2.1</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
+      <c r="AK36">
         <v>1.3</v>
-      </c>
-      <c r="AK36">
-        <v>1.55</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O37">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="Q37">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="R37">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S37">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="U37">
+        <v>2.5</v>
+      </c>
+      <c r="V37">
+        <v>1.44</v>
+      </c>
+      <c r="W37">
+        <v>1.05</v>
+      </c>
+      <c r="X37">
+        <v>1.04</v>
+      </c>
+      <c r="Y37">
+        <v>1.22</v>
+      </c>
+      <c r="Z37">
+        <v>3.8</v>
+      </c>
+      <c r="AA37">
+        <v>1.82</v>
+      </c>
+      <c r="AB37">
+        <v>1.9</v>
+      </c>
+      <c r="AC37">
         <v>3.2</v>
       </c>
-      <c r="V37">
-        <v>1.35</v>
-      </c>
-      <c r="W37">
-        <v>1.06</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
+      <c r="AD37">
         <v>1.33</v>
       </c>
-      <c r="Z37">
-        <v>3</v>
-      </c>
-      <c r="AA37">
-        <v>2.06</v>
-      </c>
-      <c r="AB37">
-        <v>1.68</v>
-      </c>
-      <c r="AC37">
-        <v>3.9</v>
-      </c>
-      <c r="AD37">
-        <v>1.22</v>
-      </c>
       <c r="AE37">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>3.75</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S38">
         <v>1.29</v>
@@ -6536,10 +6536,10 @@
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>3.92</v>
+        <v>4.07</v>
       </c>
       <c r="AA38">
         <v>1.73</v>
@@ -6708,7 +6708,7 @@
         <v>2.18</v>
       </c>
       <c r="AB39">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AC39">
         <v>3.45</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>2.6</v>
       </c>
       <c r="O40">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P40">
         <v>2.6</v>
@@ -7031,7 +7031,7 @@
         <v>3.2</v>
       </c>
       <c r="AA41">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB41">
         <v>1.71</v>
@@ -7650,7 +7650,7 @@
         <v>3.37</v>
       </c>
       <c r="P45">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q45">
         <v>2.7</v>
@@ -7813,7 +7813,7 @@
         <v>3.25</v>
       </c>
       <c r="P46">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q46">
         <v>3.89</v>
@@ -7828,10 +7828,10 @@
         <v>2.75</v>
       </c>
       <c r="U46">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W46">
         <v>1.07</v>
@@ -7843,7 +7843,7 @@
         <v>1.37</v>
       </c>
       <c r="Z46">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="AA46">
         <v>2.11</v>
@@ -7852,7 +7852,7 @@
         <v>1.65</v>
       </c>
       <c r="AC46">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="AD46">
         <v>1.2</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="O47">
         <v>5.1</v>
@@ -7994,7 +7994,7 @@
         <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W47">
         <v>1.12</v>
@@ -8142,13 +8142,13 @@
         <v>5.75</v>
       </c>
       <c r="Q48">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T48">
         <v>3</v>
@@ -8163,7 +8163,7 @@
         <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.25</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK48">
         <v>2.44</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU50"/>
+  <dimension ref="A1:AU51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Q5">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
-        <v>2.31</v>
+        <v>3.08</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z5">
-        <v>4.1</v>
+        <v>6.55</v>
       </c>
       <c r="AA5">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AB5">
-        <v>2.1</v>
+        <v>2.97</v>
       </c>
       <c r="AC5">
-        <v>2.52</v>
+        <v>1.84</v>
       </c>
       <c r="AD5">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="O6">
-        <v>5.1</v>
+        <v>3.89</v>
       </c>
       <c r="P6">
-        <v>6.8</v>
+        <v>5.22</v>
       </c>
       <c r="Q6">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="S6">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="T6">
-        <v>4.05</v>
+        <v>3.18</v>
       </c>
       <c r="U6">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>6.55</v>
+        <v>4.25</v>
       </c>
       <c r="AA6">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
-        <v>1.84</v>
+        <v>2.49</v>
       </c>
       <c r="AD6">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>3.58</v>
+        <v>2.6</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R7">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="S7">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
         <v>2.38</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z7">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA7">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB7">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD7">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,10 +1622,10 @@
         <v>2.99</v>
       </c>
       <c r="Q8">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="R8">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="S8">
         <v>1.34</v>
@@ -1637,40 +1637,40 @@
         <v>2.69</v>
       </c>
       <c r="V8">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W8">
         <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA8">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC8">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
         <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG8">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Gamo Chencha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:30:00</t>
+          <t>2026-10-26 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-26 11:00:00</t>
+          <t>2026-10-26 10:30:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.94</v>
+        <v>1.26</v>
       </c>
       <c r="O11">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="P11">
-        <v>3.56</v>
+        <v>7.8</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-26 12:00:00</t>
+          <t>2026-10-26 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2223,22 +2223,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Halaba Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Halaba Ketema</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="O14">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
+        <v>3.3</v>
+      </c>
+      <c r="Q14">
+        <v>2.8</v>
+      </c>
+      <c r="R14">
         <v>1.95</v>
       </c>
-      <c r="Q14">
-        <v>3.28</v>
-      </c>
-      <c r="R14">
+      <c r="S14">
+        <v>1.44</v>
+      </c>
+      <c r="T14">
+        <v>2.45</v>
+      </c>
+      <c r="U14">
+        <v>3.3</v>
+      </c>
+      <c r="V14">
+        <v>1.29</v>
+      </c>
+      <c r="W14">
+        <v>1.05</v>
+      </c>
+      <c r="X14">
+        <v>1.04</v>
+      </c>
+      <c r="Y14">
+        <v>1.4</v>
+      </c>
+      <c r="Z14">
+        <v>2.56</v>
+      </c>
+      <c r="AA14">
         <v>2.5</v>
       </c>
-      <c r="S14">
-        <v>1.25</v>
-      </c>
-      <c r="T14">
-        <v>3.6</v>
-      </c>
-      <c r="U14">
-        <v>2.32</v>
-      </c>
-      <c r="V14">
-        <v>1.58</v>
-      </c>
-      <c r="W14">
-        <v>1.11</v>
-      </c>
-      <c r="X14">
-        <v>1</v>
-      </c>
-      <c r="Y14">
-        <v>1.16</v>
-      </c>
-      <c r="Z14">
-        <v>4.8</v>
-      </c>
-      <c r="AA14">
-        <v>1.57</v>
-      </c>
       <c r="AB14">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC14">
-        <v>2.28</v>
+        <v>4.35</v>
       </c>
       <c r="AD14">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="AG14">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AK14">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-26 13:00:00</t>
+          <t>2026-10-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="Q15">
-        <v>1.78</v>
+        <v>3.85</v>
       </c>
       <c r="R15">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="V15">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="W15">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AA15">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AB15">
-        <v>2.81</v>
+        <v>2.35</v>
       </c>
       <c r="AC15">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AD15">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AF15">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,65 +2917,65 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="O16">
+        <v>5.25</v>
+      </c>
+      <c r="P16">
+        <v>7</v>
+      </c>
+      <c r="Q16">
+        <v>1.78</v>
+      </c>
+      <c r="R16">
+        <v>2.92</v>
+      </c>
+      <c r="S16">
+        <v>1.19</v>
+      </c>
+      <c r="T16">
+        <v>4</v>
+      </c>
+      <c r="U16">
+        <v>2.04</v>
+      </c>
+      <c r="V16">
+        <v>1.75</v>
+      </c>
+      <c r="W16">
+        <v>1.2</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>1.07</v>
+      </c>
+      <c r="Z16">
+        <v>7</v>
+      </c>
+      <c r="AA16">
+        <v>1.36</v>
+      </c>
+      <c r="AB16">
         <v>2.7</v>
       </c>
-      <c r="P16">
-        <v>2.87</v>
-      </c>
-      <c r="Q16">
-        <v>3.69</v>
-      </c>
-      <c r="R16">
-        <v>1.85</v>
-      </c>
-      <c r="S16">
-        <v>1.64</v>
-      </c>
-      <c r="T16">
-        <v>2.2</v>
-      </c>
-      <c r="U16">
-        <v>3.8</v>
-      </c>
-      <c r="V16">
-        <v>1.22</v>
-      </c>
-      <c r="W16">
-        <v>1.04</v>
-      </c>
-      <c r="X16">
-        <v>1.13</v>
-      </c>
-      <c r="Y16">
-        <v>1.62</v>
-      </c>
-      <c r="Z16">
+      <c r="AC16">
+        <v>1.92</v>
+      </c>
+      <c r="AD16">
+        <v>1.76</v>
+      </c>
+      <c r="AE16">
+        <v>1.3</v>
+      </c>
+      <c r="AF16">
+        <v>1.61</v>
+      </c>
+      <c r="AG16">
         <v>2.25</v>
       </c>
-      <c r="AA16">
-        <v>2.96</v>
-      </c>
-      <c r="AB16">
-        <v>1.37</v>
-      </c>
-      <c r="AC16">
-        <v>6.1</v>
-      </c>
-      <c r="AD16">
-        <v>1.11</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>2.25</v>
-      </c>
-      <c r="AG16">
-        <v>1.57</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="O17">
-        <v>5.75</v>
+        <v>2.7</v>
       </c>
       <c r="P17">
-        <v>1.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q17">
-        <v>8.75</v>
+        <v>3.69</v>
       </c>
       <c r="R17">
-        <v>2.85</v>
+        <v>1.85</v>
       </c>
       <c r="S17">
-        <v>1.16</v>
+        <v>1.64</v>
       </c>
       <c r="T17">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>1.98</v>
+        <v>3.8</v>
       </c>
       <c r="V17">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
       <c r="W17">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Y17">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="Z17">
-        <v>5.4</v>
+        <v>2.25</v>
       </c>
       <c r="AA17">
-        <v>1.38</v>
+        <v>2.96</v>
       </c>
       <c r="AB17">
-        <v>2.62</v>
+        <v>1.37</v>
       </c>
       <c r="AC17">
-        <v>2.01</v>
+        <v>6.1</v>
       </c>
       <c r="AD17">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="AE17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="AK17">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>7.17</v>
+        <v>10.5</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="P18">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="Q18">
-        <v>5.54</v>
+        <v>8.75</v>
       </c>
       <c r="R18">
-        <v>2.24</v>
+        <v>2.85</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T18">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.09</v>
+      </c>
+      <c r="Z18">
+        <v>5.4</v>
+      </c>
+      <c r="AA18">
+        <v>1.38</v>
+      </c>
+      <c r="AB18">
+        <v>2.62</v>
+      </c>
+      <c r="AC18">
+        <v>2.01</v>
+      </c>
+      <c r="AD18">
+        <v>1.69</v>
+      </c>
+      <c r="AE18">
+        <v>1.27</v>
+      </c>
+      <c r="AF18">
+        <v>1.9</v>
+      </c>
+      <c r="AG18">
+        <v>1.78</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.04</v>
+      </c>
+      <c r="AK18">
         <v>1.03</v>
-      </c>
-      <c r="Y18">
-        <v>1.18</v>
-      </c>
-      <c r="Z18">
-        <v>3.84</v>
-      </c>
-      <c r="AA18">
-        <v>1.71</v>
-      </c>
-      <c r="AB18">
-        <v>2.08</v>
-      </c>
-      <c r="AC18">
-        <v>2.66</v>
-      </c>
-      <c r="AD18">
-        <v>1.37</v>
-      </c>
-      <c r="AE18">
-        <v>1.11</v>
-      </c>
-      <c r="AF18">
-        <v>1.73</v>
-      </c>
-      <c r="AG18">
-        <v>2</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.25</v>
-      </c>
-      <c r="AK18">
-        <v>1.11</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.69</v>
+        <v>7.17</v>
       </c>
       <c r="O19">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>2.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q19">
-        <v>3.37</v>
+        <v>5.54</v>
       </c>
       <c r="R19">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="S19">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="U19">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>2.65</v>
+        <v>3.84</v>
       </c>
       <c r="AA19">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AB19">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="AC19">
-        <v>4.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD19">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-26 13:30:00</t>
+          <t>2026-10-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.13</v>
       </c>
       <c r="P20">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q20">
-        <v>2.23</v>
+        <v>3.37</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="S20">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="T20">
-        <v>3.18</v>
+        <v>2.31</v>
       </c>
       <c r="U20">
-        <v>2.45</v>
+        <v>3.48</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="Z20">
-        <v>3.85</v>
+        <v>2.65</v>
       </c>
       <c r="AA20">
-        <v>1.8</v>
+        <v>2.43</v>
       </c>
       <c r="AB20">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AC20">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="AD20">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="AG20">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AK20">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-10-26 13:45:00</t>
+          <t>2026-10-26 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.74</v>
+        <v>1.7</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>2.21</v>
+        <v>3.95</v>
       </c>
       <c r="Q21">
-        <v>3.41</v>
+        <v>2.23</v>
       </c>
       <c r="R21">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U21">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V21">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
         <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="AA21">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AC21">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
         <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-10-26 14:00:00</t>
+          <t>2026-10-26 13:45:00</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="Q22">
-        <v>4.48</v>
+        <v>3.41</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U22">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V22">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z22">
-        <v>4.17</v>
+        <v>3.72</v>
       </c>
       <c r="AA22">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB22">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AC22">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="AD22">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE22">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.86</v>
+        <v>1.49</v>
       </c>
       <c r="AK22">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q23">
-        <v>2.3</v>
+        <v>4.48</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.21</v>
       </c>
       <c r="Z23">
-        <v>3.79</v>
+        <v>4.17</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AB23">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="AC23">
-        <v>2.94</v>
+        <v>2.67</v>
       </c>
       <c r="AD23">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.19</v>
+        <v>1.86</v>
       </c>
       <c r="AK23">
-        <v>1.89</v>
+        <v>1.16</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
         <v>2.3</v>
       </c>
-      <c r="O24">
-        <v>3.6</v>
-      </c>
-      <c r="P24">
-        <v>2.55</v>
-      </c>
-      <c r="Q24">
-        <v>2.9</v>
-      </c>
       <c r="R24">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>5.28</v>
+        <v>3.79</v>
       </c>
       <c r="AA24">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>2.49</v>
+        <v>1.99</v>
       </c>
       <c r="AC24">
-        <v>2.21</v>
+        <v>2.94</v>
       </c>
       <c r="AD24">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AE24">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AG24">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="Q25">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="V25">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>3.58</v>
+        <v>5.28</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AB25">
-        <v>1.98</v>
+        <v>2.49</v>
       </c>
       <c r="AC25">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="AD25">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AE25">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="O26">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="P26">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="Q26">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
+        <v>1.1</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>1.21</v>
+      </c>
+      <c r="Z26">
+        <v>3.58</v>
+      </c>
+      <c r="AA26">
+        <v>1.85</v>
+      </c>
+      <c r="AB26">
+        <v>1.95</v>
+      </c>
+      <c r="AC26">
+        <v>2.92</v>
+      </c>
+      <c r="AD26">
+        <v>1.31</v>
+      </c>
+      <c r="AE26">
         <v>1.08</v>
       </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26">
-        <v>1.28</v>
-      </c>
-      <c r="Z26">
-        <v>3.5</v>
-      </c>
-      <c r="AA26">
-        <v>1.93</v>
-      </c>
-      <c r="AB26">
-        <v>1.85</v>
-      </c>
-      <c r="AC26">
-        <v>3.25</v>
-      </c>
-      <c r="AD26">
-        <v>1.32</v>
-      </c>
-      <c r="AE26">
-        <v>1.05</v>
-      </c>
       <c r="AF26">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-26 14:30:00</t>
+          <t>2026-10-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>5.25</v>
+        <v>2.35</v>
       </c>
       <c r="O27">
-        <v>3.92</v>
+        <v>3.23</v>
       </c>
       <c r="P27">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q27">
-        <v>5.75</v>
+        <v>3.05</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S27">
         <v>1.36</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U27">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="V27">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
         <v>1.06</v>
@@ -4746,28 +4746,28 @@
         <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA27">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AB27">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AD27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>2.23</v>
+        <v>1.35</v>
       </c>
       <c r="AK27">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-10-26 15:00:00</t>
+          <t>2026-10-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
+        <v>5.25</v>
+      </c>
+      <c r="O28">
+        <v>3.8</v>
+      </c>
+      <c r="P28">
+        <v>1.5</v>
+      </c>
+      <c r="Q28">
+        <v>5.75</v>
+      </c>
+      <c r="R28">
+        <v>2.25</v>
+      </c>
+      <c r="S28">
+        <v>1.36</v>
+      </c>
+      <c r="T28">
+        <v>3</v>
+      </c>
+      <c r="U28">
+        <v>2.56</v>
+      </c>
+      <c r="V28">
         <v>1.43</v>
       </c>
-      <c r="O28">
-        <v>4.45</v>
-      </c>
-      <c r="P28">
-        <v>6</v>
-      </c>
-      <c r="Q28">
-        <v>1.88</v>
-      </c>
-      <c r="R28">
-        <v>2.53</v>
-      </c>
-      <c r="S28">
-        <v>1.2</v>
-      </c>
-      <c r="T28">
-        <v>3.75</v>
-      </c>
-      <c r="U28">
-        <v>2.15</v>
-      </c>
-      <c r="V28">
-        <v>1.65</v>
-      </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="Z28">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA28">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AB28">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.12</v>
+        <v>2.23</v>
       </c>
       <c r="AK28">
-        <v>2.74</v>
+        <v>1.07</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,81 +5036,81 @@
         </is>
       </c>
       <c r="N29">
+        <v>1.44</v>
+      </c>
+      <c r="O29">
+        <v>4.45</v>
+      </c>
+      <c r="P29">
+        <v>5.8</v>
+      </c>
+      <c r="Q29">
+        <v>1.88</v>
+      </c>
+      <c r="R29">
+        <v>2.53</v>
+      </c>
+      <c r="S29">
+        <v>1.2</v>
+      </c>
+      <c r="T29">
+        <v>3.64</v>
+      </c>
+      <c r="U29">
         <v>2.15</v>
       </c>
-      <c r="O29">
-        <v>3.4</v>
-      </c>
-      <c r="P29">
-        <v>2.38</v>
-      </c>
-      <c r="Q29">
-        <v>2.91</v>
-      </c>
-      <c r="R29">
-        <v>2.18</v>
-      </c>
-      <c r="S29">
-        <v>1.31</v>
-      </c>
-      <c r="T29">
-        <v>3.22</v>
-      </c>
-      <c r="U29">
-        <v>2.54</v>
-      </c>
       <c r="V29">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
+        <v>1.1</v>
+      </c>
+      <c r="Z29">
+        <v>5.1</v>
+      </c>
+      <c r="AA29">
+        <v>1.44</v>
+      </c>
+      <c r="AB29">
+        <v>2.42</v>
+      </c>
+      <c r="AC29">
+        <v>2.26</v>
+      </c>
+      <c r="AD29">
+        <v>1.65</v>
+      </c>
+      <c r="AE29">
         <v>1.19</v>
       </c>
-      <c r="Z29">
-        <v>4</v>
-      </c>
-      <c r="AA29">
-        <v>1.74</v>
-      </c>
-      <c r="AB29">
-        <v>2.01</v>
-      </c>
-      <c r="AC29">
+      <c r="AF29">
+        <v>1.7</v>
+      </c>
+      <c r="AG29">
+        <v>2.05</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.12</v>
+      </c>
+      <c r="AK29">
         <v>2.74</v>
       </c>
-      <c r="AD29">
-        <v>1.35</v>
-      </c>
-      <c r="AE29">
-        <v>1.1</v>
-      </c>
-      <c r="AF29">
-        <v>1.59</v>
-      </c>
-      <c r="AG29">
-        <v>2.15</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.3</v>
-      </c>
-      <c r="AK29">
-        <v>1.5</v>
-      </c>
       <c r="AL29">
         <v>0</v>
       </c>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-10-26 15:05:00</t>
+          <t>2026-10-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G30">
@@ -5202,61 +5202,61 @@
         <v>2.15</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="Q30">
-        <v>2.71</v>
+        <v>2.91</v>
       </c>
       <c r="R30">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T30">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="U30">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="V30">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="W30">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z30">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA30">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="AB30">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="AC30">
-        <v>2.19</v>
+        <v>2.74</v>
       </c>
       <c r="AD30">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="AE30">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AG30">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-10-26 15:30:00</t>
+          <t>2026-10-26 15:05:00</t>
         </is>
       </c>
     </row>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="O31">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31">
-        <v>2.87</v>
+        <v>1.49</v>
       </c>
       <c r="AB31">
+        <v>2.6</v>
+      </c>
+      <c r="AC31">
+        <v>2.19</v>
+      </c>
+      <c r="AD31">
+        <v>1.63</v>
+      </c>
+      <c r="AE31">
+        <v>1.25</v>
+      </c>
+      <c r="AF31">
         <v>1.4</v>
       </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5478,27 +5478,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="O32">
-        <v>4.45</v>
+        <v>3.05</v>
       </c>
       <c r="P32">
+        <v>4.2</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>2.87</v>
+      </c>
+      <c r="AB32">
         <v>1.4</v>
       </c>
-      <c r="Q32">
-        <v>5.8</v>
-      </c>
-      <c r="R32">
-        <v>2.27</v>
-      </c>
-      <c r="S32">
-        <v>1.35</v>
-      </c>
-      <c r="T32">
-        <v>3</v>
-      </c>
-      <c r="U32">
-        <v>2.62</v>
-      </c>
-      <c r="V32">
-        <v>1.44</v>
-      </c>
-      <c r="W32">
-        <v>1.1</v>
-      </c>
-      <c r="X32">
-        <v>1</v>
-      </c>
-      <c r="Y32">
-        <v>1.25</v>
-      </c>
-      <c r="Z32">
-        <v>3.26</v>
-      </c>
-      <c r="AA32">
-        <v>1.81</v>
-      </c>
-      <c r="AB32">
-        <v>2.01</v>
-      </c>
       <c r="AC32">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-10-26 15:45:00</t>
+          <t>2026-10-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.88</v>
+        <v>7.7</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="P33">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-10-26 16:30:00</t>
+          <t>2026-10-26 15:45:00</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.64</v>
+        <v>1.88</v>
       </c>
       <c r="O34">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="P34">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="Q34">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.03</v>
+        <v>2.64</v>
       </c>
       <c r="O35">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="P35">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q35">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="R35">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.08</v>
+        <v>2.72</v>
       </c>
       <c r="U35">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z35">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AA35">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AB35">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AC35">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD35">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AG35">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
+        <v>1.25</v>
+      </c>
+      <c r="AK35">
         <v>1.26</v>
-      </c>
-      <c r="AK35">
-        <v>1.61</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,65 +6177,65 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="O36">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="P36">
-        <v>2.31</v>
+        <v>3.16</v>
       </c>
       <c r="Q36">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="R36">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S36">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="T36">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="U36">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z36">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="AA36">
+        <v>1.76</v>
+      </c>
+      <c r="AB36">
+        <v>1.92</v>
+      </c>
+      <c r="AC36">
+        <v>2.88</v>
+      </c>
+      <c r="AD36">
+        <v>1.32</v>
+      </c>
+      <c r="AE36">
+        <v>1.09</v>
+      </c>
+      <c r="AF36">
+        <v>1.63</v>
+      </c>
+      <c r="AG36">
         <v>2.06</v>
       </c>
-      <c r="AB36">
-        <v>1.68</v>
-      </c>
-      <c r="AC36">
-        <v>3.9</v>
-      </c>
-      <c r="AD36">
-        <v>1.22</v>
-      </c>
-      <c r="AE36">
-        <v>1.04</v>
-      </c>
-      <c r="AF36">
-        <v>1.83</v>
-      </c>
-      <c r="AG36">
-        <v>1.85</v>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-26 16:45:00</t>
+          <t>2026-10-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P37">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="Q37">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="R37">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S37">
+        <v>1.45</v>
+      </c>
+      <c r="T37">
+        <v>2.71</v>
+      </c>
+      <c r="U37">
+        <v>3.2</v>
+      </c>
+      <c r="V37">
+        <v>1.35</v>
+      </c>
+      <c r="W37">
+        <v>1.06</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.33</v>
+      </c>
+      <c r="Z37">
+        <v>3</v>
+      </c>
+      <c r="AA37">
+        <v>2.06</v>
+      </c>
+      <c r="AB37">
+        <v>1.68</v>
+      </c>
+      <c r="AC37">
+        <v>3.9</v>
+      </c>
+      <c r="AD37">
+        <v>1.22</v>
+      </c>
+      <c r="AE37">
+        <v>1.04</v>
+      </c>
+      <c r="AF37">
+        <v>1.83</v>
+      </c>
+      <c r="AG37">
+        <v>1.85</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.36</v>
       </c>
-      <c r="T37">
-        <v>3</v>
-      </c>
-      <c r="U37">
-        <v>2.5</v>
-      </c>
-      <c r="V37">
-        <v>1.44</v>
-      </c>
-      <c r="W37">
-        <v>1.05</v>
-      </c>
-      <c r="X37">
-        <v>1.04</v>
-      </c>
-      <c r="Y37">
-        <v>1.22</v>
-      </c>
-      <c r="Z37">
-        <v>3.8</v>
-      </c>
-      <c r="AA37">
-        <v>1.82</v>
-      </c>
-      <c r="AB37">
-        <v>1.9</v>
-      </c>
-      <c r="AC37">
-        <v>3.2</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.08</v>
-      </c>
-      <c r="AF37">
-        <v>1.73</v>
-      </c>
-      <c r="AG37">
-        <v>2.1</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.29</v>
-      </c>
       <c r="AK37">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,61 +6503,61 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O38">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>2.05</v>
+        <v>2.66</v>
       </c>
       <c r="Q38">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="R38">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U38">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
         <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>4.07</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB38">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD38">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
         <v>2.2</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK38">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-26 17:00:00</t>
+          <t>2026-10-26 16:45:00</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="O39">
-        <v>3.35</v>
+        <v>3.53</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="Q39">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="R39">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S39">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="U39">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="V39">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.1</v>
+        <v>4.07</v>
       </c>
       <c r="AA39">
+        <v>1.73</v>
+      </c>
+      <c r="AB39">
+        <v>2.07</v>
+      </c>
+      <c r="AC39">
+        <v>2.9</v>
+      </c>
+      <c r="AD39">
+        <v>1.39</v>
+      </c>
+      <c r="AE39">
+        <v>1.14</v>
+      </c>
+      <c r="AF39">
+        <v>1.59</v>
+      </c>
+      <c r="AG39">
         <v>2.18</v>
-      </c>
-      <c r="AB39">
-        <v>1.74</v>
-      </c>
-      <c r="AC39">
-        <v>3.45</v>
-      </c>
-      <c r="AD39">
-        <v>1.25</v>
-      </c>
-      <c r="AE39">
-        <v>1.05</v>
-      </c>
-      <c r="AF39">
-        <v>1.91</v>
-      </c>
-      <c r="AG39">
-        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,81 +6829,81 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="O40">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P40">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="Q40">
+        <v>2.58</v>
+      </c>
+      <c r="R40">
+        <v>2.21</v>
+      </c>
+      <c r="S40">
+        <v>1.44</v>
+      </c>
+      <c r="T40">
+        <v>2.5</v>
+      </c>
+      <c r="U40">
         <v>3.2</v>
-      </c>
-      <c r="R40">
-        <v>1.93</v>
-      </c>
-      <c r="S40">
-        <v>1.4</v>
-      </c>
-      <c r="T40">
-        <v>2.45</v>
-      </c>
-      <c r="U40">
-        <v>2.95</v>
       </c>
       <c r="V40">
         <v>1.33</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z40">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA40">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AB40">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AC40">
-        <v>3.89</v>
+        <v>3.45</v>
       </c>
       <c r="AD40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE40">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG40">
+        <v>1.8</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.25</v>
+      </c>
+      <c r="AK40">
         <v>1.83</v>
       </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.34</v>
-      </c>
-      <c r="AK40">
-        <v>1.4</v>
-      </c>
       <c r="AL40">
         <v>0</v>
       </c>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-26 17:30:00</t>
+          <t>2026-10-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="O41">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="P41">
-        <v>3.65</v>
+        <v>2.59</v>
       </c>
       <c r="Q41">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S41">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U41">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z41">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA41">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB41">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AC41">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="AD41">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF41">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG41">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK41">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-26 17:45:00</t>
+          <t>2026-10-26 17:30:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="Q42">
+        <v>2.4</v>
+      </c>
+      <c r="R42">
+        <v>2.1</v>
+      </c>
+      <c r="S42">
+        <v>1.43</v>
+      </c>
+      <c r="T42">
+        <v>2.88</v>
+      </c>
+      <c r="U42">
+        <v>2.8</v>
+      </c>
+      <c r="V42">
+        <v>1.36</v>
+      </c>
+      <c r="W42">
+        <v>1.05</v>
+      </c>
+      <c r="X42">
+        <v>1.04</v>
+      </c>
+      <c r="Y42">
+        <v>1.3</v>
+      </c>
+      <c r="Z42">
+        <v>3.2</v>
+      </c>
+      <c r="AA42">
         <v>2.05</v>
       </c>
-      <c r="R42">
-        <v>2.4</v>
-      </c>
-      <c r="S42">
-        <v>1.3</v>
-      </c>
-      <c r="T42">
-        <v>3.3</v>
-      </c>
-      <c r="U42">
-        <v>2.5</v>
-      </c>
-      <c r="V42">
-        <v>1.5</v>
-      </c>
-      <c r="W42">
-        <v>1.11</v>
-      </c>
-      <c r="X42">
-        <v>1.02</v>
-      </c>
-      <c r="Y42">
-        <v>1.21</v>
-      </c>
-      <c r="Z42">
-        <v>4.35</v>
-      </c>
-      <c r="AA42">
-        <v>1.66</v>
-      </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AC42">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="AD42">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AE42">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AG42">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-26 18:00:00</t>
+          <t>2026-10-26 17:45:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-26 19:00:00</t>
+          <t>2026-10-26 18:00:00</t>
         </is>
       </c>
     </row>
@@ -7434,27 +7434,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-26 19:05:00</t>
+          <t>2026-10-26 19:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z45">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE45">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK45">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-10-26 19:30:00</t>
+          <t>2026-10-26 19:05:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
+        <v>1.95</v>
+      </c>
+      <c r="O46">
+        <v>3.35</v>
+      </c>
+      <c r="P46">
         <v>3.3</v>
       </c>
-      <c r="O46">
-        <v>3.25</v>
-      </c>
-      <c r="P46">
-        <v>1.98</v>
-      </c>
       <c r="Q46">
-        <v>3.89</v>
+        <v>2.5</v>
       </c>
       <c r="R46">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U46">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="V46">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W46">
         <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z46">
-        <v>3.02</v>
+        <v>3.66</v>
       </c>
       <c r="AA46">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="AB46">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AC46">
-        <v>3.97</v>
+        <v>3.18</v>
       </c>
       <c r="AD46">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AE46">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG46">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
+        <v>3.3</v>
+      </c>
+      <c r="O47">
+        <v>3.25</v>
+      </c>
+      <c r="P47">
+        <v>1.98</v>
+      </c>
+      <c r="Q47">
+        <v>3.89</v>
+      </c>
+      <c r="R47">
+        <v>1.97</v>
+      </c>
+      <c r="S47">
+        <v>1.4</v>
+      </c>
+      <c r="T47">
+        <v>2.75</v>
+      </c>
+      <c r="U47">
+        <v>2.83</v>
+      </c>
+      <c r="V47">
         <v>1.33</v>
       </c>
-      <c r="O47">
-        <v>5.1</v>
-      </c>
-      <c r="P47">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q47">
-        <v>1.75</v>
-      </c>
-      <c r="R47">
-        <v>2.5</v>
-      </c>
-      <c r="S47">
-        <v>1.25</v>
-      </c>
-      <c r="T47">
-        <v>3.56</v>
-      </c>
-      <c r="U47">
-        <v>2.25</v>
-      </c>
-      <c r="V47">
-        <v>1.57</v>
-      </c>
       <c r="W47">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="Z47">
-        <v>4.65</v>
+        <v>3.02</v>
       </c>
       <c r="AA47">
-        <v>1.6</v>
+        <v>2.11</v>
       </c>
       <c r="AB47">
-        <v>2.39</v>
+        <v>1.65</v>
       </c>
       <c r="AC47">
-        <v>2.45</v>
+        <v>3.97</v>
       </c>
       <c r="AD47">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AE47">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AF47">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG47">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK47">
-        <v>3.09</v>
+        <v>1.16</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-10-26 20:00:00</t>
+          <t>2026-10-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="P48">
-        <v>5.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q48">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="R48">
+        <v>2.5</v>
+      </c>
+      <c r="S48">
+        <v>1.25</v>
+      </c>
+      <c r="T48">
+        <v>3.56</v>
+      </c>
+      <c r="U48">
         <v>2.25</v>
       </c>
-      <c r="S48">
-        <v>1.35</v>
-      </c>
-      <c r="T48">
-        <v>3</v>
-      </c>
-      <c r="U48">
-        <v>2.63</v>
-      </c>
       <c r="V48">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>3.28</v>
+        <v>4.65</v>
       </c>
       <c r="AA48">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC48">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD48">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AE48">
+        <v>1.22</v>
+      </c>
+      <c r="AF48">
+        <v>1.88</v>
+      </c>
+      <c r="AG48">
+        <v>1.82</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.11</v>
       </c>
-      <c r="AF48">
-        <v>2</v>
-      </c>
-      <c r="AG48">
-        <v>1.72</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.15</v>
-      </c>
       <c r="AK48">
-        <v>2.44</v>
+        <v>3.09</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-10-26 20:30:00</t>
+          <t>2026-10-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-10-26 21:00:00</t>
+          <t>2026-10-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -8412,156 +8412,319 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Montego Bay United</t>
         </is>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr">
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>0</v>
-      </c>
-      <c r="AK50">
-        <v>0</v>
-      </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
-      <c r="AO50">
-        <v>-1</v>
-      </c>
-      <c r="AP50">
-        <v>-1</v>
-      </c>
-      <c r="AQ50">
-        <v>0</v>
-      </c>
-      <c r="AR50">
-        <v>0</v>
-      </c>
-      <c r="AS50">
-        <v>0</v>
-      </c>
-      <c r="AT50">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
         <is>
           <t>2026-10-26 22:00:00</t>
         </is>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1637,7 +1637,7 @@
         <v>2.69</v>
       </c>
       <c r="V8">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
         <v>1.05</v>
@@ -1649,13 +1649,13 @@
         <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA8">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB8">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
         <v>3.28</v>
@@ -1670,7 +1670,7 @@
         <v>1.74</v>
       </c>
       <c r="AG8">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
         <v>1.52</v>
@@ -3424,13 +3424,13 @@
         <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W19">
         <v>1.12</v>
@@ -3445,7 +3445,7 @@
         <v>3.84</v>
       </c>
       <c r="AA19">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB19">
         <v>2.08</v>
@@ -3937,7 +3937,7 @@
         <v>1.68</v>
       </c>
       <c r="AB22">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AC22">
         <v>2.78</v>
@@ -4589,7 +4589,7 @@
         <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC26">
         <v>2.92</v>
@@ -4620,7 +4620,7 @@
         <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O27">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
         <v>2.7</v>
@@ -4737,7 +4737,7 @@
         <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1</v>
@@ -4900,7 +4900,7 @@
         <v>1.43</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>1</v>
@@ -4918,7 +4918,7 @@
         <v>1.95</v>
       </c>
       <c r="AC28">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AD28">
         <v>1.31</v>
@@ -5733,7 +5733,7 @@
         <v>2.01</v>
       </c>
       <c r="AC33">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD33">
         <v>1.37</v>
@@ -5761,7 +5761,7 @@
         <v>2.9</v>
       </c>
       <c r="AK33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6026,52 +6026,52 @@
         <v>3.75</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T35">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="U35">
         <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AA35">
         <v>2</v>
       </c>
       <c r="AB35">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AC35">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AD35">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AG35">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,10 +6186,10 @@
         <v>3.16</v>
       </c>
       <c r="Q36">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="R36">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S36">
         <v>1.28</v>
@@ -6198,7 +6198,7 @@
         <v>3.08</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V36">
         <v>1.44</v>
@@ -6210,31 +6210,31 @@
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA36">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB36">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
         <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1133,55 +1133,55 @@
         <v>6.8</v>
       </c>
       <c r="Q5">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="S5">
+        <v>1.18</v>
+      </c>
+      <c r="T5">
+        <v>3.92</v>
+      </c>
+      <c r="U5">
+        <v>1.95</v>
+      </c>
+      <c r="V5">
+        <v>1.75</v>
+      </c>
+      <c r="W5">
         <v>1.16</v>
-      </c>
-      <c r="T5">
-        <v>4.05</v>
-      </c>
-      <c r="U5">
-        <v>1.91</v>
-      </c>
-      <c r="V5">
-        <v>1.8</v>
-      </c>
-      <c r="W5">
-        <v>1.17</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z5">
-        <v>6.55</v>
+        <v>6.15</v>
       </c>
       <c r="AA5">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB5">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AC5">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AD5">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AE5">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="O6">
-        <v>3.89</v>
+        <v>4.15</v>
       </c>
       <c r="P6">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -1302,10 +1302,10 @@
         <v>2.6</v>
       </c>
       <c r="S6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
         <v>2.38</v>
@@ -1465,13 +1465,13 @@
         <v>2.31</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U7">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="V7">
         <v>1.53</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2117,13 +2117,13 @@
         <v>2.5</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T11">
         <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
         <v>1.5</v>
@@ -2144,7 +2144,7 @@
         <v>1.71</v>
       </c>
       <c r="AB11">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
         <v>2.71</v>
@@ -2156,7 +2156,7 @@
         <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG11">
         <v>1.61</v>
@@ -2763,7 +2763,7 @@
         <v>1.95</v>
       </c>
       <c r="Q15">
-        <v>3.85</v>
+        <v>3.28</v>
       </c>
       <c r="R15">
         <v>2.35</v>
@@ -2793,7 +2793,7 @@
         <v>4.8</v>
       </c>
       <c r="AA15">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
         <v>2.35</v>
@@ -2959,7 +2959,7 @@
         <v>1.36</v>
       </c>
       <c r="AB16">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AC16">
         <v>1.92</v>
@@ -3089,22 +3089,22 @@
         <v>2.87</v>
       </c>
       <c r="Q17">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="R17">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="S17">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="T17">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U17">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="V17">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W17">
         <v>1.04</v>
@@ -3137,7 +3137,7 @@
         <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>1.65</v>
       </c>
       <c r="Q19">
-        <v>5.54</v>
+        <v>5.1</v>
       </c>
       <c r="R19">
         <v>2.24</v>
@@ -3442,7 +3442,7 @@
         <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AA19">
         <v>1.73</v>
@@ -3463,7 +3463,7 @@
         <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>2.43</v>
       </c>
       <c r="AB20">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AC20">
         <v>4.75</v>
@@ -3642,7 +3642,7 @@
         <v>1.39</v>
       </c>
       <c r="AK20">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
         <v>1.73</v>
       </c>
       <c r="Q23">
-        <v>4.48</v>
+        <v>4.32</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -4257,7 +4257,7 @@
         <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="AA24">
         <v>1.81</v>
@@ -4387,13 +4387,13 @@
         <v>2.3</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
         <v>2.38</v>
@@ -4405,10 +4405,10 @@
         <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W25">
         <v>1.17</v>
@@ -4423,7 +4423,7 @@
         <v>5.28</v>
       </c>
       <c r="AA25">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AB25">
         <v>2.49</v>
@@ -4457,7 +4457,7 @@
         <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O29">
         <v>4.45</v>
@@ -5081,10 +5081,10 @@
         <v>2.42</v>
       </c>
       <c r="AC29">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AD29">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE29">
         <v>1.19</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
         <v>2.91</v>
@@ -5220,7 +5220,7 @@
         <v>3.22</v>
       </c>
       <c r="U30">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="V30">
         <v>1.49</v>
@@ -5371,10 +5371,10 @@
         <v>3</v>
       </c>
       <c r="Q31">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="R31">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5398,7 +5398,7 @@
         <v>1.09</v>
       </c>
       <c r="Z31">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA31">
         <v>1.49</v>
@@ -5854,10 +5854,10 @@
         <v>1.88</v>
       </c>
       <c r="O34">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6521,7 +6521,7 @@
         <v>1.36</v>
       </c>
       <c r="T38">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U38">
         <v>2.5</v>
@@ -6536,7 +6536,7 @@
         <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
         <v>3.8</v>
@@ -6545,13 +6545,13 @@
         <v>1.82</v>
       </c>
       <c r="AB38">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC38">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE38">
         <v>1.08</v>
@@ -6678,7 +6678,7 @@
         <v>3.75</v>
       </c>
       <c r="R39">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S39">
         <v>1.29</v>
@@ -6693,37 +6693,37 @@
         <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>4.07</v>
+        <v>3.92</v>
       </c>
       <c r="AA39">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB39">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC39">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD39">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF39">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6832,16 +6832,16 @@
         <v>1.92</v>
       </c>
       <c r="O40">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
         <v>4</v>
       </c>
       <c r="Q40">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="R40">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="S40">
         <v>1.44</v>
@@ -6850,7 +6850,7 @@
         <v>2.5</v>
       </c>
       <c r="U40">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="V40">
         <v>1.33</v>
@@ -6862,13 +6862,13 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z40">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA40">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AB40">
         <v>1.74</v>
@@ -6883,7 +6883,7 @@
         <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG40">
         <v>1.8</v>
@@ -7345,7 +7345,7 @@
         <v>1.5</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7357,7 +7357,7 @@
         <v>4.35</v>
       </c>
       <c r="AA43">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB43">
         <v>2.15</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O46">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
         <v>3.3</v>
@@ -7828,7 +7828,7 @@
         <v>2.73</v>
       </c>
       <c r="U46">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="V46">
         <v>1.42</v>
@@ -7843,7 +7843,7 @@
         <v>1.28</v>
       </c>
       <c r="Z46">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="AA46">
         <v>1.92</v>
@@ -7858,7 +7858,7 @@
         <v>1.34</v>
       </c>
       <c r="AE46">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF46">
         <v>1.7</v>
@@ -7976,7 +7976,7 @@
         <v>3.25</v>
       </c>
       <c r="P47">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q47">
         <v>3.89</v>
@@ -7991,7 +7991,7 @@
         <v>2.75</v>
       </c>
       <c r="U47">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="V47">
         <v>1.33</v>
@@ -8006,7 +8006,7 @@
         <v>1.37</v>
       </c>
       <c r="Z47">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="AA47">
         <v>2.11</v>
@@ -8151,7 +8151,7 @@
         <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="U48">
         <v>2.25</v>
@@ -8172,7 +8172,7 @@
         <v>4.65</v>
       </c>
       <c r="AA48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB48">
         <v>2.39</v>
@@ -8305,7 +8305,7 @@
         <v>5.75</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R49">
         <v>2.25</v>
@@ -8350,7 +8350,7 @@
         <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG49">
         <v>1.72</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
         <v>2.44</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2156,7 +2156,7 @@
         <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
         <v>1.61</v>
@@ -2796,7 +2796,7 @@
         <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AC15">
         <v>2.28</v>
@@ -3137,7 +3137,7 @@
         <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>1.2</v>
@@ -3279,7 +3279,7 @@
         <v>1.09</v>
       </c>
       <c r="Z18">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA18">
         <v>1.38</v>
@@ -3297,10 +3297,10 @@
         <v>1.27</v>
       </c>
       <c r="AF18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG18">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3738,10 +3738,10 @@
         <v>3.7</v>
       </c>
       <c r="P21">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="Q21">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="R21">
         <v>2.3</v>
@@ -3750,10 +3750,10 @@
         <v>1.27</v>
       </c>
       <c r="T21">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U21">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V21">
         <v>1.5</v>
@@ -3768,22 +3768,22 @@
         <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="AA21">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC21">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
         <v>1.67</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>2.6</v>
       </c>
       <c r="Q25">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R25">
         <v>2.38</v>
@@ -4457,7 +4457,7 @@
         <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>2.25</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
         <v>2.7</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O28">
         <v>3.8</v>
@@ -4882,13 +4882,13 @@
         <v>1.5</v>
       </c>
       <c r="Q28">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
         <v>3</v>
@@ -4906,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z28">
         <v>3.6</v>
@@ -4918,7 +4918,7 @@
         <v>1.95</v>
       </c>
       <c r="AC28">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AD28">
         <v>1.31</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
         <v>2.6</v>
@@ -5368,7 +5368,7 @@
         <v>3.8</v>
       </c>
       <c r="P31">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q31">
         <v>2.67</v>
@@ -5691,7 +5691,7 @@
         <v>7.7</v>
       </c>
       <c r="O33">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="P33">
         <v>1.4</v>
@@ -6023,10 +6023,10 @@
         <v>2.3</v>
       </c>
       <c r="Q35">
-        <v>3.75</v>
+        <v>3.81</v>
       </c>
       <c r="R35">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
         <v>1.34</v>
@@ -6047,10 +6047,10 @@
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z35">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
         <v>2</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6195,13 +6195,13 @@
         <v>1.28</v>
       </c>
       <c r="T36">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="U36">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
         <v>1.08</v>
@@ -6216,7 +6216,7 @@
         <v>3.68</v>
       </c>
       <c r="AA36">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB36">
         <v>1.95</v>
@@ -6720,7 +6720,7 @@
         <v>1.16</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
         <v>2.2</v>
@@ -7007,7 +7007,7 @@
         <v>1.93</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T41">
         <v>2.45</v>
@@ -7360,7 +7360,7 @@
         <v>1.65</v>
       </c>
       <c r="AB43">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC43">
         <v>2.64</v>
@@ -7831,10 +7831,10 @@
         <v>2.81</v>
       </c>
       <c r="V46">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
         <v>1</v>
@@ -7976,7 +7976,7 @@
         <v>3.25</v>
       </c>
       <c r="P47">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q47">
         <v>3.89</v>
@@ -8024,7 +8024,7 @@
         <v>1.04</v>
       </c>
       <c r="AF47">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG47">
         <v>1.83</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1643,7 +1643,7 @@
         <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
         <v>1.3</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="P27">
         <v>2.7</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU51"/>
+  <dimension ref="A1:AU52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="P11">
         <v>7.8</v>
@@ -2120,10 +2120,10 @@
         <v>1.28</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
         <v>1.5</v>
@@ -2138,25 +2138,25 @@
         <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>3.96</v>
+        <v>4.07</v>
       </c>
       <c r="AA11">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB11">
         <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AD11">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
         <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG11">
         <v>1.61</v>
@@ -4067,10 +4067,10 @@
         <v>1.73</v>
       </c>
       <c r="Q23">
-        <v>4.32</v>
+        <v>4.48</v>
       </c>
       <c r="R23">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
         <v>3.4</v>
@@ -5217,16 +5217,16 @@
         <v>1.31</v>
       </c>
       <c r="T30">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V30">
         <v>1.49</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X30">
         <v>1.03</v>
@@ -5419,7 +5419,7 @@
         <v>1.4</v>
       </c>
       <c r="AG31">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="P34">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA34">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>2.84</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="O35">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="P35">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q35">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.03</v>
+        <v>2.64</v>
       </c>
       <c r="O36">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q36">
-        <v>2.5</v>
+        <v>3.81</v>
       </c>
       <c r="R36">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T36">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z36">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC36">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG36">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="O37">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="P37">
-        <v>2.31</v>
+        <v>3.16</v>
       </c>
       <c r="Q37">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="R37">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S37">
+        <v>1.28</v>
+      </c>
+      <c r="T37">
+        <v>3.07</v>
+      </c>
+      <c r="U37">
+        <v>2.59</v>
+      </c>
+      <c r="V37">
         <v>1.45</v>
       </c>
-      <c r="T37">
-        <v>2.71</v>
-      </c>
-      <c r="U37">
-        <v>3.2</v>
-      </c>
-      <c r="V37">
-        <v>1.35</v>
-      </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y37">
+        <v>1.2</v>
+      </c>
+      <c r="Z37">
+        <v>3.68</v>
+      </c>
+      <c r="AA37">
+        <v>1.81</v>
+      </c>
+      <c r="AB37">
+        <v>1.95</v>
+      </c>
+      <c r="AC37">
+        <v>2.83</v>
+      </c>
+      <c r="AD37">
         <v>1.33</v>
       </c>
-      <c r="Z37">
-        <v>3</v>
-      </c>
-      <c r="AA37">
-        <v>2.06</v>
-      </c>
-      <c r="AB37">
-        <v>1.68</v>
-      </c>
-      <c r="AC37">
-        <v>3.9</v>
-      </c>
-      <c r="AD37">
-        <v>1.22</v>
-      </c>
       <c r="AE37">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-26 16:45:00</t>
+          <t>2026-10-26 16:30:00</t>
         </is>
       </c>
     </row>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P38">
-        <v>2.66</v>
+        <v>2.31</v>
       </c>
       <c r="Q38">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="R38">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S38">
+        <v>1.45</v>
+      </c>
+      <c r="T38">
+        <v>2.71</v>
+      </c>
+      <c r="U38">
+        <v>3.2</v>
+      </c>
+      <c r="V38">
+        <v>1.35</v>
+      </c>
+      <c r="W38">
+        <v>1.06</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.33</v>
+      </c>
+      <c r="Z38">
+        <v>3</v>
+      </c>
+      <c r="AA38">
+        <v>2.06</v>
+      </c>
+      <c r="AB38">
+        <v>1.68</v>
+      </c>
+      <c r="AC38">
+        <v>3.9</v>
+      </c>
+      <c r="AD38">
+        <v>1.22</v>
+      </c>
+      <c r="AE38">
+        <v>1.04</v>
+      </c>
+      <c r="AF38">
+        <v>1.83</v>
+      </c>
+      <c r="AG38">
+        <v>1.85</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.36</v>
       </c>
-      <c r="T38">
-        <v>2.99</v>
-      </c>
-      <c r="U38">
-        <v>2.5</v>
-      </c>
-      <c r="V38">
-        <v>1.44</v>
-      </c>
-      <c r="W38">
-        <v>1.05</v>
-      </c>
-      <c r="X38">
-        <v>1.04</v>
-      </c>
-      <c r="Y38">
-        <v>1.25</v>
-      </c>
-      <c r="Z38">
-        <v>3.8</v>
-      </c>
-      <c r="AA38">
-        <v>1.82</v>
-      </c>
-      <c r="AB38">
-        <v>1.88</v>
-      </c>
-      <c r="AC38">
-        <v>3.1</v>
-      </c>
-      <c r="AD38">
-        <v>1.32</v>
-      </c>
-      <c r="AE38">
-        <v>1.08</v>
-      </c>
-      <c r="AF38">
-        <v>1.65</v>
-      </c>
-      <c r="AG38">
-        <v>2.2</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.29</v>
-      </c>
       <c r="AK38">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,61 +6666,61 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>2.05</v>
+        <v>2.66</v>
       </c>
       <c r="Q39">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="R39">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U39">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AB39">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC39">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AD39">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AE39">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG39">
         <v>2.2</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-26 17:00:00</t>
+          <t>2026-10-26 16:45:00</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="P40">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="Q40">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="R40">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="U40">
-        <v>3.23</v>
+        <v>2.47</v>
       </c>
       <c r="V40">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA40">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="AB40">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="AC40">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="AD40">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE40">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG40">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,81 +6992,81 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.6</v>
+        <v>1.93</v>
       </c>
       <c r="O41">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
+        <v>4</v>
+      </c>
+      <c r="Q41">
         <v>2.59</v>
       </c>
-      <c r="Q41">
-        <v>3.2</v>
-      </c>
       <c r="R41">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="S41">
         <v>1.44</v>
       </c>
       <c r="T41">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U41">
-        <v>2.95</v>
+        <v>3.23</v>
       </c>
       <c r="V41">
         <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z41">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA41">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AB41">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AC41">
-        <v>3.89</v>
+        <v>3.45</v>
       </c>
       <c r="AD41">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE41">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG41">
+        <v>1.8</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.25</v>
+      </c>
+      <c r="AK41">
         <v>1.83</v>
       </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.34</v>
-      </c>
-      <c r="AK41">
-        <v>1.4</v>
-      </c>
       <c r="AL41">
         <v>0</v>
       </c>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-26 17:30:00</t>
+          <t>2026-10-26 17:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="O42">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="P42">
-        <v>3.65</v>
+        <v>2.59</v>
       </c>
       <c r="Q42">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S42">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T42">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U42">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z42">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA42">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB42">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AC42">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="AD42">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE42">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG42">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK42">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-26 17:45:00</t>
+          <t>2026-10-26 17:30:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="O43">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="Q43">
+        <v>2.4</v>
+      </c>
+      <c r="R43">
+        <v>2.1</v>
+      </c>
+      <c r="S43">
+        <v>1.43</v>
+      </c>
+      <c r="T43">
+        <v>2.88</v>
+      </c>
+      <c r="U43">
+        <v>2.8</v>
+      </c>
+      <c r="V43">
+        <v>1.36</v>
+      </c>
+      <c r="W43">
+        <v>1.05</v>
+      </c>
+      <c r="X43">
+        <v>1.04</v>
+      </c>
+      <c r="Y43">
+        <v>1.3</v>
+      </c>
+      <c r="Z43">
+        <v>3.2</v>
+      </c>
+      <c r="AA43">
         <v>2.05</v>
       </c>
-      <c r="R43">
-        <v>2.4</v>
-      </c>
-      <c r="S43">
-        <v>1.3</v>
-      </c>
-      <c r="T43">
-        <v>3.3</v>
-      </c>
-      <c r="U43">
-        <v>2.5</v>
-      </c>
-      <c r="V43">
-        <v>1.5</v>
-      </c>
-      <c r="W43">
-        <v>1.12</v>
-      </c>
-      <c r="X43">
-        <v>1.02</v>
-      </c>
-      <c r="Y43">
-        <v>1.21</v>
-      </c>
-      <c r="Z43">
-        <v>4.35</v>
-      </c>
-      <c r="AA43">
-        <v>1.65</v>
-      </c>
       <c r="AB43">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AC43">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="AD43">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-26 18:00:00</t>
+          <t>2026-10-26 17:45:00</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-26 19:00:00</t>
+          <t>2026-10-26 18:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-10-26 19:05:00</t>
+          <t>2026-10-26 19:00:00</t>
         </is>
       </c>
     </row>
@@ -7760,27 +7760,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z46">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA46">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD46">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE46">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF46">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-10-26 19:30:00</t>
+          <t>2026-10-26 19:05:00</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
+        <v>2.02</v>
+      </c>
+      <c r="O47">
+        <v>3.52</v>
+      </c>
+      <c r="P47">
         <v>3.3</v>
       </c>
-      <c r="O47">
-        <v>3.25</v>
-      </c>
-      <c r="P47">
-        <v>1.98</v>
-      </c>
       <c r="Q47">
-        <v>3.89</v>
+        <v>2.5</v>
       </c>
       <c r="R47">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
+        <v>1.38</v>
+      </c>
+      <c r="T47">
+        <v>2.73</v>
+      </c>
+      <c r="U47">
+        <v>2.81</v>
+      </c>
+      <c r="V47">
         <v>1.4</v>
       </c>
-      <c r="T47">
-        <v>2.75</v>
-      </c>
-      <c r="U47">
-        <v>3.19</v>
-      </c>
-      <c r="V47">
-        <v>1.33</v>
-      </c>
       <c r="W47">
+        <v>1.1</v>
+      </c>
+      <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="Y47">
+        <v>1.28</v>
+      </c>
+      <c r="Z47">
+        <v>3.68</v>
+      </c>
+      <c r="AA47">
+        <v>1.92</v>
+      </c>
+      <c r="AB47">
+        <v>1.92</v>
+      </c>
+      <c r="AC47">
+        <v>3.18</v>
+      </c>
+      <c r="AD47">
+        <v>1.34</v>
+      </c>
+      <c r="AE47">
         <v>1.07</v>
       </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
-        <v>1.37</v>
-      </c>
-      <c r="Z47">
-        <v>2.83</v>
-      </c>
-      <c r="AA47">
-        <v>2.11</v>
-      </c>
-      <c r="AB47">
-        <v>1.65</v>
-      </c>
-      <c r="AC47">
-        <v>3.97</v>
-      </c>
-      <c r="AD47">
-        <v>1.2</v>
-      </c>
-      <c r="AE47">
-        <v>1.04</v>
-      </c>
       <c r="AF47">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AG47">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
+        <v>3.3</v>
+      </c>
+      <c r="O48">
+        <v>3.25</v>
+      </c>
+      <c r="P48">
+        <v>1.98</v>
+      </c>
+      <c r="Q48">
+        <v>3.89</v>
+      </c>
+      <c r="R48">
+        <v>1.97</v>
+      </c>
+      <c r="S48">
+        <v>1.4</v>
+      </c>
+      <c r="T48">
+        <v>2.75</v>
+      </c>
+      <c r="U48">
+        <v>3.19</v>
+      </c>
+      <c r="V48">
         <v>1.33</v>
       </c>
-      <c r="O48">
-        <v>5.1</v>
-      </c>
-      <c r="P48">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q48">
-        <v>1.75</v>
-      </c>
-      <c r="R48">
-        <v>2.5</v>
-      </c>
-      <c r="S48">
-        <v>1.25</v>
-      </c>
-      <c r="T48">
-        <v>3.5</v>
-      </c>
-      <c r="U48">
-        <v>2.25</v>
-      </c>
-      <c r="V48">
-        <v>1.57</v>
-      </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="Z48">
-        <v>4.65</v>
+        <v>2.83</v>
       </c>
       <c r="AA48">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="AB48">
-        <v>2.39</v>
+        <v>1.65</v>
       </c>
       <c r="AC48">
-        <v>2.45</v>
+        <v>3.97</v>
       </c>
       <c r="AD48">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AF48">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG48">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK48">
-        <v>3.09</v>
+        <v>1.16</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-10-26 20:00:00</t>
+          <t>2026-10-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="P49">
-        <v>5.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q49">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="R49">
+        <v>2.5</v>
+      </c>
+      <c r="S49">
+        <v>1.25</v>
+      </c>
+      <c r="T49">
+        <v>3.5</v>
+      </c>
+      <c r="U49">
         <v>2.25</v>
       </c>
-      <c r="S49">
-        <v>1.35</v>
-      </c>
-      <c r="T49">
-        <v>3</v>
-      </c>
-      <c r="U49">
-        <v>2.63</v>
-      </c>
       <c r="V49">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z49">
-        <v>3.28</v>
+        <v>4.65</v>
       </c>
       <c r="AA49">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AB49">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC49">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD49">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AE49">
+        <v>1.21</v>
+      </c>
+      <c r="AF49">
+        <v>1.88</v>
+      </c>
+      <c r="AG49">
+        <v>1.82</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.11</v>
       </c>
-      <c r="AF49">
-        <v>1.98</v>
-      </c>
-      <c r="AG49">
-        <v>1.72</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.22</v>
-      </c>
       <c r="AK49">
-        <v>2.44</v>
+        <v>3.09</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-10-26 20:30:00</t>
+          <t>2026-10-26 20:00:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-10-26 21:00:00</t>
+          <t>2026-10-26 20:30:00</t>
         </is>
       </c>
     </row>
@@ -8575,156 +8575,319 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Montego Bay United</t>
         </is>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51" t="inlineStr">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51">
-        <v>0</v>
-      </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <v>0</v>
-      </c>
-      <c r="Y51">
-        <v>0</v>
-      </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-      <c r="AA51">
-        <v>0</v>
-      </c>
-      <c r="AB51">
-        <v>0</v>
-      </c>
-      <c r="AC51">
-        <v>0</v>
-      </c>
-      <c r="AD51">
-        <v>0</v>
-      </c>
-      <c r="AE51">
-        <v>0</v>
-      </c>
-      <c r="AF51">
-        <v>0</v>
-      </c>
-      <c r="AG51">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>0</v>
-      </c>
-      <c r="AK51">
-        <v>0</v>
-      </c>
-      <c r="AL51">
-        <v>0</v>
-      </c>
-      <c r="AM51">
-        <v>-1</v>
-      </c>
-      <c r="AN51">
-        <v>-1</v>
-      </c>
-      <c r="AO51">
-        <v>-1</v>
-      </c>
-      <c r="AP51">
-        <v>-1</v>
-      </c>
-      <c r="AQ51">
-        <v>0</v>
-      </c>
-      <c r="AR51">
-        <v>0</v>
-      </c>
-      <c r="AS51">
-        <v>0</v>
-      </c>
-      <c r="AT51">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>-1</v>
+      </c>
+      <c r="AN52">
+        <v>-1</v>
+      </c>
+      <c r="AO52">
+        <v>-1</v>
+      </c>
+      <c r="AP52">
+        <v>-1</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
         <is>
           <t>2026-10-26 22:00:00</t>
         </is>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1338,10 +1338,10 @@
         <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG6">
         <v>2</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>3.12</v>
       </c>
       <c r="U7">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="V7">
         <v>1.53</v>
@@ -2138,7 +2138,7 @@
         <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="AA11">
         <v>1.68</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -2298,31 +2298,31 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>1.76</v>
       </c>
       <c r="AE16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF16">
         <v>1.61</v>
@@ -3089,10 +3089,10 @@
         <v>2.87</v>
       </c>
       <c r="Q17">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="R17">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="S17">
         <v>1.62</v>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG17">
         <v>1.57</v>
@@ -3252,7 +3252,7 @@
         <v>1.2</v>
       </c>
       <c r="Q18">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="R18">
         <v>2.85</v>
@@ -3279,7 +3279,7 @@
         <v>1.09</v>
       </c>
       <c r="Z18">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="AA18">
         <v>1.38</v>
@@ -3297,7 +3297,7 @@
         <v>1.27</v>
       </c>
       <c r="AF18">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG18">
         <v>1.77</v>
@@ -3412,7 +3412,7 @@
         <v>3.75</v>
       </c>
       <c r="P19">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q19">
         <v>5.1</v>
@@ -3421,10 +3421,10 @@
         <v>2.24</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U19">
         <v>2.54</v>
@@ -3433,7 +3433,7 @@
         <v>1.49</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3445,7 +3445,7 @@
         <v>3.85</v>
       </c>
       <c r="AA19">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB19">
         <v>2.08</v>
@@ -4589,7 +4589,7 @@
         <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AC26">
         <v>2.92</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O27">
         <v>3.23</v>
@@ -4946,7 +4946,7 @@
         <v>2.23</v>
       </c>
       <c r="AK28">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q30">
         <v>2.91</v>
@@ -5229,7 +5229,7 @@
         <v>1.12</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.19</v>
@@ -5416,7 +5416,7 @@
         <v>1.25</v>
       </c>
       <c r="AF31">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG31">
         <v>2.64</v>
@@ -5691,7 +5691,7 @@
         <v>7.7</v>
       </c>
       <c r="O33">
-        <v>4.8</v>
+        <v>4.35</v>
       </c>
       <c r="P33">
         <v>1.4</v>
@@ -5742,7 +5742,7 @@
         <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG33">
         <v>1.67</v>
@@ -5761,7 +5761,7 @@
         <v>2.9</v>
       </c>
       <c r="AK33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>3.25</v>
       </c>
       <c r="P39">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q39">
         <v>2.92</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
         <v>1.55</v>
@@ -6841,7 +6841,7 @@
         <v>3.75</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S40">
         <v>1.29</v>
@@ -6850,7 +6850,7 @@
         <v>3.2</v>
       </c>
       <c r="U40">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V40">
         <v>1.46</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O41">
         <v>3.4</v>
@@ -7001,19 +7001,19 @@
         <v>4</v>
       </c>
       <c r="Q41">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="R41">
         <v>2.07</v>
       </c>
       <c r="S41">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T41">
         <v>2.5</v>
       </c>
       <c r="U41">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="V41">
         <v>1.33</v>
@@ -7034,7 +7034,7 @@
         <v>2.12</v>
       </c>
       <c r="AB41">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC41">
         <v>3.45</v>
@@ -7973,10 +7973,10 @@
         <v>2.02</v>
       </c>
       <c r="O47">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -8299,10 +8299,10 @@
         <v>1.33</v>
       </c>
       <c r="O49">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P49">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q49">
         <v>1.75</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1175,7 +1175,7 @@
         <v>1.77</v>
       </c>
       <c r="AE5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
         <v>1.68</v>
@@ -1197,7 +1197,7 @@
         <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
         <v>1.61</v>
@@ -2274,28 +2274,28 @@
         <v>3.5</v>
       </c>
       <c r="Q12">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
         <v>1.2</v>
@@ -2322,7 +2322,7 @@
         <v>1.64</v>
       </c>
       <c r="AG12">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2597,19 +2597,19 @@
         <v>3.1</v>
       </c>
       <c r="P14">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q14">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S14">
         <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="U14">
         <v>3.3</v>
@@ -2636,7 +2636,7 @@
         <v>1.5</v>
       </c>
       <c r="AC14">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AD14">
         <v>1.17</v>
@@ -2645,10 +2645,10 @@
         <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AG14">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.31</v>
       </c>
       <c r="AK14">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R16">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="S16">
         <v>1.19</v>
@@ -3255,7 +3255,7 @@
         <v>8.5</v>
       </c>
       <c r="R18">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="S18">
         <v>1.16</v>
@@ -3279,7 +3279,7 @@
         <v>1.09</v>
       </c>
       <c r="Z18">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA18">
         <v>1.38</v>
@@ -3297,10 +3297,10 @@
         <v>1.27</v>
       </c>
       <c r="AF18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG18">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>3.7</v>
       </c>
       <c r="P21">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -3747,13 +3747,13 @@
         <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V21">
         <v>1.5</v>
@@ -3774,7 +3774,7 @@
         <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AC21">
         <v>2.7</v>
@@ -5045,10 +5045,10 @@
         <v>5.8</v>
       </c>
       <c r="Q29">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R29">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="S29">
         <v>1.2</v>
@@ -5063,7 +5063,7 @@
         <v>1.65</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5072,13 +5072,13 @@
         <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AA29">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB29">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AC29">
         <v>2.35</v>
@@ -5087,7 +5087,7 @@
         <v>1.6</v>
       </c>
       <c r="AE29">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF29">
         <v>1.7</v>
@@ -5109,7 +5109,7 @@
         <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5217,10 +5217,10 @@
         <v>1.31</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U30">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V30">
         <v>1.49</v>
@@ -5761,7 +5761,7 @@
         <v>2.9</v>
       </c>
       <c r="AK33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5875,7 +5875,7 @@
         <v>2</v>
       </c>
       <c r="V34">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W34">
         <v>1.2</v>
@@ -5884,16 +5884,16 @@
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z34">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA34">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB34">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="AC34">
         <v>1.97</v>
@@ -5902,7 +5902,7 @@
         <v>1.77</v>
       </c>
       <c r="AE34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF34">
         <v>1.53</v>
@@ -5924,7 +5924,7 @@
         <v>1.09</v>
       </c>
       <c r="AK34">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="O35">
-        <v>3.48</v>
+        <v>3.32</v>
       </c>
       <c r="P35">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="O36">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="P36">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q36">
         <v>3.81</v>
@@ -6222,10 +6222,10 @@
         <v>1.84</v>
       </c>
       <c r="AC36">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AK36">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,19 +6349,19 @@
         <v>3.16</v>
       </c>
       <c r="Q37">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R37">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
         <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="U37">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="V37">
         <v>1.45</v>
@@ -6373,16 +6373,16 @@
         <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z37">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA37">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB37">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC37">
         <v>2.83</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
         <v>1.55</v>
@@ -6883,7 +6883,7 @@
         <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
         <v>2.2</v>
@@ -7001,19 +7001,19 @@
         <v>4</v>
       </c>
       <c r="Q41">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R41">
         <v>2.07</v>
       </c>
       <c r="S41">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T41">
         <v>2.5</v>
       </c>
       <c r="U41">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="V41">
         <v>1.33</v>
@@ -7025,16 +7025,16 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z41">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA41">
         <v>2.12</v>
       </c>
       <c r="AB41">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC41">
         <v>3.45</v>
@@ -7046,10 +7046,10 @@
         <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG41">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O49">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="P49">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Q49">
         <v>1.75</v>
@@ -8474,7 +8474,7 @@
         <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T50">
         <v>3</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1643,7 +1643,7 @@
         <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
         <v>1.3</v>
@@ -1655,7 +1655,7 @@
         <v>1.93</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC8">
         <v>3.28</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
         <v>1.52</v>
@@ -2132,7 +2132,7 @@
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.18</v>
@@ -2147,7 +2147,7 @@
         <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
@@ -2612,10 +2612,10 @@
         <v>2.47</v>
       </c>
       <c r="U14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W14">
         <v>1.05</v>
@@ -2624,10 +2624,10 @@
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z14">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AA14">
         <v>2.5</v>
@@ -4088,7 +4088,7 @@
         <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
         <v>1.21</v>
@@ -4131,7 +4131,7 @@
         <v>1.86</v>
       </c>
       <c r="AK23">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>1.9</v>
       </c>
       <c r="O32">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5761,7 +5761,7 @@
         <v>2.9</v>
       </c>
       <c r="AK33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5866,19 +5866,19 @@
         <v>2.54</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T34">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U34">
         <v>2</v>
       </c>
       <c r="V34">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W34">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -5899,7 +5899,7 @@
         <v>1.97</v>
       </c>
       <c r="AD34">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AE34">
         <v>1.34</v>
@@ -6222,19 +6222,19 @@
         <v>1.84</v>
       </c>
       <c r="AC36">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.62</v>
       </c>
       <c r="AK36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6518,16 +6518,16 @@
         <v>2.05</v>
       </c>
       <c r="S38">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T38">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="U38">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="V38">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W38">
         <v>1.06</v>
@@ -6542,10 +6542,10 @@
         <v>3</v>
       </c>
       <c r="AA38">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC38">
         <v>3.9</v>
@@ -6684,7 +6684,7 @@
         <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="U39">
         <v>2.5</v>
@@ -6714,7 +6714,7 @@
         <v>3.1</v>
       </c>
       <c r="AD39">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
         <v>1.08</v>
@@ -6850,7 +6850,7 @@
         <v>3.2</v>
       </c>
       <c r="U40">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="V40">
         <v>1.46</v>
@@ -6862,10 +6862,10 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z40">
-        <v>3.92</v>
+        <v>4.26</v>
       </c>
       <c r="AA40">
         <v>1.68</v>
@@ -7001,13 +7001,13 @@
         <v>4</v>
       </c>
       <c r="Q41">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="R41">
         <v>2.07</v>
       </c>
       <c r="S41">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T41">
         <v>2.5</v>
@@ -7025,10 +7025,10 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z41">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA41">
         <v>2.12</v>
@@ -7046,7 +7046,7 @@
         <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG41">
         <v>1.78</v>
@@ -7357,7 +7357,7 @@
         <v>3.2</v>
       </c>
       <c r="AA43">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB43">
         <v>1.71</v>
@@ -8148,10 +8148,10 @@
         <v>1.97</v>
       </c>
       <c r="S48">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T48">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U48">
         <v>3.19</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="O49">
         <v>4.95</v>
@@ -8489,7 +8489,7 @@
         <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.25</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2138,7 +2138,7 @@
         <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA11">
         <v>1.68</v>
@@ -2147,7 +2147,7 @@
         <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
@@ -2274,25 +2274,25 @@
         <v>3.5</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="R12">
         <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2322,7 +2322,7 @@
         <v>1.64</v>
       </c>
       <c r="AG12">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>1.93</v>
       </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T14">
         <v>2.47</v>
@@ -2618,7 +2618,7 @@
         <v>1.25</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>1.04</v>
@@ -2796,7 +2796,7 @@
         <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AC15">
         <v>2.28</v>
@@ -3089,10 +3089,10 @@
         <v>2.87</v>
       </c>
       <c r="Q17">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="R17">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="S17">
         <v>1.62</v>
@@ -3113,22 +3113,22 @@
         <v>1.13</v>
       </c>
       <c r="Y17">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Z17">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA17">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="AB17">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC17">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="AD17">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE17">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
         <v>1.36</v>
@@ -3421,7 +3421,7 @@
         <v>2.24</v>
       </c>
       <c r="S19">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T19">
         <v>3.22</v>
@@ -3445,7 +3445,7 @@
         <v>3.85</v>
       </c>
       <c r="AA19">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB19">
         <v>2.08</v>
@@ -4088,7 +4088,7 @@
         <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.21</v>
@@ -4257,7 +4257,7 @@
         <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="AA24">
         <v>1.81</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O25">
         <v>3.5</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
         <v>2.88</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4900,7 +4900,7 @@
         <v>1.43</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK30">
         <v>1.5</v>
@@ -5371,10 +5371,10 @@
         <v>2.95</v>
       </c>
       <c r="Q31">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="R31">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5407,7 +5407,7 @@
         <v>2.6</v>
       </c>
       <c r="AC31">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AD31">
         <v>1.63</v>
@@ -5419,7 +5419,7 @@
         <v>1.41</v>
       </c>
       <c r="AG31">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>1.9</v>
       </c>
       <c r="O32">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P32">
         <v>4.4</v>
@@ -5691,7 +5691,7 @@
         <v>7.7</v>
       </c>
       <c r="O33">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="P33">
         <v>1.4</v>
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
         <v>3.26</v>
@@ -5761,7 +5761,7 @@
         <v>2.9</v>
       </c>
       <c r="AK33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6883,7 +6883,7 @@
         <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG40">
         <v>2.2</v>
@@ -7523,7 +7523,7 @@
         <v>1.62</v>
       </c>
       <c r="AB44">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC44">
         <v>2.5</v>
@@ -7976,7 +7976,7 @@
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7991,7 +7991,7 @@
         <v>2.73</v>
       </c>
       <c r="U47">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="V47">
         <v>1.4</v>
@@ -8006,7 +8006,7 @@
         <v>1.28</v>
       </c>
       <c r="Z47">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA47">
         <v>1.92</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O50">
         <v>3.8</v>
@@ -8489,7 +8489,7 @@
         <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.25</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O5">
         <v>5.1</v>
       </c>
       <c r="P5">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="Q5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="S5">
         <v>1.18</v>
       </c>
       <c r="T5">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="U5">
         <v>1.95</v>
@@ -1151,7 +1151,7 @@
         <v>1.75</v>
       </c>
       <c r="W5">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,25 +1160,25 @@
         <v>1.06</v>
       </c>
       <c r="Z5">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA5">
         <v>1.36</v>
       </c>
       <c r="AB5">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AC5">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AD5">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AE5">
         <v>1.28</v>
       </c>
       <c r="AF5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
         <v>2.05</v>
@@ -1197,7 +1197,7 @@
         <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O6">
         <v>4.15</v>
       </c>
       <c r="P6">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -1640,10 +1640,10 @@
         <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
         <v>1.3</v>
@@ -2105,7 +2105,7 @@
         <v>1.25</v>
       </c>
       <c r="O11">
-        <v>5.2</v>
+        <v>4.95</v>
       </c>
       <c r="P11">
         <v>7.8</v>
@@ -3412,7 +3412,7 @@
         <v>3.75</v>
       </c>
       <c r="P19">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="Q19">
         <v>5.1</v>
@@ -3433,7 +3433,7 @@
         <v>1.49</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3738,7 +3738,7 @@
         <v>3.7</v>
       </c>
       <c r="P21">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -3750,7 +3750,7 @@
         <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U21">
         <v>2.45</v>
@@ -3934,7 +3934,7 @@
         <v>3.72</v>
       </c>
       <c r="AA22">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB22">
         <v>2.07</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O23">
         <v>3.6</v>
@@ -4067,10 +4067,10 @@
         <v>1.73</v>
       </c>
       <c r="Q23">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -4094,7 +4094,7 @@
         <v>1.21</v>
       </c>
       <c r="Z23">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="AA23">
         <v>1.66</v>
@@ -4103,10 +4103,10 @@
         <v>2.21</v>
       </c>
       <c r="AC23">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE23">
         <v>1.15</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q25">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
         <v>2.38</v>
@@ -4405,10 +4405,10 @@
         <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V25">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W25">
         <v>1.17</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="O28">
         <v>3.8</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="O29">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P29">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>1.89</v>
@@ -5078,22 +5078,22 @@
         <v>1.46</v>
       </c>
       <c r="AB29">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AC29">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AD29">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE29">
         <v>1.18</v>
       </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG29">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>1.9</v>
       </c>
       <c r="O32">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P32">
         <v>4.4</v>
@@ -5691,7 +5691,7 @@
         <v>7.7</v>
       </c>
       <c r="O33">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P33">
         <v>1.4</v>
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
         <v>3.26</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="O34">
         <v>5.25</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="O35">
         <v>3.32</v>
@@ -6186,22 +6186,22 @@
         <v>2.1</v>
       </c>
       <c r="Q36">
-        <v>3.81</v>
+        <v>4.1</v>
       </c>
       <c r="R36">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S36">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U36">
         <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W36">
         <v>1.06</v>
@@ -6216,25 +6216,25 @@
         <v>3.5</v>
       </c>
       <c r="AA36">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB36">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AC36">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD36">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG36">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.62</v>
       </c>
       <c r="AK36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6358,7 +6358,7 @@
         <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
         <v>2.58</v>
@@ -6705,7 +6705,7 @@
         <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB39">
         <v>1.88</v>
@@ -6859,7 +6859,7 @@
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.21</v>
@@ -6883,7 +6883,7 @@
         <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
         <v>2.2</v>
@@ -6995,7 +6995,7 @@
         <v>1.9</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="P41">
         <v>4</v>
@@ -7031,7 +7031,7 @@
         <v>3.04</v>
       </c>
       <c r="AA41">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB41">
         <v>1.71</v>
@@ -7502,7 +7502,7 @@
         <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V44">
         <v>1.5</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O47">
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7988,10 +7988,10 @@
         <v>1.38</v>
       </c>
       <c r="T47">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="U47">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="V47">
         <v>1.4</v>
@@ -8003,22 +8003,22 @@
         <v>1</v>
       </c>
       <c r="Y47">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z47">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA47">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AB47">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC47">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="AD47">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE47">
         <v>1.07</v>
@@ -8043,7 +8043,7 @@
         <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="O49">
         <v>4.95</v>
@@ -8335,7 +8335,7 @@
         <v>4.65</v>
       </c>
       <c r="AA49">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB49">
         <v>2.39</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2597,7 +2597,7 @@
         <v>3.1</v>
       </c>
       <c r="P14">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q14">
         <v>2.72</v>
@@ -2609,7 +2609,7 @@
         <v>1.46</v>
       </c>
       <c r="T14">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="U14">
         <v>3.25</v>
@@ -2627,7 +2627,7 @@
         <v>1.43</v>
       </c>
       <c r="Z14">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="AA14">
         <v>2.5</v>
@@ -2639,7 +2639,7 @@
         <v>4.6</v>
       </c>
       <c r="AD14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
         <v>1.01</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="O18">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="P18">
         <v>1.2</v>
@@ -3255,10 +3255,10 @@
         <v>8.5</v>
       </c>
       <c r="R18">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="S18">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
         <v>4.1</v>
@@ -3279,7 +3279,7 @@
         <v>1.09</v>
       </c>
       <c r="Z18">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="AA18">
         <v>1.38</v>
@@ -3297,10 +3297,10 @@
         <v>1.27</v>
       </c>
       <c r="AF18">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG18">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>7.17</v>
+        <v>4.33</v>
       </c>
       <c r="O19">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q19">
-        <v>5.1</v>
+        <v>5.43</v>
       </c>
       <c r="R19">
         <v>2.24</v>
@@ -3424,13 +3424,13 @@
         <v>1.29</v>
       </c>
       <c r="T19">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
         <v>1.12</v>
@@ -3442,13 +3442,13 @@
         <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AA19">
         <v>1.73</v>
       </c>
       <c r="AB19">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
         <v>2.66</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O22">
         <v>3.35</v>
@@ -3937,7 +3937,7 @@
         <v>1.72</v>
       </c>
       <c r="AB22">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AC22">
         <v>2.78</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="O26">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="O27">
         <v>3.23</v>
       </c>
       <c r="P27">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q27">
         <v>3.05</v>
@@ -4755,7 +4755,7 @@
         <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AD27">
         <v>1.32</v>
@@ -7354,7 +7354,7 @@
         <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="AA43">
         <v>2.1</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="O5">
-        <v>5.1</v>
+        <v>4.15</v>
       </c>
       <c r="P5">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="R5">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="S5">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Z5">
-        <v>6.05</v>
+        <v>4.25</v>
       </c>
       <c r="AA5">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="AD5">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AE5">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF5">
         <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK5">
-        <v>3.48</v>
+        <v>2.63</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
       </c>
       <c r="R6">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V6">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA6">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AD6">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE6">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q7">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="R7">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="S7">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T7">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="U7">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z7">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AC7">
-        <v>2.52</v>
+        <v>1.9</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK7">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         <v>7.8</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R11">
         <v>2.5</v>
@@ -2120,16 +2120,16 @@
         <v>1.28</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
         <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2147,16 +2147,16 @@
         <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG11">
         <v>1.61</v>
@@ -2304,10 +2304,10 @@
         <v>3.7</v>
       </c>
       <c r="AA12">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC12">
         <v>2.81</v>
@@ -2775,10 +2775,10 @@
         <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V15">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W15">
         <v>1.11</v>
@@ -2790,13 +2790,13 @@
         <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>4.8</v>
+        <v>5.01</v>
       </c>
       <c r="AA15">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB15">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AC15">
         <v>2.28</v>
@@ -2805,7 +2805,7 @@
         <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF15">
         <v>1.5</v>
@@ -2959,7 +2959,7 @@
         <v>1.36</v>
       </c>
       <c r="AB16">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AC16">
         <v>1.92</v>
@@ -3089,16 +3089,16 @@
         <v>2.87</v>
       </c>
       <c r="Q17">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="R17">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="S17">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T17">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -3110,31 +3110,31 @@
         <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y17">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Z17">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AA17">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AB17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC17">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AD17">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG17">
         <v>1.57</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4067,10 +4067,10 @@
         <v>1.73</v>
       </c>
       <c r="Q23">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="R23">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -4079,7 +4079,7 @@
         <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V23">
         <v>1.53</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>4.19</v>
+        <v>4.4</v>
       </c>
       <c r="AA23">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB23">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="AC23">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AD23">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>3.7</v>
       </c>
       <c r="P25">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -4423,7 +4423,7 @@
         <v>5.28</v>
       </c>
       <c r="AA25">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB25">
         <v>2.49</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
         <v>2.91</v>
@@ -5374,7 +5374,7 @@
         <v>2.63</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O32">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         <v>7.7</v>
       </c>
       <c r="O33">
-        <v>4.4</v>
+        <v>4.88</v>
       </c>
       <c r="P33">
         <v>1.4</v>
@@ -5857,7 +5857,7 @@
         <v>5.25</v>
       </c>
       <c r="P34">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="Q34">
         <v>1.84</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="O35">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB39">
         <v>1.88</v>
@@ -6883,7 +6883,7 @@
         <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG40">
         <v>2.2</v>
@@ -6995,7 +6995,7 @@
         <v>1.9</v>
       </c>
       <c r="O41">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
         <v>4</v>
@@ -7339,7 +7339,7 @@
         <v>2.88</v>
       </c>
       <c r="U43">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V43">
         <v>1.36</v>
@@ -7520,7 +7520,7 @@
         <v>4.35</v>
       </c>
       <c r="AA44">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB44">
         <v>2.14</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O47">
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7991,28 +7991,28 @@
         <v>2.74</v>
       </c>
       <c r="U47">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="V47">
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="AA47">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB47">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC47">
         <v>3.09</v>
@@ -8024,10 +8024,10 @@
         <v>1.07</v>
       </c>
       <c r="AF47">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG47">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         <v>8.4</v>
       </c>
       <c r="Q49">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R49">
         <v>2.5</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -807,22 +807,22 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>4.95</v>
       </c>
       <c r="P11">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="Q11">
         <v>1.7</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P14">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
         <v>2.72</v>
@@ -2606,10 +2606,10 @@
         <v>1.93</v>
       </c>
       <c r="S14">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T14">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="U14">
         <v>3.25</v>
@@ -2618,7 +2618,7 @@
         <v>1.25</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1.04</v>
@@ -2627,13 +2627,13 @@
         <v>1.43</v>
       </c>
       <c r="Z14">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="AA14">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB14">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC14">
         <v>4.6</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="O15">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P15">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>3.28</v>
+        <v>1.76</v>
       </c>
       <c r="R15">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T15">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="V15">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z15">
-        <v>5.01</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="AC15">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AD15">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE15">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF15">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="O16">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="Q16">
-        <v>1.76</v>
+        <v>3.28</v>
       </c>
       <c r="R16">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="S16">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U16">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="V16">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="W16">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>5.01</v>
       </c>
       <c r="AA16">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AB16">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="AC16">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AD16">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF16">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3605,7 +3605,7 @@
         <v>1.46</v>
       </c>
       <c r="Z20">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AA20">
         <v>2.43</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="Q22">
-        <v>3.41</v>
+        <v>3.06</v>
       </c>
       <c r="R22">
         <v>2.2</v>
@@ -3913,13 +3913,13 @@
         <v>1.32</v>
       </c>
       <c r="T22">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="V22">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W22">
         <v>1.11</v>
@@ -3928,25 +3928,25 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="AA22">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB22">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC22">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD22">
         <v>1.41</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
         <v>1.62</v>
@@ -4230,16 +4230,16 @@
         <v>0</v>
       </c>
       <c r="Q24">
+        <v>2.17</v>
+      </c>
+      <c r="R24">
         <v>2.3</v>
-      </c>
-      <c r="R24">
-        <v>2.25</v>
       </c>
       <c r="S24">
         <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="U24">
         <v>2.5</v>
@@ -4254,28 +4254,28 @@
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z24">
-        <v>3.79</v>
+        <v>3.95</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB24">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AC24">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="AD24">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
         <v>2</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK24">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4420,16 +4420,16 @@
         <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>5.28</v>
+        <v>5.35</v>
       </c>
       <c r="AA25">
         <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AC25">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AD25">
         <v>1.65</v>
@@ -4568,10 +4568,10 @@
         <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
         <v>1.1</v>
@@ -4580,16 +4580,16 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
         <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC26">
         <v>2.92</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="O27">
         <v>3.23</v>
       </c>
       <c r="P27">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="Q27">
         <v>3.05</v>
@@ -4725,19 +4725,19 @@
         <v>2</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T27">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="U27">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="V27">
         <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
         <v>1</v>
@@ -4746,7 +4746,7 @@
         <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="AA27">
         <v>1.93</v>
@@ -4755,7 +4755,7 @@
         <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="AD27">
         <v>1.32</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="O28">
         <v>3.8</v>
@@ -4912,13 +4912,13 @@
         <v>3.6</v>
       </c>
       <c r="AA28">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
         <v>1.95</v>
       </c>
       <c r="AC28">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="AD28">
         <v>1.31</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O30">
         <v>3.4</v>
@@ -5217,7 +5217,7 @@
         <v>1.31</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
         <v>2.42</v>
@@ -5235,7 +5235,7 @@
         <v>1.19</v>
       </c>
       <c r="Z30">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="AA30">
         <v>1.74</v>
@@ -5374,7 +5374,7 @@
         <v>2.63</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5398,7 +5398,7 @@
         <v>1.09</v>
       </c>
       <c r="Z31">
-        <v>5.55</v>
+        <v>5.63</v>
       </c>
       <c r="AA31">
         <v>1.49</v>
@@ -5528,7 +5528,7 @@
         <v>1.91</v>
       </c>
       <c r="O32">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P32">
         <v>3.9</v>
@@ -5691,7 +5691,7 @@
         <v>7.7</v>
       </c>
       <c r="O33">
-        <v>4.88</v>
+        <v>4.54</v>
       </c>
       <c r="P33">
         <v>1.4</v>
@@ -5700,7 +5700,7 @@
         <v>5.8</v>
       </c>
       <c r="R33">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="S33">
         <v>1.35</v>
@@ -5712,19 +5712,19 @@
         <v>2.62</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
         <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>3.26</v>
+        <v>4.1</v>
       </c>
       <c r="AA33">
         <v>1.81</v>
@@ -5733,16 +5733,16 @@
         <v>2.01</v>
       </c>
       <c r="AC33">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD33">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AG33">
         <v>1.67</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="O34">
         <v>5.25</v>
       </c>
       <c r="P34">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="Q34">
         <v>1.84</v>
@@ -5887,7 +5887,7 @@
         <v>1.08</v>
       </c>
       <c r="Z34">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA34">
         <v>1.37</v>
@@ -5899,7 +5899,7 @@
         <v>1.97</v>
       </c>
       <c r="AD34">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE34">
         <v>1.34</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>3.1</v>
       </c>
       <c r="O38">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P38">
         <v>2.31</v>
@@ -6518,19 +6518,19 @@
         <v>2.05</v>
       </c>
       <c r="S38">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T38">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="U38">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="V38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
         <v>1.02</v>
@@ -6545,7 +6545,7 @@
         <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC38">
         <v>3.9</v>
@@ -6672,7 +6672,7 @@
         <v>3.25</v>
       </c>
       <c r="P39">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q39">
         <v>2.92</v>
@@ -6684,7 +6684,7 @@
         <v>1.36</v>
       </c>
       <c r="T39">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="U39">
         <v>2.5</v>
@@ -6865,16 +6865,16 @@
         <v>1.21</v>
       </c>
       <c r="Z40">
-        <v>4.26</v>
+        <v>3.92</v>
       </c>
       <c r="AA40">
         <v>1.68</v>
       </c>
       <c r="AB40">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC40">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AD40">
         <v>1.43</v>
@@ -6883,7 +6883,7 @@
         <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
         <v>2.2</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O41">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P41">
         <v>4</v>
       </c>
       <c r="Q41">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="R41">
         <v>2.07</v>
@@ -7013,7 +7013,7 @@
         <v>2.5</v>
       </c>
       <c r="U41">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="V41">
         <v>1.33</v>
@@ -7022,10 +7022,10 @@
         <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z41">
         <v>3.04</v>
@@ -7034,19 +7034,19 @@
         <v>2.2</v>
       </c>
       <c r="AB41">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC41">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AD41">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE41">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG41">
         <v>1.78</v>
@@ -7194,16 +7194,16 @@
         <v>2.92</v>
       </c>
       <c r="AA42">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB42">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC42">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="AD42">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE42">
         <v>1.03</v>
@@ -7228,7 +7228,7 @@
         <v>1.34</v>
       </c>
       <c r="AK42">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7520,7 +7520,7 @@
         <v>4.35</v>
       </c>
       <c r="AA44">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB44">
         <v>2.14</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O47">
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7985,10 +7985,10 @@
         <v>2.2</v>
       </c>
       <c r="S47">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T47">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="U47">
         <v>2.81</v>
@@ -8009,16 +8009,16 @@
         <v>3.8</v>
       </c>
       <c r="AA47">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB47">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC47">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="AD47">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE47">
         <v>1.07</v>
@@ -8043,7 +8043,7 @@
         <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -807,22 +807,22 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>5.7</v>
       </c>
       <c r="Q5">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R5">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S5">
         <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U5">
         <v>2.25</v>
@@ -1154,7 +1154,7 @@
         <v>1.1</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
         <v>1.15</v>
@@ -1166,10 +1166,10 @@
         <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC5">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AD5">
         <v>1.46</v>
@@ -1197,7 +1197,7 @@
         <v>1.13</v>
       </c>
       <c r="AK5">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S6">
         <v>1.28</v>
@@ -1317,7 +1317,7 @@
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.18</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
         <v>5.5</v>
       </c>
       <c r="P7">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q7">
         <v>1.65</v>
@@ -1465,7 +1465,7 @@
         <v>2.8</v>
       </c>
       <c r="S7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
         <v>3.82</v>
@@ -1474,7 +1474,7 @@
         <v>1.95</v>
       </c>
       <c r="V7">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W7">
         <v>1.18</v>
@@ -1489,16 +1489,16 @@
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB7">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AC7">
         <v>1.9</v>
       </c>
       <c r="AD7">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE7">
         <v>1.3</v>
@@ -2108,7 +2108,7 @@
         <v>4.95</v>
       </c>
       <c r="P11">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q11">
         <v>1.7</v>
@@ -2156,7 +2156,7 @@
         <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
         <v>1.61</v>
@@ -2292,16 +2292,16 @@
         <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
         <v>1.72</v>
@@ -2310,19 +2310,19 @@
         <v>2.07</v>
       </c>
       <c r="AC12">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="Q15">
-        <v>1.76</v>
+        <v>3.28</v>
       </c>
       <c r="R15">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="S15">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="V15">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="W15">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>5.01</v>
       </c>
       <c r="AA15">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AB15">
-        <v>3.1</v>
+        <v>2.27</v>
       </c>
       <c r="AC15">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AD15">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF15">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P16">
+        <v>7</v>
+      </c>
+      <c r="Q16">
+        <v>1.76</v>
+      </c>
+      <c r="R16">
+        <v>2.56</v>
+      </c>
+      <c r="S16">
+        <v>1.19</v>
+      </c>
+      <c r="T16">
+        <v>4.5</v>
+      </c>
+      <c r="U16">
         <v>1.95</v>
       </c>
-      <c r="Q16">
-        <v>3.28</v>
-      </c>
-      <c r="R16">
-        <v>2.35</v>
-      </c>
-      <c r="S16">
-        <v>1.25</v>
-      </c>
-      <c r="T16">
-        <v>3.6</v>
-      </c>
-      <c r="U16">
-        <v>2.33</v>
-      </c>
       <c r="V16">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z16">
-        <v>5.01</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AB16">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="AC16">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AD16">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE16">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG16">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="O20">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="P20">
         <v>2.55</v>
@@ -3762,7 +3762,7 @@
         <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
         <v>1.18</v>
@@ -3774,10 +3774,10 @@
         <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AC21">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AD21">
         <v>1.36</v>
@@ -3901,7 +3901,7 @@
         <v>3.3</v>
       </c>
       <c r="P22">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="Q22">
         <v>3.06</v>
@@ -4079,7 +4079,7 @@
         <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V23">
         <v>1.53</v>
@@ -4088,7 +4088,7 @@
         <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
         <v>1.18</v>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="R24">
         <v>2.3</v>
@@ -4242,7 +4242,7 @@
         <v>3.26</v>
       </c>
       <c r="U24">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V24">
         <v>1.44</v>
@@ -4251,28 +4251,28 @@
         <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AA24">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB24">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AC24">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AD24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
         <v>1.73</v>
@@ -4294,7 +4294,7 @@
         <v>1.18</v>
       </c>
       <c r="AK24">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>3.3</v>
       </c>
       <c r="P26">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AK26">
         <v>1.22</v>
@@ -5039,28 +5039,28 @@
         <v>1.49</v>
       </c>
       <c r="O29">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="P29">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Q29">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R29">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="S29">
         <v>1.2</v>
       </c>
       <c r="T29">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="U29">
         <v>2.15</v>
       </c>
       <c r="V29">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="W29">
         <v>1.11</v>
@@ -5069,25 +5069,25 @@
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z29">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA29">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB29">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AC29">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AD29">
         <v>1.57</v>
       </c>
       <c r="AE29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
         <v>1.65</v>
@@ -5109,7 +5109,7 @@
         <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5404,10 +5404,10 @@
         <v>1.49</v>
       </c>
       <c r="AB31">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AC31">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD31">
         <v>1.63</v>
@@ -6201,7 +6201,7 @@
         <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
         <v>1.06</v>
@@ -6216,10 +6216,10 @@
         <v>3.5</v>
       </c>
       <c r="AA36">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB36">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
         <v>2.92</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,22 +6349,22 @@
         <v>3.16</v>
       </c>
       <c r="Q37">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S37">
         <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="U37">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6376,13 +6376,13 @@
         <v>1.21</v>
       </c>
       <c r="Z37">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA37">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC37">
         <v>2.83</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK37">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6545,7 +6545,7 @@
         <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC38">
         <v>3.9</v>
@@ -6669,10 +6669,10 @@
         <v>2.45</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q39">
         <v>2.92</v>
@@ -6693,7 +6693,7 @@
         <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1.04</v>
@@ -6883,7 +6883,7 @@
         <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG40">
         <v>2.2</v>
@@ -6998,7 +6998,7 @@
         <v>3.46</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>3.63</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -7028,19 +7028,19 @@
         <v>1.4</v>
       </c>
       <c r="Z41">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AA41">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB41">
         <v>1.7</v>
       </c>
       <c r="AC41">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="AD41">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE41">
         <v>1.04</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O43">
         <v>3.45</v>
@@ -7339,7 +7339,7 @@
         <v>2.88</v>
       </c>
       <c r="U43">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V43">
         <v>1.36</v>
@@ -7354,7 +7354,7 @@
         <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="AA43">
         <v>2.1</v>
@@ -8139,7 +8139,7 @@
         <v>3.25</v>
       </c>
       <c r="P48">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q48">
         <v>3.89</v>
@@ -8148,13 +8148,13 @@
         <v>1.97</v>
       </c>
       <c r="S48">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T48">
         <v>2.71</v>
       </c>
       <c r="U48">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="V48">
         <v>1.33</v>
@@ -8166,7 +8166,7 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z48">
         <v>2.83</v>
@@ -8178,7 +8178,7 @@
         <v>1.65</v>
       </c>
       <c r="AC48">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="AD48">
         <v>1.2</v>
@@ -8477,7 +8477,7 @@
         <v>1.39</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U50">
         <v>2.63</v>
@@ -8489,7 +8489,7 @@
         <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.25</v>
@@ -8504,10 +8504,10 @@
         <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="AD50">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE50">
         <v>1.11</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -807,22 +807,22 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,16 +970,16 @@
         <v>3.96</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -994,10 +994,10 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA4">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="O8">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="Q8">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="U8">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z8">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA8">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AB8">
         <v>1.73</v>
       </c>
       <c r="AC8">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
         <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2120,16 +2120,16 @@
         <v>1.28</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
         <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2141,7 +2141,7 @@
         <v>4.33</v>
       </c>
       <c r="AA11">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB11">
         <v>2.15</v>
@@ -2594,10 +2594,10 @@
         <v>1.95</v>
       </c>
       <c r="O14">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q14">
         <v>2.72</v>
@@ -2627,7 +2627,7 @@
         <v>1.43</v>
       </c>
       <c r="Z14">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AA14">
         <v>2.4</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="O15">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P15">
+        <v>7</v>
+      </c>
+      <c r="Q15">
+        <v>1.76</v>
+      </c>
+      <c r="R15">
+        <v>2.56</v>
+      </c>
+      <c r="S15">
+        <v>1.19</v>
+      </c>
+      <c r="T15">
+        <v>4.5</v>
+      </c>
+      <c r="U15">
         <v>1.95</v>
       </c>
-      <c r="Q15">
-        <v>3.28</v>
-      </c>
-      <c r="R15">
-        <v>2.35</v>
-      </c>
-      <c r="S15">
-        <v>1.25</v>
-      </c>
-      <c r="T15">
-        <v>3.6</v>
-      </c>
-      <c r="U15">
-        <v>2.33</v>
-      </c>
       <c r="V15">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z15">
-        <v>5.01</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.27</v>
+        <v>3.1</v>
       </c>
       <c r="AC15">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="AD15">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE15">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF15">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK15">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="O16">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="Q16">
-        <v>1.76</v>
+        <v>3.28</v>
       </c>
       <c r="R16">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="S16">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="U16">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="V16">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="W16">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>5.01</v>
       </c>
       <c r="AA16">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AB16">
-        <v>3.1</v>
+        <v>2.27</v>
       </c>
       <c r="AC16">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="AD16">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF16">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,16 +3089,16 @@
         <v>2.87</v>
       </c>
       <c r="Q17">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="R17">
         <v>1.83</v>
       </c>
       <c r="S17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T17">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -3113,31 +3113,31 @@
         <v>1.1</v>
       </c>
       <c r="Y17">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z17">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="AA17">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB17">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AD17">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG17">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.4</v>
       </c>
       <c r="AK17">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>4.33</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
         <v>1.6</v>
@@ -3424,7 +3424,7 @@
         <v>1.29</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U19">
         <v>2.38</v>
@@ -3445,7 +3445,7 @@
         <v>3.84</v>
       </c>
       <c r="AA19">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB19">
         <v>2.1</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O22">
         <v>3.3</v>
       </c>
       <c r="P22">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="Q22">
         <v>3.06</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AK22">
         <v>1.38</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O23">
         <v>3.6</v>
@@ -4076,7 +4076,7 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="U23">
         <v>2.38</v>
@@ -4399,16 +4399,16 @@
         <v>2.38</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T25">
         <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V25">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W25">
         <v>1.17</v>
@@ -4580,10 +4580,10 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
         <v>1.85</v>
@@ -4592,7 +4592,7 @@
         <v>1.91</v>
       </c>
       <c r="AC26">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
         <v>1.31</v>
@@ -4912,7 +4912,7 @@
         <v>3.6</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB28">
         <v>1.95</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AK28">
         <v>1.13</v>
@@ -5057,10 +5057,10 @@
         <v>3.55</v>
       </c>
       <c r="U29">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="V29">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W29">
         <v>1.11</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK29">
         <v>2.62</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
         <v>3.4</v>
@@ -5208,7 +5208,7 @@
         <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="R30">
         <v>2.18</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AK30">
         <v>1.5</v>
@@ -5371,10 +5371,10 @@
         <v>2.95</v>
       </c>
       <c r="Q31">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5407,7 +5407,7 @@
         <v>2.56</v>
       </c>
       <c r="AC31">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD31">
         <v>1.63</v>
@@ -5435,7 +5435,7 @@
         <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5724,7 +5724,7 @@
         <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA33">
         <v>1.81</v>
@@ -5739,7 +5739,7 @@
         <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
         <v>2.11</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>2.9</v>
+        <v>1.14</v>
       </c>
       <c r="AK33">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5884,25 +5884,25 @@
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z34">
         <v>6.5</v>
       </c>
       <c r="AA34">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB34">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="AC34">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD34">
         <v>1.8</v>
       </c>
       <c r="AE34">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF34">
         <v>1.53</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.2</v>
+        <v>2.03</v>
       </c>
       <c r="O36">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="P36">
-        <v>2.1</v>
+        <v>3.16</v>
       </c>
       <c r="Q36">
-        <v>4.1</v>
+        <v>2.62</v>
       </c>
       <c r="R36">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T36">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z36">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA36">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC36">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.03</v>
+        <v>3.2</v>
       </c>
       <c r="O37">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="P37">
-        <v>3.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q37">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="R37">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="U37">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z37">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA37">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB37">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC37">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD37">
+        <v>1.31</v>
+      </c>
+      <c r="AE37">
+        <v>1.08</v>
+      </c>
+      <c r="AF37">
+        <v>1.66</v>
+      </c>
+      <c r="AG37">
+        <v>2.05</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>1.65</v>
+      </c>
+      <c r="AK37">
         <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.09</v>
-      </c>
-      <c r="AF37">
-        <v>1.62</v>
-      </c>
-      <c r="AG37">
-        <v>2.08</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.27</v>
-      </c>
-      <c r="AK37">
-        <v>1.59</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         <v>2.31</v>
       </c>
       <c r="Q38">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="R38">
         <v>2.05</v>
@@ -6545,7 +6545,7 @@
         <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC38">
         <v>3.9</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AK38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="O39">
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q39">
         <v>2.92</v>
@@ -6705,7 +6705,7 @@
         <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB39">
         <v>1.88</v>
@@ -6739,7 +6739,7 @@
         <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>3.3</v>
       </c>
       <c r="O40">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="P40">
         <v>2.05</v>
@@ -6850,7 +6850,7 @@
         <v>3.2</v>
       </c>
       <c r="U40">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
         <v>1.46</v>
@@ -7001,7 +7001,7 @@
         <v>3.63</v>
       </c>
       <c r="Q41">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="R41">
         <v>2.07</v>
@@ -7191,13 +7191,13 @@
         <v>1.38</v>
       </c>
       <c r="Z42">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AA42">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB42">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC42">
         <v>3.82</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK42">
         <v>1.42</v>
@@ -7327,7 +7327,7 @@
         <v>3.65</v>
       </c>
       <c r="Q43">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R43">
         <v>2.1</v>
@@ -7342,7 +7342,7 @@
         <v>2.8</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W43">
         <v>1.05</v>
@@ -7354,10 +7354,10 @@
         <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="AA43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB43">
         <v>1.71</v>
@@ -7375,7 +7375,7 @@
         <v>1.9</v>
       </c>
       <c r="AG43">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7496,34 +7496,34 @@
         <v>2.4</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T44">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U44">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V44">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W44">
         <v>1.12</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.35</v>
+        <v>4.58</v>
       </c>
       <c r="AA44">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB44">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC44">
         <v>2.5</v>
@@ -7532,13 +7532,13 @@
         <v>1.46</v>
       </c>
       <c r="AE44">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF44">
         <v>1.67</v>
       </c>
       <c r="AG44">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="O47">
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7991,7 +7991,7 @@
         <v>2.76</v>
       </c>
       <c r="U47">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="V47">
         <v>1.4</v>
@@ -8043,7 +8043,7 @@
         <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8139,7 +8139,7 @@
         <v>3.25</v>
       </c>
       <c r="P48">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q48">
         <v>3.89</v>
@@ -8151,10 +8151,10 @@
         <v>1.44</v>
       </c>
       <c r="T48">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="U48">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="V48">
         <v>1.33</v>
@@ -8178,7 +8178,7 @@
         <v>1.65</v>
       </c>
       <c r="AC48">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="AD48">
         <v>1.2</v>
@@ -8206,7 +8206,7 @@
         <v>1.21</v>
       </c>
       <c r="AK48">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="O49">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="P49">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Q49">
         <v>1.73</v>
@@ -8369,7 +8369,7 @@
         <v>1.11</v>
       </c>
       <c r="AK49">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="O5">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="P5">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="Q5">
+        <v>1.65</v>
+      </c>
+      <c r="R5">
+        <v>2.8</v>
+      </c>
+      <c r="S5">
+        <v>1.2</v>
+      </c>
+      <c r="T5">
+        <v>3.82</v>
+      </c>
+      <c r="U5">
         <v>1.95</v>
       </c>
-      <c r="R5">
-        <v>2.63</v>
-      </c>
-      <c r="S5">
-        <v>1.25</v>
-      </c>
-      <c r="T5">
+      <c r="V5">
+        <v>1.75</v>
+      </c>
+      <c r="W5">
+        <v>1.18</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.07</v>
+      </c>
+      <c r="Z5">
+        <v>7</v>
+      </c>
+      <c r="AA5">
+        <v>1.36</v>
+      </c>
+      <c r="AB5">
+        <v>2.75</v>
+      </c>
+      <c r="AC5">
+        <v>1.9</v>
+      </c>
+      <c r="AD5">
+        <v>1.77</v>
+      </c>
+      <c r="AE5">
+        <v>1.3</v>
+      </c>
+      <c r="AF5">
+        <v>1.67</v>
+      </c>
+      <c r="AG5">
+        <v>2.05</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.04</v>
+      </c>
+      <c r="AK5">
         <v>3.4</v>
-      </c>
-      <c r="U5">
-        <v>2.25</v>
-      </c>
-      <c r="V5">
-        <v>1.55</v>
-      </c>
-      <c r="W5">
-        <v>1.1</v>
-      </c>
-      <c r="X5">
-        <v>1.03</v>
-      </c>
-      <c r="Y5">
-        <v>1.15</v>
-      </c>
-      <c r="Z5">
-        <v>4.25</v>
-      </c>
-      <c r="AA5">
-        <v>1.57</v>
-      </c>
-      <c r="AB5">
-        <v>2.35</v>
-      </c>
-      <c r="AC5">
-        <v>2.51</v>
-      </c>
-      <c r="AD5">
-        <v>1.46</v>
-      </c>
-      <c r="AE5">
-        <v>1.17</v>
-      </c>
-      <c r="AF5">
-        <v>1.7</v>
-      </c>
-      <c r="AG5">
-        <v>2</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.13</v>
-      </c>
-      <c r="AK5">
-        <v>2.6</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA6">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC6">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AD6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T7">
-        <v>3.82</v>
+        <v>3.12</v>
       </c>
       <c r="U7">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="V7">
+        <v>1.53</v>
+      </c>
+      <c r="W7">
+        <v>1.08</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
+        <v>1.18</v>
+      </c>
+      <c r="Z7">
+        <v>4.4</v>
+      </c>
+      <c r="AA7">
+        <v>1.63</v>
+      </c>
+      <c r="AB7">
+        <v>2.1</v>
+      </c>
+      <c r="AC7">
+        <v>2.63</v>
+      </c>
+      <c r="AD7">
+        <v>1.44</v>
+      </c>
+      <c r="AE7">
+        <v>1.14</v>
+      </c>
+      <c r="AF7">
         <v>1.75</v>
       </c>
-      <c r="W7">
-        <v>1.18</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>1.07</v>
-      </c>
-      <c r="Z7">
-        <v>7</v>
-      </c>
-      <c r="AA7">
-        <v>1.36</v>
-      </c>
-      <c r="AB7">
-        <v>2.75</v>
-      </c>
-      <c r="AC7">
-        <v>1.9</v>
-      </c>
-      <c r="AD7">
-        <v>1.77</v>
-      </c>
-      <c r="AE7">
-        <v>1.3</v>
-      </c>
-      <c r="AF7">
-        <v>1.67</v>
-      </c>
       <c r="AG7">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
         <v>3.5</v>
@@ -2292,7 +2292,7 @@
         <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2319,7 +2319,7 @@
         <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG12">
         <v>2.25</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.24</v>
+        <v>2.13</v>
       </c>
       <c r="O13">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="P13">
-        <v>1.89</v>
+        <v>3.48</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
+        <v>2.15</v>
+      </c>
+      <c r="O14">
+        <v>2.92</v>
+      </c>
+      <c r="P14">
+        <v>3.1</v>
+      </c>
+      <c r="Q14">
+        <v>2.9</v>
+      </c>
+      <c r="R14">
         <v>1.95</v>
       </c>
-      <c r="O14">
-        <v>3.1</v>
-      </c>
-      <c r="P14">
-        <v>3.65</v>
-      </c>
-      <c r="Q14">
-        <v>2.72</v>
-      </c>
-      <c r="R14">
-        <v>1.93</v>
-      </c>
       <c r="S14">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T14">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U14">
         <v>3.25</v>
@@ -2621,34 +2621,34 @@
         <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y14">
         <v>1.43</v>
       </c>
       <c r="Z14">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AA14">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB14">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC14">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AD14">
         <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF14">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AG14">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R15">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="S15">
         <v>1.19</v>
@@ -2775,10 +2775,10 @@
         <v>4.5</v>
       </c>
       <c r="U15">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V15">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W15">
         <v>1.2</v>
@@ -2929,7 +2929,7 @@
         <v>3.28</v>
       </c>
       <c r="R16">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="S16">
         <v>1.25</v>
@@ -2938,10 +2938,10 @@
         <v>3.6</v>
       </c>
       <c r="U16">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="V16">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W16">
         <v>1.11</v>
@@ -2953,16 +2953,16 @@
         <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>5.01</v>
+        <v>5.07</v>
       </c>
       <c r="AA16">
         <v>1.54</v>
       </c>
       <c r="AB16">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="AC16">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="AD16">
         <v>1.5</v>
@@ -3098,7 +3098,7 @@
         <v>1.62</v>
       </c>
       <c r="T17">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -3107,13 +3107,13 @@
         <v>1.18</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
         <v>1.1</v>
       </c>
       <c r="Y17">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z17">
         <v>2.3</v>
@@ -3122,10 +3122,10 @@
         <v>2.88</v>
       </c>
       <c r="AB17">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AC17">
-        <v>6.5</v>
+        <v>6.18</v>
       </c>
       <c r="AD17">
         <v>1.1</v>
@@ -3134,10 +3134,10 @@
         <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3406,43 +3406,43 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="O19">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q19">
-        <v>5.43</v>
+        <v>5.45</v>
       </c>
       <c r="R19">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="S19">
         <v>1.29</v>
       </c>
       <c r="T19">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="U19">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AA19">
         <v>1.7</v>
@@ -3451,19 +3451,19 @@
         <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD19">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
         <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3735,61 +3735,61 @@
         <v>1.75</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P21">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q21">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="U21">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="AA21">
         <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC21">
         <v>2.81</v>
       </c>
       <c r="AD21">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE21">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF21">
         <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK21">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="O22">
         <v>3.3</v>
       </c>
       <c r="P22">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="Q22">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S22">
         <v>1.32</v>
@@ -3916,7 +3916,7 @@
         <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="V22">
         <v>1.47</v>
@@ -3940,7 +3940,7 @@
         <v>2.04</v>
       </c>
       <c r="AC22">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="AD22">
         <v>1.41</v>
@@ -3952,7 +3952,7 @@
         <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.26</v>
       </c>
       <c r="AK22">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="Q23">
         <v>4.33</v>
@@ -4076,7 +4076,7 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
         <v>2.38</v>
@@ -4088,7 +4088,7 @@
         <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.18</v>
@@ -4233,13 +4233,13 @@
         <v>2.3</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S24">
         <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="U24">
         <v>2.63</v>
@@ -4260,10 +4260,10 @@
         <v>3.8</v>
       </c>
       <c r="AA24">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC24">
         <v>3.1</v>
@@ -4275,10 +4275,10 @@
         <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4420,22 +4420,22 @@
         <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="AA25">
         <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AC25">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AD25">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE25">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF25">
         <v>1.44</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O26">
         <v>3.3</v>
@@ -4562,7 +4562,7 @@
         <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
         <v>2.88</v>
@@ -4574,7 +4574,7 @@
         <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4586,16 +4586,16 @@
         <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB26">
         <v>1.91</v>
       </c>
       <c r="AC26">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="AD26">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE26">
         <v>1.08</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
         <v>1.22</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O27">
         <v>3.23</v>
       </c>
       <c r="P27">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
         <v>3.05</v>
@@ -4728,10 +4728,10 @@
         <v>1.37</v>
       </c>
       <c r="T27">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="U27">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
         <v>1.4</v>
@@ -4746,7 +4746,7 @@
         <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="AA27">
         <v>1.93</v>
@@ -4755,7 +4755,7 @@
         <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="AD27">
         <v>1.32</v>
@@ -4764,10 +4764,10 @@
         <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG27">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="P28">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -4918,13 +4918,13 @@
         <v>1.95</v>
       </c>
       <c r="AC28">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AD28">
         <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
         <v>1.85</v>
@@ -5368,13 +5368,13 @@
         <v>3.8</v>
       </c>
       <c r="P31">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q31">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="R31">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5386,7 +5386,7 @@
         <v>2.1</v>
       </c>
       <c r="V31">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W31">
         <v>1.18</v>
@@ -5398,13 +5398,13 @@
         <v>1.09</v>
       </c>
       <c r="Z31">
-        <v>5.63</v>
+        <v>5.7</v>
       </c>
       <c r="AA31">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB31">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC31">
         <v>2.19</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O32">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>4.54</v>
+        <v>4.45</v>
       </c>
       <c r="P33">
         <v>1.4</v>
@@ -5700,7 +5700,7 @@
         <v>5.8</v>
       </c>
       <c r="R33">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S33">
         <v>1.35</v>
@@ -5715,16 +5715,16 @@
         <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
         <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA33">
         <v>1.81</v>
@@ -5739,10 +5739,10 @@
         <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AG33">
         <v>1.67</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
         <v>1.03</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="O34">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P34">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q34">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="R34">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="S34">
         <v>1.18</v>
       </c>
       <c r="T34">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U34">
         <v>2</v>
       </c>
       <c r="V34">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W34">
         <v>1.22</v>
@@ -5887,28 +5887,28 @@
         <v>1.07</v>
       </c>
       <c r="Z34">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA34">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB34">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="AC34">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AD34">
         <v>1.8</v>
       </c>
       <c r="AE34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG34">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK34">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>3.1</v>
       </c>
       <c r="O38">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P38">
         <v>2.31</v>
@@ -6521,10 +6521,10 @@
         <v>1.45</v>
       </c>
       <c r="T38">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U38">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="V38">
         <v>1.35</v>
@@ -6542,7 +6542,7 @@
         <v>3</v>
       </c>
       <c r="AA38">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB38">
         <v>1.66</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AK38">
         <v>1.29</v>
@@ -6681,16 +6681,16 @@
         <v>2.14</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T39">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="U39">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="V39">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W39">
         <v>1.07</v>
@@ -6998,10 +6998,10 @@
         <v>3.46</v>
       </c>
       <c r="P41">
-        <v>3.63</v>
+        <v>4.2</v>
       </c>
       <c r="Q41">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="R41">
         <v>2.07</v>
@@ -7013,10 +7013,10 @@
         <v>2.5</v>
       </c>
       <c r="U41">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
         <v>1.07</v>
@@ -7025,7 +7025,7 @@
         <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z41">
         <v>3.1</v>
@@ -7046,7 +7046,7 @@
         <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG41">
         <v>1.78</v>
@@ -7490,7 +7490,7 @@
         <v>4.33</v>
       </c>
       <c r="Q44">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="R44">
         <v>2.4</v>
@@ -7520,10 +7520,10 @@
         <v>4.58</v>
       </c>
       <c r="AA44">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB44">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC44">
         <v>2.5</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O45">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="P45">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="Q45">
         <v>1.82</v>
@@ -7816,55 +7816,55 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8021,7 +8021,7 @@
         <v>1.34</v>
       </c>
       <c r="AE47">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
         <v>1.69</v>
@@ -8139,7 +8139,7 @@
         <v>3.25</v>
       </c>
       <c r="P48">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q48">
         <v>3.89</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O50">
         <v>3.8</v>
@@ -8489,7 +8489,7 @@
         <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.25</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC52">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="P2">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB2">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="R3">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="S3">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="T3">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="U3">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="V3">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y3">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="Z3">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="AA3">
-        <v>3.43</v>
+        <v>3.06</v>
       </c>
       <c r="AB3">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>2.61</v>
+        <v>2.29</v>
       </c>
       <c r="AG3">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="O4">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>3.96</v>
+        <v>4.33</v>
       </c>
       <c r="Q4">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="R4">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="S4">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T4">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="Z4">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF4">
-        <v>2.73</v>
+        <v>2.31</v>
       </c>
       <c r="AG4">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="O5">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="P5">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q5">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="R5">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="S5">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="U5">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="V5">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AB5">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AD5">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="U6">
-        <v>2.25</v>
+        <v>2.64</v>
       </c>
       <c r="V6">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
+        <v>1.22</v>
+      </c>
+      <c r="Z6">
+        <v>3.9</v>
+      </c>
+      <c r="AA6">
+        <v>1.77</v>
+      </c>
+      <c r="AB6">
+        <v>1.9</v>
+      </c>
+      <c r="AC6">
+        <v>3</v>
+      </c>
+      <c r="AD6">
+        <v>1.32</v>
+      </c>
+      <c r="AE6">
         <v>1.15</v>
       </c>
-      <c r="Z6">
-        <v>4.25</v>
-      </c>
-      <c r="AA6">
-        <v>1.57</v>
-      </c>
-      <c r="AB6">
-        <v>2.35</v>
-      </c>
-      <c r="AC6">
-        <v>2.51</v>
-      </c>
-      <c r="AD6">
-        <v>1.46</v>
-      </c>
-      <c r="AE6">
-        <v>1.17</v>
-      </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK6">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="R7">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="S7">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="U7">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z7">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC7">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="AD7">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AF7">
         <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK7">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>1.25</v>
       </c>
       <c r="O11">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="P11">
         <v>7.8</v>
@@ -2117,13 +2117,13 @@
         <v>2.5</v>
       </c>
       <c r="S11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
         <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V11">
         <v>1.44</v>
@@ -2138,16 +2138,16 @@
         <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
         <v>1.67</v>
       </c>
       <c r="AB11">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
@@ -2159,7 +2159,7 @@
         <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="O13">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="P13">
-        <v>3.48</v>
+        <v>3.17</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="O14">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="P14">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q14">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S14">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T14">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V14">
         <v>1.25</v>
@@ -2621,34 +2621,34 @@
         <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y14">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z14">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="AA14">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AB14">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC14">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE14">
         <v>1</v>
       </c>
       <c r="AF14">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG14">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="Q15">
-        <v>1.77</v>
+        <v>3.28</v>
       </c>
       <c r="R15">
-        <v>2.97</v>
+        <v>2.52</v>
       </c>
       <c r="S15">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="V15">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>5.08</v>
       </c>
       <c r="AA15">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AB15">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC15">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="AD15">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF15">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P16">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>3.28</v>
+        <v>1.76</v>
       </c>
       <c r="R16">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T16">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="U16">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="V16">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z16">
-        <v>5.07</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AB16">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="AC16">
-        <v>2.47</v>
+        <v>1.99</v>
       </c>
       <c r="AD16">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE16">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG16">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK16">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P19">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="Q19">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="R19">
         <v>2.18</v>
@@ -3424,13 +3424,13 @@
         <v>1.29</v>
       </c>
       <c r="T19">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
         <v>1.08</v>
@@ -3439,31 +3439,31 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA19">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB19">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC19">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
         <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="O20">
         <v>3</v>
@@ -3578,7 +3578,7 @@
         <v>2.55</v>
       </c>
       <c r="Q20">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="R20">
         <v>1.83</v>
@@ -3599,13 +3599,13 @@
         <v>1</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y20">
         <v>1.46</v>
       </c>
       <c r="Z20">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AA20">
         <v>2.43</v>
@@ -3614,13 +3614,13 @@
         <v>1.51</v>
       </c>
       <c r="AC20">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="AD20">
         <v>1.16</v>
       </c>
       <c r="AE20">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
         <v>1.99</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O21">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
         <v>3.55</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
         <v>1.87</v>
@@ -4067,7 +4067,7 @@
         <v>1.61</v>
       </c>
       <c r="Q23">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="R23">
         <v>2.3</v>
@@ -4100,7 +4100,7 @@
         <v>1.64</v>
       </c>
       <c r="AB23">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
         <v>2.63</v>
@@ -4112,7 +4112,7 @@
         <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
         <v>2.15</v>
@@ -4553,7 +4553,7 @@
         <v>3.3</v>
       </c>
       <c r="P26">
-        <v>2.56</v>
+        <v>1.97</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -4562,7 +4562,7 @@
         <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
         <v>2.88</v>
@@ -4574,7 +4574,7 @@
         <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4586,7 +4586,7 @@
         <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
         <v>1.91</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="O29">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="P29">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q29">
         <v>1.92</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK29">
         <v>2.62</v>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q30">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="R30">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="S30">
         <v>1.31</v>
@@ -5220,13 +5220,13 @@
         <v>3.3</v>
       </c>
       <c r="U30">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="V30">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1.02</v>
@@ -5238,25 +5238,25 @@
         <v>4.04</v>
       </c>
       <c r="AA30">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AB30">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC30">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD30">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE30">
         <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG30">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
         <v>5.7</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="O33">
-        <v>4.45</v>
+        <v>4.72</v>
       </c>
       <c r="P33">
         <v>1.4</v>
       </c>
       <c r="Q33">
-        <v>5.8</v>
+        <v>5.61</v>
       </c>
       <c r="R33">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
         <v>1.35</v>
@@ -5742,7 +5742,7 @@
         <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AG33">
         <v>1.67</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK33">
         <v>1.03</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="O34">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P34">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q34">
         <v>1.78</v>
@@ -5887,7 +5887,7 @@
         <v>1.07</v>
       </c>
       <c r="Z34">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA34">
         <v>1.34</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK34">
         <v>3.12</v>
@@ -6017,10 +6017,10 @@
         <v>2.01</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P35">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O38">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P38">
         <v>2.31</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P39">
         <v>2.7</v>
@@ -6684,10 +6684,10 @@
         <v>1.37</v>
       </c>
       <c r="T39">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="U39">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="V39">
         <v>1.41</v>
@@ -7188,13 +7188,13 @@
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z42">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AA42">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AB42">
         <v>1.61</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
         <v>1.42</v>
@@ -7324,7 +7324,7 @@
         <v>3.45</v>
       </c>
       <c r="P43">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -7333,19 +7333,19 @@
         <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U43">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V43">
         <v>1.37</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
         <v>1.04</v>
@@ -7354,7 +7354,7 @@
         <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AA43">
         <v>2.05</v>
@@ -7366,7 +7366,7 @@
         <v>3.5</v>
       </c>
       <c r="AD43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE43">
         <v>1.04</v>
@@ -7490,7 +7490,7 @@
         <v>4.33</v>
       </c>
       <c r="Q44">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="R44">
         <v>2.4</v>
@@ -7505,7 +7505,7 @@
         <v>2.25</v>
       </c>
       <c r="V44">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W44">
         <v>1.12</v>
@@ -7517,19 +7517,19 @@
         <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.58</v>
+        <v>4.63</v>
       </c>
       <c r="AA44">
         <v>1.61</v>
       </c>
       <c r="AB44">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC44">
         <v>2.5</v>
       </c>
       <c r="AD44">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE44">
         <v>1.2</v>
@@ -7647,10 +7647,10 @@
         <v>1.36</v>
       </c>
       <c r="O45">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="P45">
-        <v>5.75</v>
+        <v>5.1</v>
       </c>
       <c r="Q45">
         <v>1.82</v>
@@ -7659,16 +7659,16 @@
         <v>2.7</v>
       </c>
       <c r="S45">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T45">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="V45">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W45">
         <v>1.21</v>
@@ -7683,22 +7683,22 @@
         <v>5.75</v>
       </c>
       <c r="AA45">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB45">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AC45">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AD45">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE45">
         <v>1.3</v>
       </c>
       <c r="AF45">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
         <v>2.34</v>
@@ -7807,65 +7807,65 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q46">
+        <v>2.22</v>
+      </c>
+      <c r="R46">
         <v>2.3</v>
       </c>
-      <c r="R46">
-        <v>2.25</v>
-      </c>
       <c r="S46">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="U46">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="AA46">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB46">
+        <v>1.99</v>
+      </c>
+      <c r="AC46">
+        <v>2.68</v>
+      </c>
+      <c r="AD46">
+        <v>1.41</v>
+      </c>
+      <c r="AE46">
+        <v>1.13</v>
+      </c>
+      <c r="AF46">
+        <v>1.65</v>
+      </c>
+      <c r="AG46">
         <v>2.05</v>
       </c>
-      <c r="AC46">
-        <v>2.88</v>
-      </c>
-      <c r="AD46">
-        <v>1.4</v>
-      </c>
-      <c r="AE46">
-        <v>1.14</v>
-      </c>
-      <c r="AF46">
-        <v>1.67</v>
-      </c>
-      <c r="AG46">
-        <v>2.1</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK46">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="O47">
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -7997,7 +7997,7 @@
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
         <v>1.04</v>
@@ -8139,7 +8139,7 @@
         <v>3.25</v>
       </c>
       <c r="P48">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q48">
         <v>3.89</v>
@@ -8151,10 +8151,10 @@
         <v>1.44</v>
       </c>
       <c r="T48">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="U48">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="V48">
         <v>1.33</v>
@@ -8178,7 +8178,7 @@
         <v>1.65</v>
       </c>
       <c r="AC48">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="AD48">
         <v>1.2</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="O49">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P49">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q49">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R49">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8347,7 +8347,7 @@
         <v>1.53</v>
       </c>
       <c r="AE49">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF49">
         <v>1.88</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q50">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R50">
         <v>2.25</v>
@@ -8477,7 +8477,7 @@
         <v>1.39</v>
       </c>
       <c r="T50">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="U50">
         <v>2.63</v>
@@ -8504,13 +8504,13 @@
         <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="AD50">
         <v>1.33</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
         <v>1.98</v>
@@ -8631,7 +8631,7 @@
         <v>19.5</v>
       </c>
       <c r="Q51">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="R51">
         <v>4.1</v>
@@ -8643,25 +8643,25 @@
         <v>6.1</v>
       </c>
       <c r="U51">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V51">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="W51">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51">
         <v>1.04</v>
       </c>
       <c r="Z51">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AA51">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AB51">
         <v>4.8</v>
@@ -8673,13 +8673,13 @@
         <v>2.56</v>
       </c>
       <c r="AE51">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AF51">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG51">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>3.16</v>
       </c>
       <c r="P52">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="Q52">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q3">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="R3">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="S3">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T3">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="U3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
         <v>1.01</v>
       </c>
       <c r="X3">
+        <v>1.05</v>
+      </c>
+      <c r="Y3">
+        <v>1.51</v>
+      </c>
+      <c r="Z3">
+        <v>2.33</v>
+      </c>
+      <c r="AA3">
+        <v>2.56</v>
+      </c>
+      <c r="AB3">
+        <v>1.4</v>
+      </c>
+      <c r="AC3">
+        <v>5.3</v>
+      </c>
+      <c r="AD3">
         <v>1.09</v>
       </c>
-      <c r="Y3">
-        <v>1.66</v>
-      </c>
-      <c r="Z3">
-        <v>2.13</v>
-      </c>
-      <c r="AA3">
-        <v>3.06</v>
-      </c>
-      <c r="AB3">
-        <v>1.32</v>
-      </c>
-      <c r="AC3">
-        <v>5.8</v>
-      </c>
-      <c r="AD3">
-        <v>1.07</v>
-      </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AG3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.45</v>
+        <v>3.01</v>
       </c>
       <c r="R4">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="S4">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="T4">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="U4">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y4">
+        <v>1.66</v>
+      </c>
+      <c r="Z4">
+        <v>2.13</v>
+      </c>
+      <c r="AA4">
+        <v>3.06</v>
+      </c>
+      <c r="AB4">
+        <v>1.32</v>
+      </c>
+      <c r="AC4">
+        <v>5.8</v>
+      </c>
+      <c r="AD4">
+        <v>1.07</v>
+      </c>
+      <c r="AE4">
+        <v>1.03</v>
+      </c>
+      <c r="AF4">
+        <v>2.29</v>
+      </c>
+      <c r="AG4">
         <v>1.51</v>
       </c>
-      <c r="Z4">
-        <v>2.33</v>
-      </c>
-      <c r="AA4">
-        <v>2.56</v>
-      </c>
-      <c r="AB4">
-        <v>1.4</v>
-      </c>
-      <c r="AC4">
-        <v>5.3</v>
-      </c>
-      <c r="AD4">
-        <v>1.09</v>
-      </c>
-      <c r="AE4">
-        <v>1.01</v>
-      </c>
-      <c r="AF4">
-        <v>2.31</v>
-      </c>
-      <c r="AG4">
-        <v>1.5</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="O10">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q12">
         <v>2.39</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="O14">
         <v>2.85</v>
       </c>
       <c r="P14">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q14">
         <v>3.22</v>
       </c>
       <c r="R14">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S14">
         <v>1.53</v>
@@ -2618,7 +2618,7 @@
         <v>1.25</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1.11</v>
@@ -2627,10 +2627,10 @@
         <v>1.47</v>
       </c>
       <c r="Z14">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AA14">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AB14">
         <v>1.47</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="O15">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P15">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>3.28</v>
+        <v>1.76</v>
       </c>
       <c r="R15">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T15">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="U15">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="V15">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z15">
-        <v>5.08</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC15">
-        <v>2.47</v>
+        <v>1.99</v>
       </c>
       <c r="AD15">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE15">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF15">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK15">
-        <v>1.23</v>
+        <v>3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="O16">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="Q16">
-        <v>1.76</v>
+        <v>3.28</v>
       </c>
       <c r="R16">
-        <v>2.98</v>
+        <v>2.52</v>
       </c>
       <c r="S16">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="U16">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="V16">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="W16">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>5.08</v>
       </c>
       <c r="AA16">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AB16">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC16">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="AD16">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF16">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="O18">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="P18">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Q18">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R18">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="S18">
+        <v>1.22</v>
+      </c>
+      <c r="T18">
+        <v>3.8</v>
+      </c>
+      <c r="U18">
+        <v>2.05</v>
+      </c>
+      <c r="V18">
+        <v>1.66</v>
+      </c>
+      <c r="W18">
         <v>1.17</v>
       </c>
-      <c r="T18">
-        <v>4.1</v>
-      </c>
-      <c r="U18">
-        <v>1.98</v>
-      </c>
-      <c r="V18">
-        <v>1.71</v>
-      </c>
-      <c r="W18">
-        <v>1.18</v>
-      </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA18">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB18">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AC18">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AD18">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AE18">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF18">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG18">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.04</v>
       </c>
       <c r="AK18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="O19">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="Q19">
         <v>5.43</v>
@@ -3445,7 +3445,7 @@
         <v>3.82</v>
       </c>
       <c r="AA19">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB19">
         <v>1.98</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>2.13</v>
       </c>
       <c r="AK19">
         <v>1.12</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Q22">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="R22">
         <v>2.14</v>
@@ -3934,7 +3934,7 @@
         <v>3.85</v>
       </c>
       <c r="AA22">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB22">
         <v>2.04</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O26">
         <v>3.3</v>
       </c>
       <c r="P26">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q26">
         <v>4</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S26">
         <v>1.35</v>
@@ -4589,7 +4589,7 @@
         <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC26">
         <v>2.93</v>
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="O27">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
+        <v>2.71</v>
+      </c>
+      <c r="Q27">
         <v>2.75</v>
       </c>
-      <c r="Q27">
-        <v>3.05</v>
-      </c>
       <c r="R27">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S27">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V27">
         <v>1.4</v>
@@ -4749,10 +4749,10 @@
         <v>3.56</v>
       </c>
       <c r="AA27">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC27">
         <v>3.29</v>
@@ -4761,7 +4761,7 @@
         <v>1.32</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
         <v>1.73</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="O28">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="P28">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q28">
-        <v>6</v>
+        <v>5.03</v>
       </c>
       <c r="R28">
         <v>2.25</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AK28">
         <v>1.13</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AK30">
         <v>1.44</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O36">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
         <v>2.62</v>
@@ -6216,7 +6216,7 @@
         <v>3.8</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB36">
         <v>2</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P37">
         <v>2.1</v>
@@ -6352,7 +6352,7 @@
         <v>4.1</v>
       </c>
       <c r="R37">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S37">
         <v>1.33</v>
@@ -6382,7 +6382,7 @@
         <v>1.85</v>
       </c>
       <c r="AB37">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC37">
         <v>2.92</v>
@@ -6391,7 +6391,7 @@
         <v>1.31</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
         <v>1.66</v>
@@ -6413,7 +6413,7 @@
         <v>1.65</v>
       </c>
       <c r="AK37">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>3.3</v>
       </c>
       <c r="O40">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="P40">
         <v>2.05</v>
@@ -6850,10 +6850,10 @@
         <v>3.2</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V40">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
         <v>1.06</v>
@@ -6868,13 +6868,13 @@
         <v>3.92</v>
       </c>
       <c r="AA40">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB40">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC40">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AD40">
         <v>1.43</v>
@@ -6883,7 +6883,7 @@
         <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
         <v>2.2</v>
@@ -7001,10 +7001,10 @@
         <v>4.2</v>
       </c>
       <c r="Q41">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="R41">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="S41">
         <v>1.46</v>
@@ -7013,7 +7013,7 @@
         <v>2.5</v>
       </c>
       <c r="U41">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="V41">
         <v>1.3</v>
@@ -7065,7 +7065,7 @@
         <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="O43">
         <v>3.45</v>
       </c>
       <c r="P43">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -7354,13 +7354,13 @@
         <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="AA43">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB43">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC43">
         <v>3.5</v>
@@ -7391,7 +7391,7 @@
         <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL43">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P3">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R3">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="S3">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="T3">
+        <v>2.15</v>
+      </c>
+      <c r="U3">
+        <v>4.1</v>
+      </c>
+      <c r="V3">
+        <v>1.2</v>
+      </c>
+      <c r="W3">
+        <v>1.02</v>
+      </c>
+      <c r="X3">
+        <v>1.11</v>
+      </c>
+      <c r="Y3">
+        <v>1.62</v>
+      </c>
+      <c r="Z3">
+        <v>2.12</v>
+      </c>
+      <c r="AA3">
+        <v>2.9</v>
+      </c>
+      <c r="AB3">
+        <v>1.36</v>
+      </c>
+      <c r="AC3">
+        <v>7</v>
+      </c>
+      <c r="AD3">
+        <v>1.07</v>
+      </c>
+      <c r="AE3">
+        <v>1.02</v>
+      </c>
+      <c r="AF3">
         <v>2.4</v>
-      </c>
-      <c r="U3">
-        <v>3.8</v>
-      </c>
-      <c r="V3">
-        <v>1.22</v>
-      </c>
-      <c r="W3">
-        <v>1.01</v>
-      </c>
-      <c r="X3">
-        <v>1.05</v>
-      </c>
-      <c r="Y3">
-        <v>1.51</v>
-      </c>
-      <c r="Z3">
-        <v>2.33</v>
-      </c>
-      <c r="AA3">
-        <v>2.56</v>
-      </c>
-      <c r="AB3">
-        <v>1.4</v>
-      </c>
-      <c r="AC3">
-        <v>5.3</v>
-      </c>
-      <c r="AD3">
-        <v>1.09</v>
-      </c>
-      <c r="AE3">
-        <v>1.01</v>
-      </c>
-      <c r="AF3">
-        <v>2.31</v>
       </c>
       <c r="AG3">
         <v>1.5</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="R4">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S4">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T4">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y4">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Z4">
         <v>2.13</v>
       </c>
       <c r="AA4">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="AB4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC4">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>1.07</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AG4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK4">
         <v>1.53</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC5">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AD5">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE5">
         <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK5">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q6">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
-        <v>3.29</v>
+        <v>3.82</v>
       </c>
       <c r="U6">
-        <v>2.64</v>
+        <v>1.99</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="Z6">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AB6">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="AC6">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="AD6">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK6">
-        <v>2.01</v>
+        <v>3.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,61 +1450,61 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="O7">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="P7">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q7">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="R7">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="U7">
-        <v>1.99</v>
+        <v>2.31</v>
       </c>
       <c r="V7">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="W7">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AA7">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AD7">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AE7">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG7">
         <v>2</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         <v>1.25</v>
       </c>
       <c r="O11">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P11">
-        <v>7.8</v>
+        <v>9.25</v>
       </c>
       <c r="Q11">
         <v>1.7</v>
@@ -2120,13 +2120,13 @@
         <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
         <v>2.6</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
         <v>1.11</v>
@@ -2141,10 +2141,10 @@
         <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB11">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC11">
         <v>2.88</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q12">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="R12">
         <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
         <v>1.09</v>
@@ -2298,31 +2298,31 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="AA12">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB12">
         <v>2.07</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AD12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
         <v>1.73</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="O13">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="P13">
-        <v>3.17</v>
+        <v>3.91</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R15">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="S15">
         <v>1.19</v>
@@ -2787,22 +2787,22 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA15">
         <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AC15">
         <v>1.99</v>
       </c>
       <c r="AD15">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AE15">
         <v>1.33</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q16">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="R16">
         <v>2.52</v>
@@ -2959,7 +2959,7 @@
         <v>1.54</v>
       </c>
       <c r="AB16">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AC16">
         <v>2.47</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3125,7 +3125,7 @@
         <v>1.39</v>
       </c>
       <c r="AC17">
-        <v>6.18</v>
+        <v>6.2</v>
       </c>
       <c r="AD17">
         <v>1.1</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O23">
         <v>3.55</v>
@@ -4067,7 +4067,7 @@
         <v>1.61</v>
       </c>
       <c r="Q23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R23">
         <v>2.3</v>
@@ -4097,7 +4097,7 @@
         <v>4.4</v>
       </c>
       <c r="AA23">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB23">
         <v>2.15</v>
@@ -4260,10 +4260,10 @@
         <v>3.8</v>
       </c>
       <c r="AA24">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB24">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AC24">
         <v>3.1</v>
@@ -4294,7 +4294,7 @@
         <v>1.18</v>
       </c>
       <c r="AK24">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O25">
         <v>3.7</v>
@@ -5214,7 +5214,7 @@
         <v>2.37</v>
       </c>
       <c r="S30">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
         <v>3.3</v>
@@ -5235,13 +5235,13 @@
         <v>1.19</v>
       </c>
       <c r="Z30">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="AA30">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB30">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC30">
         <v>2.78</v>
@@ -5253,7 +5253,7 @@
         <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
         <v>2.3</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="P31">
         <v>3.15</v>
       </c>
       <c r="Q31">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R31">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5386,28 +5386,28 @@
         <v>2.1</v>
       </c>
       <c r="V31">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W31">
         <v>1.18</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>5.7</v>
+        <v>5.74</v>
       </c>
       <c r="AA31">
         <v>1.47</v>
       </c>
       <c r="AB31">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AC31">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AD31">
         <v>1.63</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK31">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="O32">
         <v>3</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="O33">
         <v>4.72</v>
@@ -5697,7 +5697,7 @@
         <v>1.4</v>
       </c>
       <c r="Q33">
-        <v>5.61</v>
+        <v>5.7</v>
       </c>
       <c r="R33">
         <v>2.23</v>
@@ -5718,13 +5718,13 @@
         <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA33">
         <v>1.81</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
         <v>1.03</v>
@@ -5860,22 +5860,22 @@
         <v>6.5</v>
       </c>
       <c r="Q34">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="R34">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="S34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U34">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V34">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="W34">
         <v>1.22</v>
@@ -5899,7 +5899,7 @@
         <v>1.95</v>
       </c>
       <c r="AD34">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE34">
         <v>1.34</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="O35">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="P35">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6506,13 +6506,13 @@
         <v>3.15</v>
       </c>
       <c r="O38">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P38">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="R38">
         <v>2.05</v>
@@ -6687,10 +6687,10 @@
         <v>3.05</v>
       </c>
       <c r="U39">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
         <v>1.07</v>
@@ -6739,7 +6739,7 @@
         <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O41">
         <v>3.46</v>
@@ -7004,16 +7004,16 @@
         <v>2.4</v>
       </c>
       <c r="R41">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S41">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T41">
         <v>2.5</v>
       </c>
       <c r="U41">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="V41">
         <v>1.3</v>
@@ -7031,7 +7031,7 @@
         <v>3.1</v>
       </c>
       <c r="AA41">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB41">
         <v>1.7</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
         <v>1.93</v>
@@ -7327,19 +7327,19 @@
         <v>4.05</v>
       </c>
       <c r="Q43">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R43">
         <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T43">
         <v>2.67</v>
       </c>
       <c r="U43">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="V43">
         <v>1.37</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7484,25 +7484,25 @@
         <v>1.61</v>
       </c>
       <c r="O44">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P44">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R44">
         <v>2.4</v>
       </c>
       <c r="S44">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
         <v>3.26</v>
       </c>
       <c r="U44">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V44">
         <v>1.55</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="O45">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="Q45">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R45">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S45">
         <v>1.2</v>
@@ -7665,43 +7665,43 @@
         <v>4</v>
       </c>
       <c r="U45">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V45">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="W45">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z45">
-        <v>5.75</v>
+        <v>5.15</v>
       </c>
       <c r="AA45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB45">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AC45">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AD45">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AE45">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG45">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK45">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7973,7 +7973,7 @@
         <v>2.04</v>
       </c>
       <c r="O47">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
         <v>3.4</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK47">
         <v>1.67</v>
@@ -8299,16 +8299,16 @@
         <v>1.3</v>
       </c>
       <c r="O49">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P49">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Q49">
         <v>1.67</v>
       </c>
       <c r="R49">
-        <v>2.87</v>
+        <v>2.41</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="O51">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P51">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Q51">
         <v>1.29</v>
       </c>
       <c r="R51">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="S51">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="T51">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="U51">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V51">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="W51">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X51">
         <v>1</v>
@@ -8658,28 +8658,28 @@
         <v>1.04</v>
       </c>
       <c r="Z51">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA51">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AB51">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AC51">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AD51">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AE51">
         <v>1.73</v>
       </c>
       <c r="AF51">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AG51">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.03</v>
       </c>
       <c r="AK51">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -3578,7 +3578,7 @@
         <v>2.55</v>
       </c>
       <c r="Q20">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R20">
         <v>1.83</v>
@@ -3642,7 +3642,7 @@
         <v>1.39</v>
       </c>
       <c r="AK20">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
@@ -3934,7 +3934,7 @@
         <v>3.85</v>
       </c>
       <c r="AA22">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB22">
         <v>2.04</v>
@@ -6862,28 +6862,28 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
         <v>3.92</v>
       </c>
       <c r="AA40">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB40">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AC40">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="AD40">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE40">
         <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG40">
         <v>2.2</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK40">
         <v>1.3</v>
@@ -7816,22 +7816,22 @@
         <v>4.2</v>
       </c>
       <c r="Q46">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T46">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U46">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W46">
         <v>1.11</v>
@@ -7846,19 +7846,19 @@
         <v>3.86</v>
       </c>
       <c r="AA46">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB46">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AC46">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="AD46">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE46">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
         <v>1.65</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="O52">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="P52">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA52">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB52">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.4</v>
+        <v>3.54</v>
       </c>
       <c r="O15">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>1.94</v>
       </c>
       <c r="Q15">
-        <v>1.77</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>2.96</v>
+        <v>2.52</v>
       </c>
       <c r="S15">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="V15">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>6.5</v>
+        <v>5.08</v>
       </c>
       <c r="AA15">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AB15">
-        <v>2.81</v>
+        <v>2.43</v>
       </c>
       <c r="AC15">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="AD15">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF15">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK15">
-        <v>3</v>
+        <v>1.21</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.54</v>
+        <v>1.4</v>
       </c>
       <c r="O16">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="P16">
-        <v>1.94</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="R16">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T16">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="U16">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="V16">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z16">
-        <v>5.08</v>
+        <v>6.5</v>
       </c>
       <c r="AA16">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AB16">
-        <v>2.43</v>
+        <v>2.81</v>
       </c>
       <c r="AC16">
-        <v>2.47</v>
+        <v>1.99</v>
       </c>
       <c r="AD16">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE16">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG16">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK16">
-        <v>1.21</v>
+        <v>3</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/jogos_2026-10-26.xlsx
+++ b/jogos_2026-10-26.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.54</v>
+        <v>1.4</v>
       </c>
       <c r="O15">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="P15">
-        <v>1.94</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="R15">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T15">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="U15">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="V15">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>5.08</v>
+        <v>6.5</v>
       </c>
       <c r="AA15">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.43</v>
+        <v>2.81</v>
       </c>
       <c r="AC15">
-        <v>2.47</v>
+        <v>1.99</v>
       </c>
       <c r="AD15">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE15">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF15">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK15">
-        <v>1.21</v>
+        <v>3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.4</v>
+        <v>3.54</v>
       </c>
       <c r="O16">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>7</v>
+        <v>1.94</v>
       </c>
       <c r="Q16">
-        <v>1.77</v>
+        <v>3.5</v>
       </c>
       <c r="R16">
-        <v>2.96</v>
+        <v>2.52</v>
       </c>
       <c r="S16">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="U16">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="V16">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="W16">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>6.5</v>
+        <v>5.08</v>
       </c>
       <c r="AA16">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AB16">
-        <v>2.81</v>
+        <v>2.43</v>
       </c>
       <c r="AC16">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="AD16">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF16">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>3</v>
+        <v>1.21</v>
       </c>
       <c r="AL16">
         <v>0</v>
